--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1997,6 +1997,6135 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120082669</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91884</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>654314</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7007905</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120088111</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Renudden, Renudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>654070</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7008447</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120088520</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svartnäset, Svartnäset, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>654121</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7008041</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120087568</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>654173</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7008502</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på  gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120082271</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svartnäset, Svartnäset, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>654150</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7007925</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120085193</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>654207</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7008193</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120085424</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>654284</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7008101</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120086638</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>654208</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7008351</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120086783</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>654209</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7008406</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120086159</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>654239</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7008276</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120085068</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91005</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>654217</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7008168</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120085411</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>658</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>654207</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7008193</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120082434</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>654303</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7007918</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120088261</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svartnäsviken, Svartnäsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>654154</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7008250</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120088639</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svartnäset, Svartnäset, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>654098</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7007903</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120085434</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>654217</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7008312</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120081327</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Svartnäset, Svartnäset, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>654200</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7007872</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120085506</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90905</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>654287</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7008086</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120085300</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91005</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>654207</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7008193</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120085930</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91005</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>654269</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7008197</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120087649</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>654117</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7008449</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120085648</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>654195</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7008349</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120088260</v>
+      </c>
+      <c r="B36" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>654139</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7008299</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120085706</v>
+      </c>
+      <c r="B37" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>654297</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7008132</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120087230</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>658</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>654170</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7008380</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120088364</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90905</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>654153</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7008523</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120087250</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>654191</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7008385</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120082342</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Svartnäset, Svartnäset, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>654125</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7007981</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120087102</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>654149</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7008498</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120087238</v>
+      </c>
+      <c r="B43" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>654193</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7008384</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120085493</v>
+      </c>
+      <c r="B44" t="n">
+        <v>86878</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>510</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>654196</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7008339</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120086991</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>654156</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7008421</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120088184</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>654118</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7008347</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120088072</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>654111</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7008487</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120082215</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Svartnäset, Svartnäset, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>654150</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7007925</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120085695</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>654200</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7008363</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120085468</v>
+      </c>
+      <c r="B50" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>654268</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7008096</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120082329</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>654290</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7007940</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120085919</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>654285</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7008199</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120085757</v>
+      </c>
+      <c r="B53" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>658</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>654286</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7008186</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120085755</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>654292</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7008151</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120082158</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Svartnäset, Svartnäset, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>654220</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7007891</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120088486</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Svartnäset, Svartnäset, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>654118</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7008045</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120085939</v>
+      </c>
+      <c r="B57" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>654279</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7008217</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120086958</v>
+      </c>
+      <c r="B58" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>654151</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7008440</v>
+      </c>
+      <c r="S58" t="n">
+        <v>20</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120087288</v>
+      </c>
+      <c r="B59" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>654159</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7008481</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120087985</v>
+      </c>
+      <c r="B60" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>654128</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7008520</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120086940</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78263</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>654160</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7008398</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120086920</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>654164</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7008398</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120085485</v>
+      </c>
+      <c r="B63" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>658</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>654276</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7008093</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120085491</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>654200</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7008326</v>
+      </c>
+      <c r="S64" t="n">
+        <v>20</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120085759</v>
+      </c>
+      <c r="B65" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>654293</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7008191</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120082934</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Svartnäset, Svartnäset, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>654181</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7007955</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120082214</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>654279</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7007930</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färskt bohål.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120088189</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>654128</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7008344</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Vibyggerå</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -4345,10 +4345,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120085648</v>
+        <v>120088260</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4361,21 +4361,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654195</v>
+        <v>654139</v>
       </c>
       <c r="R35" t="n">
-        <v>7008349</v>
+        <v>7008299</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4430,12 +4430,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4450,22 +4445,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120088260</v>
+        <v>120085648</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4478,21 +4473,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4502,10 +4497,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654139</v>
+        <v>654195</v>
       </c>
       <c r="R36" t="n">
-        <v>7008299</v>
+        <v>7008349</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4537,7 +4532,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4547,7 +4542,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4562,12 +4562,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120088364</v>
+        <v>120087250</v>
       </c>
       <c r="B39" t="n">
-        <v>90905</v>
+        <v>90527</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4790,25 +4790,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4818,13 +4818,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654153</v>
+        <v>654191</v>
       </c>
       <c r="R39" t="n">
-        <v>7008523</v>
+        <v>7008385</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4868,22 +4868,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120087250</v>
+        <v>120088364</v>
       </c>
       <c r="B40" t="n">
-        <v>90527</v>
+        <v>90905</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4892,25 +4892,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4920,13 +4920,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654191</v>
+        <v>654153</v>
       </c>
       <c r="R40" t="n">
-        <v>7008385</v>
+        <v>7008523</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4970,12 +4970,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5899,7 +5899,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120085695</v>
+        <v>120082329</v>
       </c>
       <c r="B49" t="n">
         <v>57310</v>
@@ -5935,14 +5935,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654200</v>
+        <v>654290</v>
       </c>
       <c r="R49" t="n">
-        <v>7008363</v>
+        <v>7007940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6004,22 +6004,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120085468</v>
+        <v>120085695</v>
       </c>
       <c r="B50" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6028,41 +6028,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654268</v>
+        <v>654200</v>
       </c>
       <c r="R50" t="n">
-        <v>7008096</v>
+        <v>7008363</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6089,9 +6089,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6106,19 +6121,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120082329</v>
+        <v>120085919</v>
       </c>
       <c r="B51" t="n">
         <v>57310</v>
@@ -6158,10 +6173,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654290</v>
+        <v>654285</v>
       </c>
       <c r="R51" t="n">
-        <v>7007940</v>
+        <v>7008199</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6193,7 +6208,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6203,7 +6218,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6235,10 +6250,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120085919</v>
+        <v>120085468</v>
       </c>
       <c r="B52" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6247,25 +6262,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6275,13 +6290,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654285</v>
+        <v>654268</v>
       </c>
       <c r="R52" t="n">
-        <v>7008199</v>
+        <v>7008096</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6308,24 +6323,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6340,12 +6340,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7232,10 +7232,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120086940</v>
+        <v>120082214</v>
       </c>
       <c r="B61" t="n">
-        <v>78263</v>
+        <v>57326</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7248,34 +7248,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654160</v>
+        <v>654279</v>
       </c>
       <c r="R61" t="n">
-        <v>7008398</v>
+        <v>7007930</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7317,7 +7317,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7332,19 +7337,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120086920</v>
+        <v>120088189</v>
       </c>
       <c r="B62" t="n">
         <v>57310</v>
@@ -7384,10 +7389,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654164</v>
+        <v>654128</v>
       </c>
       <c r="R62" t="n">
-        <v>7008398</v>
+        <v>7008344</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7419,7 +7424,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7429,12 +7434,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7449,22 +7454,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120085485</v>
+        <v>120086940</v>
       </c>
       <c r="B63" t="n">
-        <v>90846</v>
+        <v>78263</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7477,37 +7482,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654276</v>
+        <v>654160</v>
       </c>
       <c r="R63" t="n">
-        <v>7008093</v>
+        <v>7008398</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7534,9 +7539,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7551,19 +7566,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120085491</v>
+        <v>120086920</v>
       </c>
       <c r="B64" t="n">
         <v>57310</v>
@@ -7603,13 +7618,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654200</v>
+        <v>654164</v>
       </c>
       <c r="R64" t="n">
-        <v>7008326</v>
+        <v>7008398</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7638,7 +7653,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7648,12 +7663,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7680,10 +7695,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120085759</v>
+        <v>120085485</v>
       </c>
       <c r="B65" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7696,21 +7711,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7720,10 +7735,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654293</v>
+        <v>654276</v>
       </c>
       <c r="R65" t="n">
-        <v>7008191</v>
+        <v>7008093</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7782,10 +7797,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120082934</v>
+        <v>120085491</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7794,41 +7809,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654181</v>
+        <v>654200</v>
       </c>
       <c r="R66" t="n">
-        <v>7007955</v>
+        <v>7008326</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7857,7 +7872,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7867,7 +7882,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7894,10 +7914,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120082214</v>
+        <v>120085759</v>
       </c>
       <c r="B67" t="n">
-        <v>57326</v>
+        <v>90562</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7910,21 +7930,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7934,13 +7954,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654279</v>
+        <v>654293</v>
       </c>
       <c r="R67" t="n">
-        <v>7007930</v>
+        <v>7008191</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7967,24 +7987,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7999,22 +8004,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120088189</v>
+        <v>120082934</v>
       </c>
       <c r="B68" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8023,38 +8028,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654128</v>
+        <v>654181</v>
       </c>
       <c r="R68" t="n">
-        <v>7008344</v>
+        <v>7007955</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8086,7 +8091,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8096,12 +8101,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8116,12 +8116,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120082669</v>
+        <v>120087250</v>
       </c>
       <c r="B14" t="n">
-        <v>91884</v>
+        <v>90527</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,41 +2011,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654314</v>
+        <v>654191</v>
       </c>
       <c r="R14" t="n">
-        <v>7007905</v>
+        <v>7008385</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,19 +2072,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2099,22 +2089,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088111</v>
+        <v>120086991</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2123,38 +2113,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renudden, Renudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654070</v>
+        <v>654156</v>
       </c>
       <c r="R15" t="n">
-        <v>7008447</v>
+        <v>7008421</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2176,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2186,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2211,22 +2206,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088520</v>
+        <v>120085485</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2239,37 +2234,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654121</v>
+        <v>654276</v>
       </c>
       <c r="R16" t="n">
-        <v>7008041</v>
+        <v>7008093</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2296,24 +2291,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,22 +2308,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120087568</v>
+        <v>120085411</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,37 +2336,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654173</v>
+        <v>654207</v>
       </c>
       <c r="R17" t="n">
-        <v>7008502</v>
+        <v>7008193</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2413,24 +2393,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,22 +2410,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120082271</v>
+        <v>120085759</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2473,37 +2438,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654150</v>
+        <v>654293</v>
       </c>
       <c r="R18" t="n">
-        <v>7007925</v>
+        <v>7008191</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2530,24 +2495,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,22 +2512,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120085193</v>
+        <v>120082934</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,41 +2536,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654207</v>
+        <v>654181</v>
       </c>
       <c r="R19" t="n">
-        <v>7008193</v>
+        <v>7007955</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2647,9 +2597,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2664,22 +2624,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120085424</v>
+        <v>120081327</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,37 +2652,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654284</v>
+        <v>654200</v>
       </c>
       <c r="R20" t="n">
-        <v>7008101</v>
+        <v>7007872</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2749,19 +2709,14 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:29</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,19 +2731,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120086638</v>
+        <v>120088639</v>
       </c>
       <c r="B21" t="n">
         <v>57310</v>
@@ -2824,14 +2779,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654208</v>
+        <v>654098</v>
       </c>
       <c r="R21" t="n">
-        <v>7008351</v>
+        <v>7007903</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2863,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2873,12 +2828,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2905,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120086783</v>
+        <v>120085939</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2921,34 +2876,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654209</v>
+        <v>654279</v>
       </c>
       <c r="R22" t="n">
-        <v>7008406</v>
+        <v>7008217</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2980,7 +2935,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2990,12 +2945,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3022,10 +2972,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120086159</v>
+        <v>120088260</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3038,21 +2988,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654239</v>
+        <v>654139</v>
       </c>
       <c r="R23" t="n">
-        <v>7008276</v>
+        <v>7008299</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,7 +3047,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3107,12 +3057,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3084,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120085068</v>
+        <v>120086920</v>
       </c>
       <c r="B24" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3151,38 +3096,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654217</v>
+        <v>654164</v>
       </c>
       <c r="R24" t="n">
-        <v>7008168</v>
+        <v>7008398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3214,7 +3159,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3169,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3201,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120085411</v>
+        <v>120088486</v>
       </c>
       <c r="B25" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,37 +3217,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654207</v>
+        <v>654118</v>
       </c>
       <c r="R25" t="n">
-        <v>7008193</v>
+        <v>7008045</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,9 +3274,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3341,22 +3306,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120082434</v>
+        <v>120087102</v>
       </c>
       <c r="B26" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3365,38 +3330,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654303</v>
+        <v>654149</v>
       </c>
       <c r="R26" t="n">
-        <v>7007918</v>
+        <v>7008498</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3428,7 +3402,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3438,7 +3412,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3453,19 +3427,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088261</v>
+        <v>120085491</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3501,17 +3475,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svartnäsviken, Svartnäsviken, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654154</v>
+        <v>654200</v>
       </c>
       <c r="R27" t="n">
-        <v>7008250</v>
+        <v>7008326</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3540,7 +3514,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3550,12 +3524,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3582,10 +3556,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088639</v>
+        <v>120087649</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3594,41 +3568,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654098</v>
+        <v>654117</v>
       </c>
       <c r="R28" t="n">
-        <v>7007903</v>
+        <v>7008449</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3655,24 +3633,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3687,22 +3650,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120085434</v>
+        <v>120085068</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>91005</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3711,41 +3674,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
         <v>654217</v>
       </c>
       <c r="R29" t="n">
-        <v>7008312</v>
+        <v>7008168</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3774,7 +3737,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3784,12 +3747,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,10 +3774,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120081327</v>
+        <v>120085193</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3832,37 +3790,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654200</v>
+        <v>654207</v>
       </c>
       <c r="R30" t="n">
-        <v>7007872</v>
+        <v>7008193</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3892,11 +3850,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3911,22 +3864,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120085506</v>
+        <v>120088111</v>
       </c>
       <c r="B31" t="n">
-        <v>90905</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3935,38 +3888,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2062</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Renudden, Renudden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654287</v>
+        <v>654070</v>
       </c>
       <c r="R31" t="n">
-        <v>7008086</v>
+        <v>7008447</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3998,7 +3951,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4008,7 +3961,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,10 +3988,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120085300</v>
+        <v>120085695</v>
       </c>
       <c r="B32" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4047,41 +4000,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654207</v>
+        <v>654200</v>
       </c>
       <c r="R32" t="n">
-        <v>7008193</v>
+        <v>7008363</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4108,9 +4061,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4125,22 +4093,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120085930</v>
+        <v>120086159</v>
       </c>
       <c r="B33" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4149,41 +4117,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654269</v>
+        <v>654239</v>
       </c>
       <c r="R33" t="n">
-        <v>7008197</v>
+        <v>7008276</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4210,9 +4178,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4227,22 +4210,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120087649</v>
+        <v>120086638</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4251,45 +4234,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654117</v>
+        <v>654208</v>
       </c>
       <c r="R34" t="n">
-        <v>7008449</v>
+        <v>7008351</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4316,9 +4295,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4333,22 +4327,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120088260</v>
+        <v>120082271</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4361,34 +4355,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654139</v>
+        <v>654150</v>
       </c>
       <c r="R35" t="n">
-        <v>7008299</v>
+        <v>7007925</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4420,7 +4414,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4430,7 +4424,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4445,22 +4444,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120085648</v>
+        <v>120085424</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4473,34 +4472,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654195</v>
+        <v>654284</v>
       </c>
       <c r="R36" t="n">
-        <v>7008349</v>
+        <v>7008101</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4532,7 +4531,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4542,12 +4541,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4562,22 +4556,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120085706</v>
+        <v>120088189</v>
       </c>
       <c r="B37" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4586,41 +4580,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654297</v>
+        <v>654128</v>
       </c>
       <c r="R37" t="n">
-        <v>7008132</v>
+        <v>7008344</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4647,9 +4641,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4664,22 +4673,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120087230</v>
+        <v>120082342</v>
       </c>
       <c r="B38" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4688,41 +4697,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654170</v>
+        <v>654125</v>
       </c>
       <c r="R38" t="n">
-        <v>7008380</v>
+        <v>7007981</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4749,9 +4767,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4766,22 +4794,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120087250</v>
+        <v>120087238</v>
       </c>
       <c r="B39" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4790,25 +4818,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4818,10 +4846,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654191</v>
+        <v>654193</v>
       </c>
       <c r="R39" t="n">
-        <v>7008385</v>
+        <v>7008384</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4880,10 +4908,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120088364</v>
+        <v>120085434</v>
       </c>
       <c r="B40" t="n">
-        <v>90905</v>
+        <v>57310</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4892,25 +4920,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4920,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654153</v>
+        <v>654217</v>
       </c>
       <c r="R40" t="n">
-        <v>7008523</v>
+        <v>7008312</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4953,9 +4981,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4970,22 +5013,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120082342</v>
+        <v>120085757</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4994,50 +5037,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654125</v>
+        <v>654286</v>
       </c>
       <c r="R41" t="n">
-        <v>7007981</v>
+        <v>7008186</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5064,19 +5098,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5091,22 +5115,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120087102</v>
+        <v>120085930</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>91005</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5119,46 +5143,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654149</v>
+        <v>654269</v>
       </c>
       <c r="R42" t="n">
-        <v>7008498</v>
+        <v>7008197</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5185,19 +5200,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5212,22 +5217,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120087238</v>
+        <v>120088364</v>
       </c>
       <c r="B43" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5236,25 +5241,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5264,13 +5269,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654193</v>
+        <v>654153</v>
       </c>
       <c r="R43" t="n">
-        <v>7008384</v>
+        <v>7008523</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5314,22 +5319,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120085493</v>
+        <v>120085648</v>
       </c>
       <c r="B44" t="n">
-        <v>86878</v>
+        <v>57310</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5342,21 +5347,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5366,13 +5371,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654196</v>
+        <v>654195</v>
       </c>
       <c r="R44" t="n">
-        <v>7008339</v>
+        <v>7008349</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5399,9 +5404,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5416,19 +5436,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120086991</v>
+        <v>120088261</v>
       </c>
       <c r="B45" t="n">
         <v>57310</v>
@@ -5464,14 +5484,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsviken, Svartnäsviken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654156</v>
+        <v>654154</v>
       </c>
       <c r="R45" t="n">
-        <v>7008421</v>
+        <v>7008250</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5503,7 +5523,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5513,7 +5533,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5545,10 +5565,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120088184</v>
+        <v>120087288</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5561,21 +5581,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5585,13 +5605,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654118</v>
+        <v>654159</v>
       </c>
       <c r="R46" t="n">
-        <v>7008347</v>
+        <v>7008481</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5618,24 +5638,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5650,22 +5655,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120088072</v>
+        <v>120085506</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>90905</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5678,38 +5683,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654111</v>
+        <v>654287</v>
       </c>
       <c r="R47" t="n">
-        <v>7008487</v>
+        <v>7008086</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5741,7 +5742,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5751,7 +5752,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5778,10 +5779,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120082215</v>
+        <v>120085468</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5790,50 +5791,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654150</v>
+        <v>654268</v>
       </c>
       <c r="R48" t="n">
-        <v>7007925</v>
+        <v>7008096</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5860,19 +5852,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5887,22 +5869,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120082329</v>
+        <v>120082214</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5915,16 +5897,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5939,10 +5921,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654290</v>
+        <v>654279</v>
       </c>
       <c r="R49" t="n">
-        <v>7007940</v>
+        <v>7007930</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5974,7 +5956,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5984,12 +5966,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6016,7 +5998,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120085695</v>
+        <v>120088184</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -6056,10 +6038,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654200</v>
+        <v>654118</v>
       </c>
       <c r="R50" t="n">
-        <v>7008363</v>
+        <v>7008347</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6091,7 +6073,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6101,7 +6083,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6133,7 +6115,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120085919</v>
+        <v>120086783</v>
       </c>
       <c r="B51" t="n">
         <v>57310</v>
@@ -6169,14 +6151,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654285</v>
+        <v>654209</v>
       </c>
       <c r="R51" t="n">
-        <v>7008199</v>
+        <v>7008406</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6208,7 +6190,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6218,7 +6200,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6250,7 +6232,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120085468</v>
+        <v>120085706</v>
       </c>
       <c r="B52" t="n">
         <v>90527</v>
@@ -6290,10 +6272,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654268</v>
+        <v>654297</v>
       </c>
       <c r="R52" t="n">
-        <v>7008096</v>
+        <v>7008132</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6352,10 +6334,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120085757</v>
+        <v>120085919</v>
       </c>
       <c r="B53" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6368,21 +6350,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6392,13 +6374,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654286</v>
+        <v>654285</v>
       </c>
       <c r="R53" t="n">
-        <v>7008186</v>
+        <v>7008199</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6425,9 +6407,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6442,22 +6439,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120085755</v>
+        <v>120086940</v>
       </c>
       <c r="B54" t="n">
-        <v>57326</v>
+        <v>78263</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6470,39 +6467,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654292</v>
+        <v>654160</v>
       </c>
       <c r="R54" t="n">
-        <v>7008151</v>
+        <v>7008398</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6534,7 +6526,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6544,7 +6536,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6559,22 +6551,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120082158</v>
+        <v>120088072</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6583,38 +6575,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654220</v>
+        <v>654111</v>
       </c>
       <c r="R55" t="n">
-        <v>7007891</v>
+        <v>7008487</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6646,7 +6642,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6656,7 +6652,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6683,7 +6679,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120088486</v>
+        <v>120087568</v>
       </c>
       <c r="B56" t="n">
         <v>57310</v>
@@ -6719,14 +6715,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654118</v>
+        <v>654173</v>
       </c>
       <c r="R56" t="n">
-        <v>7008045</v>
+        <v>7008502</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6758,7 +6754,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6768,12 +6764,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6800,10 +6796,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120085939</v>
+        <v>120082158</v>
       </c>
       <c r="B57" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6812,38 +6808,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654279</v>
+        <v>654220</v>
       </c>
       <c r="R57" t="n">
-        <v>7008217</v>
+        <v>7007891</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6875,7 +6871,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6885,7 +6881,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6912,10 +6908,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120086958</v>
+        <v>120082434</v>
       </c>
       <c r="B58" t="n">
-        <v>90562</v>
+        <v>91832</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6928,37 +6924,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654151</v>
+        <v>654303</v>
       </c>
       <c r="R58" t="n">
-        <v>7008440</v>
+        <v>7007918</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6985,9 +6981,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7002,22 +7008,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120087288</v>
+        <v>120082329</v>
       </c>
       <c r="B59" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7030,37 +7036,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654159</v>
+        <v>654290</v>
       </c>
       <c r="R59" t="n">
-        <v>7008481</v>
+        <v>7007940</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7087,9 +7093,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7104,22 +7125,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120087985</v>
+        <v>120085300</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
+        <v>91005</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7132,41 +7153,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>654128</v>
+        <v>654207</v>
       </c>
       <c r="R60" t="n">
-        <v>7008520</v>
+        <v>7008193</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7193,19 +7210,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7220,22 +7227,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120082214</v>
+        <v>120086958</v>
       </c>
       <c r="B61" t="n">
-        <v>57326</v>
+        <v>90562</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7248,37 +7255,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654279</v>
+        <v>654151</v>
       </c>
       <c r="R61" t="n">
-        <v>7007930</v>
+        <v>7008440</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7305,24 +7312,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7337,22 +7329,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120088189</v>
+        <v>120085493</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>86878</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7365,21 +7357,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7389,13 +7381,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654128</v>
+        <v>654196</v>
       </c>
       <c r="R62" t="n">
-        <v>7008344</v>
+        <v>7008339</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7422,24 +7414,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7454,22 +7431,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120086940</v>
+        <v>120082215</v>
       </c>
       <c r="B63" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7478,38 +7455,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654160</v>
+        <v>654150</v>
       </c>
       <c r="R63" t="n">
-        <v>7008398</v>
+        <v>7007925</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7541,7 +7527,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7551,7 +7537,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7578,10 +7564,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120086920</v>
+        <v>120087230</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7594,21 +7580,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7618,13 +7604,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654164</v>
+        <v>654170</v>
       </c>
       <c r="R64" t="n">
-        <v>7008398</v>
+        <v>7008380</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7651,24 +7637,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7683,22 +7654,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120085485</v>
+        <v>120088520</v>
       </c>
       <c r="B65" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7711,37 +7682,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654276</v>
+        <v>654121</v>
       </c>
       <c r="R65" t="n">
-        <v>7008093</v>
+        <v>7008041</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7768,9 +7739,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7785,22 +7771,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120085491</v>
+        <v>120085755</v>
       </c>
       <c r="B66" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7813,16 +7799,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7831,19 +7817,24 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654200</v>
+        <v>654292</v>
       </c>
       <c r="R66" t="n">
-        <v>7008326</v>
+        <v>7008151</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7872,7 +7863,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7882,12 +7873,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7902,22 +7888,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120085759</v>
+        <v>120082669</v>
       </c>
       <c r="B67" t="n">
-        <v>90562</v>
+        <v>91884</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7930,21 +7916,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>5449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7954,13 +7940,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654293</v>
+        <v>654314</v>
       </c>
       <c r="R67" t="n">
-        <v>7008191</v>
+        <v>7007905</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7987,9 +7973,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8004,22 +8000,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120082934</v>
+        <v>120087985</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8028,38 +8024,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654181</v>
+        <v>654128</v>
       </c>
       <c r="R68" t="n">
-        <v>7007955</v>
+        <v>7008520</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8116,12 +8116,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -4568,10 +4568,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120088189</v>
+        <v>120087238</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4584,21 +4584,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4608,13 +4608,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654128</v>
+        <v>654193</v>
       </c>
       <c r="R37" t="n">
-        <v>7008344</v>
+        <v>7008384</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4641,24 +4641,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4673,22 +4658,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120082342</v>
+        <v>120088189</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4697,47 +4682,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654125</v>
+        <v>654128</v>
       </c>
       <c r="R38" t="n">
-        <v>7007981</v>
+        <v>7008344</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4769,7 +4745,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4779,7 +4755,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4794,22 +4775,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120087238</v>
+        <v>120082342</v>
       </c>
       <c r="B39" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4818,41 +4799,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654193</v>
+        <v>654125</v>
       </c>
       <c r="R39" t="n">
-        <v>7008384</v>
+        <v>7007981</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4879,9 +4869,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4896,22 +4896,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120085434</v>
+        <v>120085757</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4924,37 +4924,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654217</v>
+        <v>654286</v>
       </c>
       <c r="R40" t="n">
-        <v>7008312</v>
+        <v>7008186</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4981,24 +4981,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5013,22 +4998,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120085757</v>
+        <v>120085434</v>
       </c>
       <c r="B41" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5041,37 +5026,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654286</v>
+        <v>654217</v>
       </c>
       <c r="R41" t="n">
-        <v>7008186</v>
+        <v>7008312</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5098,9 +5083,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5115,22 +5115,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120085930</v>
+        <v>120085648</v>
       </c>
       <c r="B42" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5139,41 +5139,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654269</v>
+        <v>654195</v>
       </c>
       <c r="R42" t="n">
-        <v>7008197</v>
+        <v>7008349</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5200,9 +5200,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5217,22 +5232,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120088364</v>
+        <v>120088261</v>
       </c>
       <c r="B43" t="n">
-        <v>90905</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5241,41 +5256,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsviken, Svartnäsviken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654153</v>
+        <v>654154</v>
       </c>
       <c r="R43" t="n">
-        <v>7008523</v>
+        <v>7008250</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5302,9 +5317,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5319,22 +5349,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120085648</v>
+        <v>120085930</v>
       </c>
       <c r="B44" t="n">
-        <v>57310</v>
+        <v>91005</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5343,41 +5373,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654195</v>
+        <v>654269</v>
       </c>
       <c r="R44" t="n">
-        <v>7008349</v>
+        <v>7008197</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5404,24 +5434,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5436,22 +5451,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120088261</v>
+        <v>120088364</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>90905</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5460,41 +5475,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartnäsviken, Svartnäsviken, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654154</v>
+        <v>654153</v>
       </c>
       <c r="R45" t="n">
-        <v>7008250</v>
+        <v>7008523</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5521,24 +5536,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5553,12 +5553,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5881,10 +5881,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120082214</v>
+        <v>120088184</v>
       </c>
       <c r="B49" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5897,16 +5897,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5917,14 +5917,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654279</v>
+        <v>654118</v>
       </c>
       <c r="R49" t="n">
-        <v>7007930</v>
+        <v>7008347</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färskt bohål.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5986,19 +5986,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120088184</v>
+        <v>120086783</v>
       </c>
       <c r="B50" t="n">
         <v>57310</v>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654118</v>
+        <v>654209</v>
       </c>
       <c r="R50" t="n">
-        <v>7008347</v>
+        <v>7008406</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6103,22 +6103,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120086783</v>
+        <v>120082214</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6131,16 +6131,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6151,14 +6151,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654209</v>
+        <v>654279</v>
       </c>
       <c r="R51" t="n">
-        <v>7008406</v>
+        <v>7007930</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6679,10 +6679,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120087568</v>
+        <v>120082158</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6691,38 +6691,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654173</v>
+        <v>654220</v>
       </c>
       <c r="R56" t="n">
-        <v>7008502</v>
+        <v>7007891</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6764,12 +6764,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på  gran</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6784,22 +6779,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120082158</v>
+        <v>120087568</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6808,38 +6803,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654220</v>
+        <v>654173</v>
       </c>
       <c r="R57" t="n">
-        <v>7007891</v>
+        <v>7008502</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6871,7 +6866,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6881,7 +6876,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6896,12 +6896,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7020,10 +7020,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120082329</v>
+        <v>120086958</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7036,37 +7036,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654290</v>
+        <v>654151</v>
       </c>
       <c r="R59" t="n">
-        <v>7007940</v>
+        <v>7008440</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7093,24 +7093,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7125,12 +7110,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7239,10 +7224,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120086958</v>
+        <v>120082329</v>
       </c>
       <c r="B61" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7255,37 +7240,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654151</v>
+        <v>654290</v>
       </c>
       <c r="R61" t="n">
-        <v>7008440</v>
+        <v>7007940</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7312,9 +7297,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7329,12 +7329,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120087250</v>
+        <v>120085485</v>
       </c>
       <c r="B14" t="n">
-        <v>90527</v>
+        <v>90846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,38 +2011,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654191</v>
+        <v>654276</v>
       </c>
       <c r="R14" t="n">
-        <v>7008385</v>
+        <v>7008093</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2101,7 +2101,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120086991</v>
+        <v>120086159</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654156</v>
+        <v>654239</v>
       </c>
       <c r="R15" t="n">
-        <v>7008421</v>
+        <v>7008276</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,22 +2206,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120085485</v>
+        <v>120082271</v>
       </c>
       <c r="B16" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2234,37 +2234,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654276</v>
+        <v>654150</v>
       </c>
       <c r="R16" t="n">
-        <v>7008093</v>
+        <v>7007925</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2291,9 +2291,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,22 +2323,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120085411</v>
+        <v>120085468</v>
       </c>
       <c r="B17" t="n">
-        <v>90846</v>
+        <v>90527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2332,25 +2347,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2360,13 +2375,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654207</v>
+        <v>654268</v>
       </c>
       <c r="R17" t="n">
-        <v>7008193</v>
+        <v>7008096</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2410,22 +2425,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120085759</v>
+        <v>120085493</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>86878</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2438,37 +2453,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654293</v>
+        <v>654196</v>
       </c>
       <c r="R18" t="n">
-        <v>7008191</v>
+        <v>7008339</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,22 +2527,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120082934</v>
+        <v>120087238</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2536,41 +2551,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654181</v>
+        <v>654193</v>
       </c>
       <c r="R19" t="n">
-        <v>7007955</v>
+        <v>7008384</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2597,19 +2612,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,19 +2629,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120081327</v>
+        <v>120088184</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2672,17 +2677,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654200</v>
+        <v>654118</v>
       </c>
       <c r="R20" t="n">
-        <v>7007872</v>
+        <v>7008347</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2709,14 +2714,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,19 +2746,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088639</v>
+        <v>120086920</v>
       </c>
       <c r="B21" t="n">
         <v>57310</v>
@@ -2779,14 +2794,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654098</v>
+        <v>654164</v>
       </c>
       <c r="R21" t="n">
-        <v>7007903</v>
+        <v>7008398</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2833,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2843,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2860,10 +2875,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120085939</v>
+        <v>120088639</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,34 +2891,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654279</v>
+        <v>654098</v>
       </c>
       <c r="R22" t="n">
-        <v>7008217</v>
+        <v>7007903</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2935,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2945,7 +2960,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2960,22 +2980,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088260</v>
+        <v>120086638</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2988,21 +3008,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3012,10 +3032,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654139</v>
+        <v>654208</v>
       </c>
       <c r="R23" t="n">
-        <v>7008299</v>
+        <v>7008351</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3047,7 +3067,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3057,7 +3077,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,22 +3097,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120086920</v>
+        <v>120087288</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3100,21 +3125,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3124,13 +3149,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654164</v>
+        <v>654159</v>
       </c>
       <c r="R24" t="n">
-        <v>7008398</v>
+        <v>7008481</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3157,24 +3182,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,22 +3199,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088486</v>
+        <v>120082158</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3213,25 +3223,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3241,10 +3251,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654118</v>
+        <v>654220</v>
       </c>
       <c r="R25" t="n">
-        <v>7008045</v>
+        <v>7007891</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3276,7 +3286,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3286,12 +3296,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3306,22 +3311,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120087102</v>
+        <v>120085491</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3330,50 +3335,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654149</v>
+        <v>654200</v>
       </c>
       <c r="R26" t="n">
-        <v>7008498</v>
+        <v>7008326</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3402,7 +3398,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3412,7 +3408,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,7 +3440,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120085491</v>
+        <v>120087568</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3479,13 +3480,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654200</v>
+        <v>654173</v>
       </c>
       <c r="R27" t="n">
-        <v>7008326</v>
+        <v>7008502</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3514,7 +3515,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3524,12 +3525,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3556,10 +3557,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120087649</v>
+        <v>120087250</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3568,42 +3569,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654117</v>
+        <v>654191</v>
       </c>
       <c r="R28" t="n">
-        <v>7008449</v>
+        <v>7008385</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3662,10 +3659,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120085068</v>
+        <v>120085506</v>
       </c>
       <c r="B29" t="n">
-        <v>91005</v>
+        <v>90905</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3678,21 +3675,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>2062</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3702,10 +3699,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654217</v>
+        <v>654287</v>
       </c>
       <c r="R29" t="n">
-        <v>7008168</v>
+        <v>7008086</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3737,7 +3734,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3747,7 +3744,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3762,22 +3759,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120085193</v>
+        <v>120082934</v>
       </c>
       <c r="B30" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3786,41 +3783,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654207</v>
+        <v>654181</v>
       </c>
       <c r="R30" t="n">
-        <v>7008193</v>
+        <v>7007955</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3847,9 +3844,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3864,22 +3871,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088111</v>
+        <v>120085434</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3888,41 +3895,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Renudden, Renudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654070</v>
+        <v>654217</v>
       </c>
       <c r="R31" t="n">
-        <v>7008447</v>
+        <v>7008312</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3951,7 +3958,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3961,7 +3968,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3976,22 +3988,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120085695</v>
+        <v>120085759</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4004,37 +4016,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654200</v>
+        <v>654293</v>
       </c>
       <c r="R32" t="n">
-        <v>7008363</v>
+        <v>7008191</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4061,24 +4073,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4093,22 +4090,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120086159</v>
+        <v>120085939</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4121,34 +4118,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654239</v>
+        <v>654279</v>
       </c>
       <c r="R33" t="n">
-        <v>7008276</v>
+        <v>7008217</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4180,7 +4177,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4190,12 +4187,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4222,7 +4214,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120086638</v>
+        <v>120088189</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4262,10 +4254,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654208</v>
+        <v>654128</v>
       </c>
       <c r="R34" t="n">
-        <v>7008351</v>
+        <v>7008344</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4297,7 +4289,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4307,12 +4299,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4327,19 +4319,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120082271</v>
+        <v>120086991</v>
       </c>
       <c r="B35" t="n">
         <v>57310</v>
@@ -4375,14 +4367,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654150</v>
+        <v>654156</v>
       </c>
       <c r="R35" t="n">
-        <v>7007925</v>
+        <v>7008421</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4414,7 +4406,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4424,12 +4416,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4456,10 +4448,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120085424</v>
+        <v>120082215</v>
       </c>
       <c r="B36" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4468,38 +4460,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654284</v>
+        <v>654150</v>
       </c>
       <c r="R36" t="n">
-        <v>7008101</v>
+        <v>7007925</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4531,7 +4532,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4541,7 +4542,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4556,22 +4557,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120087238</v>
+        <v>120082669</v>
       </c>
       <c r="B37" t="n">
-        <v>90562</v>
+        <v>91884</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4584,37 +4585,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>5449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654193</v>
+        <v>654314</v>
       </c>
       <c r="R37" t="n">
-        <v>7008384</v>
+        <v>7007905</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4641,9 +4642,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4658,22 +4669,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120088189</v>
+        <v>120085930</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>91005</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4682,41 +4693,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654128</v>
+        <v>654269</v>
       </c>
       <c r="R38" t="n">
-        <v>7008344</v>
+        <v>7008197</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4743,24 +4754,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4775,22 +4771,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120082342</v>
+        <v>120085695</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4799,47 +4795,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654125</v>
+        <v>654200</v>
       </c>
       <c r="R39" t="n">
-        <v>7007981</v>
+        <v>7008363</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4871,7 +4858,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4881,7 +4868,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4908,10 +4900,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120085757</v>
+        <v>120086940</v>
       </c>
       <c r="B40" t="n">
-        <v>90846</v>
+        <v>78263</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4924,37 +4916,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654286</v>
+        <v>654160</v>
       </c>
       <c r="R40" t="n">
-        <v>7008186</v>
+        <v>7008398</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4981,9 +4973,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4998,22 +5000,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120085434</v>
+        <v>120085706</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5022,41 +5024,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654217</v>
+        <v>654297</v>
       </c>
       <c r="R41" t="n">
-        <v>7008312</v>
+        <v>7008132</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5083,24 +5085,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5115,22 +5102,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120085648</v>
+        <v>120088260</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5143,21 +5130,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5167,10 +5154,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654195</v>
+        <v>654139</v>
       </c>
       <c r="R42" t="n">
-        <v>7008349</v>
+        <v>7008299</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,7 +5189,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5212,12 +5199,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5232,22 +5214,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120088261</v>
+        <v>120088111</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5256,38 +5238,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartnäsviken, Svartnäsviken, Ång</t>
+          <t>Renudden, Renudden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654154</v>
+        <v>654070</v>
       </c>
       <c r="R43" t="n">
-        <v>7008250</v>
+        <v>7008447</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5319,7 +5301,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5329,12 +5311,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5349,19 +5326,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120085930</v>
+        <v>120085300</v>
       </c>
       <c r="B44" t="n">
         <v>91005</v>
@@ -5401,13 +5378,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654269</v>
+        <v>654207</v>
       </c>
       <c r="R44" t="n">
-        <v>7008197</v>
+        <v>7008193</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5451,22 +5428,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120088364</v>
+        <v>120088520</v>
       </c>
       <c r="B45" t="n">
-        <v>90905</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5475,41 +5452,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654153</v>
+        <v>654121</v>
       </c>
       <c r="R45" t="n">
-        <v>7008523</v>
+        <v>7008041</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5536,9 +5513,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5553,22 +5545,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120087288</v>
+        <v>120082329</v>
       </c>
       <c r="B46" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5581,37 +5573,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654159</v>
+        <v>654290</v>
       </c>
       <c r="R46" t="n">
-        <v>7008481</v>
+        <v>7007940</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5638,9 +5630,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5655,22 +5662,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120085506</v>
+        <v>120086783</v>
       </c>
       <c r="B47" t="n">
-        <v>90905</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5679,38 +5686,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654287</v>
+        <v>654209</v>
       </c>
       <c r="R47" t="n">
-        <v>7008086</v>
+        <v>7008406</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5742,7 +5749,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5752,7 +5759,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5779,10 +5791,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120085468</v>
+        <v>120085424</v>
       </c>
       <c r="B48" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5791,25 +5803,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5819,13 +5831,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654268</v>
+        <v>654284</v>
       </c>
       <c r="R48" t="n">
-        <v>7008096</v>
+        <v>7008101</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5852,9 +5864,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5869,22 +5891,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120088184</v>
+        <v>120085068</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>91005</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5893,38 +5915,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654118</v>
+        <v>654217</v>
       </c>
       <c r="R49" t="n">
-        <v>7008347</v>
+        <v>7008168</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5956,7 +5978,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5966,12 +5988,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5998,10 +6015,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120086783</v>
+        <v>120086958</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6014,21 +6031,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6038,13 +6055,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654209</v>
+        <v>654151</v>
       </c>
       <c r="R50" t="n">
-        <v>7008406</v>
+        <v>7008440</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6071,24 +6088,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6103,12 +6105,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6232,10 +6234,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120085706</v>
+        <v>120082342</v>
       </c>
       <c r="B52" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6244,41 +6246,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654297</v>
+        <v>654125</v>
       </c>
       <c r="R52" t="n">
-        <v>7008132</v>
+        <v>7007981</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6305,9 +6316,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6322,19 +6343,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120085919</v>
+        <v>120088261</v>
       </c>
       <c r="B53" t="n">
         <v>57310</v>
@@ -6370,14 +6391,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäsviken, Svartnäsviken, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654285</v>
+        <v>654154</v>
       </c>
       <c r="R53" t="n">
-        <v>7008199</v>
+        <v>7008250</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6409,7 +6430,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6419,12 +6440,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6439,22 +6460,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120086940</v>
+        <v>120085211</v>
       </c>
       <c r="B54" t="n">
-        <v>78263</v>
+        <v>90846</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6467,37 +6488,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654160</v>
+        <v>654207</v>
       </c>
       <c r="R54" t="n">
-        <v>7008398</v>
+        <v>7008193</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6524,19 +6545,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6551,19 +6562,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120088072</v>
+        <v>120087985</v>
       </c>
       <c r="B55" t="n">
         <v>97907</v>
@@ -6598,7 +6609,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6607,10 +6618,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654111</v>
+        <v>654128</v>
       </c>
       <c r="R55" t="n">
-        <v>7008487</v>
+        <v>7008520</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6642,7 +6653,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6652,7 +6663,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6679,10 +6690,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120082158</v>
+        <v>120088486</v>
       </c>
       <c r="B56" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6691,25 +6702,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6719,10 +6730,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654220</v>
+        <v>654118</v>
       </c>
       <c r="R56" t="n">
-        <v>7007891</v>
+        <v>7008045</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6754,7 +6765,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6764,7 +6775,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6779,22 +6795,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120087568</v>
+        <v>120082434</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6807,34 +6823,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654173</v>
+        <v>654303</v>
       </c>
       <c r="R57" t="n">
-        <v>7008502</v>
+        <v>7007918</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6866,7 +6882,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6876,12 +6892,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på  gran</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6896,22 +6907,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120082434</v>
+        <v>120085755</v>
       </c>
       <c r="B58" t="n">
-        <v>91832</v>
+        <v>57326</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6924,34 +6935,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654303</v>
+        <v>654292</v>
       </c>
       <c r="R58" t="n">
-        <v>7007918</v>
+        <v>7008151</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6983,7 +6999,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6993,7 +7009,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7020,10 +7036,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120086958</v>
+        <v>120085919</v>
       </c>
       <c r="B59" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7036,37 +7052,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654151</v>
+        <v>654285</v>
       </c>
       <c r="R59" t="n">
-        <v>7008440</v>
+        <v>7008199</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7093,9 +7109,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7110,22 +7141,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120085300</v>
+        <v>120088072</v>
       </c>
       <c r="B60" t="n">
-        <v>91005</v>
+        <v>97907</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7138,37 +7169,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>654207</v>
+        <v>654111</v>
       </c>
       <c r="R60" t="n">
-        <v>7008193</v>
+        <v>7008487</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7195,9 +7230,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7212,22 +7257,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120082329</v>
+        <v>120087649</v>
       </c>
       <c r="B61" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7236,41 +7281,45 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654290</v>
+        <v>654117</v>
       </c>
       <c r="R61" t="n">
-        <v>7007940</v>
+        <v>7008449</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7297,24 +7346,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7329,22 +7363,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120085493</v>
+        <v>120088364</v>
       </c>
       <c r="B62" t="n">
-        <v>86878</v>
+        <v>90905</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7353,25 +7387,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>510</v>
+        <v>2062</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7381,10 +7415,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654196</v>
+        <v>654153</v>
       </c>
       <c r="R62" t="n">
-        <v>7008339</v>
+        <v>7008523</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7443,10 +7477,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120082215</v>
+        <v>120087230</v>
       </c>
       <c r="B63" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7455,50 +7489,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654150</v>
+        <v>654170</v>
       </c>
       <c r="R63" t="n">
-        <v>7007925</v>
+        <v>7008380</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7525,19 +7550,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7552,22 +7567,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120087230</v>
+        <v>120087102</v>
       </c>
       <c r="B64" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7576,41 +7591,50 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654170</v>
+        <v>654149</v>
       </c>
       <c r="R64" t="n">
-        <v>7008380</v>
+        <v>7008498</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7637,9 +7661,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7654,22 +7688,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120088520</v>
+        <v>120085757</v>
       </c>
       <c r="B65" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7682,37 +7716,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654121</v>
+        <v>654286</v>
       </c>
       <c r="R65" t="n">
-        <v>7008041</v>
+        <v>7008186</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7739,24 +7773,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7771,22 +7790,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120085755</v>
+        <v>120085193</v>
       </c>
       <c r="B66" t="n">
-        <v>57326</v>
+        <v>90562</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7799,42 +7818,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654292</v>
+        <v>654207</v>
       </c>
       <c r="R66" t="n">
-        <v>7008151</v>
+        <v>7008193</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7861,19 +7875,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7888,22 +7892,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120082669</v>
+        <v>120085648</v>
       </c>
       <c r="B67" t="n">
-        <v>91884</v>
+        <v>57310</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7916,34 +7920,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654314</v>
+        <v>654195</v>
       </c>
       <c r="R67" t="n">
-        <v>7007905</v>
+        <v>7008349</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7975,7 +7979,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7985,7 +7989,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8000,22 +8009,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120087985</v>
+        <v>120081327</v>
       </c>
       <c r="B68" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8024,45 +8033,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654128</v>
+        <v>654200</v>
       </c>
       <c r="R68" t="n">
-        <v>7008520</v>
+        <v>7007872</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8089,19 +8094,14 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>15:59</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8116,12 +8116,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -5226,10 +5226,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120088111</v>
+        <v>120085300</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>91005</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5238,41 +5238,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Renudden, Renudden, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654070</v>
+        <v>654207</v>
       </c>
       <c r="R43" t="n">
-        <v>7008447</v>
+        <v>7008193</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5299,19 +5299,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5326,22 +5316,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120085300</v>
+        <v>120088111</v>
       </c>
       <c r="B44" t="n">
-        <v>91005</v>
+        <v>91840</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5350,41 +5340,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Renudden, Renudden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654207</v>
+        <v>654070</v>
       </c>
       <c r="R44" t="n">
-        <v>7008193</v>
+        <v>7008447</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5411,9 +5401,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5428,12 +5428,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120085485</v>
+        <v>120088486</v>
       </c>
       <c r="B14" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2015,37 +2015,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654276</v>
+        <v>654118</v>
       </c>
       <c r="R14" t="n">
-        <v>7008093</v>
+        <v>7008045</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,9 +2072,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,19 +2104,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120086159</v>
+        <v>120088639</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2137,14 +2152,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654239</v>
+        <v>654098</v>
       </c>
       <c r="R15" t="n">
-        <v>7008276</v>
+        <v>7007903</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2186,12 +2201,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,22 +2221,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120082271</v>
+        <v>120088072</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2230,38 +2245,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654150</v>
+        <v>654111</v>
       </c>
       <c r="R16" t="n">
-        <v>7007925</v>
+        <v>7008487</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,12 +2322,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,22 +2337,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120085468</v>
+        <v>120087568</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2347,41 +2361,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654268</v>
+        <v>654173</v>
       </c>
       <c r="R17" t="n">
-        <v>7008096</v>
+        <v>7008502</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2408,9 +2422,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2425,22 +2454,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120085493</v>
+        <v>120087985</v>
       </c>
       <c r="B18" t="n">
-        <v>86878</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2449,41 +2478,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654196</v>
+        <v>654128</v>
       </c>
       <c r="R18" t="n">
-        <v>7008339</v>
+        <v>7008520</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2510,9 +2543,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,22 +2570,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120087238</v>
+        <v>120085506</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2551,41 +2594,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654193</v>
+        <v>654287</v>
       </c>
       <c r="R19" t="n">
-        <v>7008384</v>
+        <v>7008086</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2612,9 +2655,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,22 +2682,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088184</v>
+        <v>120085468</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2653,41 +2706,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654118</v>
+        <v>654268</v>
       </c>
       <c r="R20" t="n">
-        <v>7008347</v>
+        <v>7008096</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,24 +2767,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2746,12 +2784,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2875,10 +2913,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088639</v>
+        <v>120085424</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2891,34 +2929,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654098</v>
+        <v>654284</v>
       </c>
       <c r="R22" t="n">
-        <v>7007903</v>
+        <v>7008101</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2950,7 +2988,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,12 +2998,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2980,22 +3013,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120086638</v>
+        <v>120085068</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>91005</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3004,38 +3037,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654208</v>
+        <v>654217</v>
       </c>
       <c r="R23" t="n">
-        <v>7008351</v>
+        <v>7008168</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3067,7 +3100,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3077,12 +3110,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3109,10 +3137,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120087288</v>
+        <v>120088111</v>
       </c>
       <c r="B24" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3121,41 +3149,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Renudden, Renudden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654159</v>
+        <v>654070</v>
       </c>
       <c r="R24" t="n">
-        <v>7008481</v>
+        <v>7008447</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3182,9 +3210,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3199,22 +3237,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120082158</v>
+        <v>120086783</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3223,38 +3261,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654220</v>
+        <v>654209</v>
       </c>
       <c r="R25" t="n">
-        <v>7007891</v>
+        <v>7008406</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,7 +3324,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3296,7 +3334,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3323,10 +3366,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120085491</v>
+        <v>120088260</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3339,21 +3382,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3363,13 +3406,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654200</v>
+        <v>654139</v>
       </c>
       <c r="R26" t="n">
-        <v>7008326</v>
+        <v>7008299</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3398,7 +3441,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3408,12 +3451,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3428,22 +3466,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120087568</v>
+        <v>120085757</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3456,37 +3494,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654173</v>
+        <v>654286</v>
       </c>
       <c r="R27" t="n">
-        <v>7008502</v>
+        <v>7008186</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3513,24 +3551,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3545,22 +3568,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120087250</v>
+        <v>120088520</v>
       </c>
       <c r="B28" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3569,41 +3592,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654191</v>
+        <v>654121</v>
       </c>
       <c r="R28" t="n">
-        <v>7008385</v>
+        <v>7008041</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3630,9 +3653,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3647,22 +3685,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120085506</v>
+        <v>120081327</v>
       </c>
       <c r="B29" t="n">
-        <v>90905</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3671,41 +3709,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654287</v>
+        <v>654200</v>
       </c>
       <c r="R29" t="n">
-        <v>7008086</v>
+        <v>7007872</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3732,19 +3770,14 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:33</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3759,22 +3792,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120082934</v>
+        <v>120085434</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3783,41 +3816,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654181</v>
+        <v>654217</v>
       </c>
       <c r="R30" t="n">
-        <v>7007955</v>
+        <v>7008312</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3846,7 +3879,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3856,7 +3889,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3883,10 +3921,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120085434</v>
+        <v>120082342</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3895,41 +3933,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654217</v>
+        <v>654125</v>
       </c>
       <c r="R31" t="n">
-        <v>7008312</v>
+        <v>7007981</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3958,7 +4005,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3968,12 +4015,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4000,10 +4042,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120085759</v>
+        <v>120085930</v>
       </c>
       <c r="B32" t="n">
-        <v>90562</v>
+        <v>91005</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4012,25 +4054,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4040,10 +4082,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654293</v>
+        <v>654269</v>
       </c>
       <c r="R32" t="n">
-        <v>7008191</v>
+        <v>7008197</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4102,10 +4144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120085939</v>
+        <v>120085493</v>
       </c>
       <c r="B33" t="n">
-        <v>90562</v>
+        <v>86878</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4118,37 +4160,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654279</v>
+        <v>654196</v>
       </c>
       <c r="R33" t="n">
-        <v>7008217</v>
+        <v>7008339</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4175,19 +4217,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4202,22 +4234,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120088189</v>
+        <v>120085193</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4230,37 +4262,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654128</v>
+        <v>654207</v>
       </c>
       <c r="R34" t="n">
-        <v>7008344</v>
+        <v>7008193</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4287,24 +4319,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4319,22 +4336,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120086991</v>
+        <v>120086958</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4347,21 +4364,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4371,13 +4388,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654156</v>
+        <v>654151</v>
       </c>
       <c r="R35" t="n">
-        <v>7008421</v>
+        <v>7008440</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4404,24 +4421,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4436,22 +4438,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120082215</v>
+        <v>120082271</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4460,37 +4462,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svartnäset, Svartnäset, Ång</t>
@@ -4532,7 +4525,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4542,7 +4535,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4569,10 +4567,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120082669</v>
+        <v>120085211</v>
       </c>
       <c r="B37" t="n">
-        <v>91884</v>
+        <v>90846</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4585,21 +4583,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4609,13 +4607,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654314</v>
+        <v>654207</v>
       </c>
       <c r="R37" t="n">
-        <v>7007905</v>
+        <v>7008193</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4642,19 +4640,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4669,22 +4657,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120085930</v>
+        <v>120086159</v>
       </c>
       <c r="B38" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4693,41 +4681,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654269</v>
+        <v>654239</v>
       </c>
       <c r="R38" t="n">
-        <v>7008197</v>
+        <v>7008276</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4754,9 +4742,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4771,19 +4774,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120085695</v>
+        <v>120085648</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4823,10 +4826,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654200</v>
+        <v>654195</v>
       </c>
       <c r="R39" t="n">
-        <v>7008363</v>
+        <v>7008349</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4858,7 +4861,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4868,7 +4871,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4900,10 +4903,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120086940</v>
+        <v>120082214</v>
       </c>
       <c r="B40" t="n">
-        <v>78263</v>
+        <v>57326</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4916,34 +4919,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654160</v>
+        <v>654279</v>
       </c>
       <c r="R40" t="n">
-        <v>7008398</v>
+        <v>7007930</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4975,7 +4978,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4985,7 +4988,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5000,22 +5008,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120085706</v>
+        <v>120087649</v>
       </c>
       <c r="B41" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5024,38 +5032,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654297</v>
+        <v>654117</v>
       </c>
       <c r="R41" t="n">
-        <v>7008132</v>
+        <v>7008449</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5114,10 +5126,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120088260</v>
+        <v>120082669</v>
       </c>
       <c r="B42" t="n">
-        <v>90580</v>
+        <v>91884</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5130,34 +5142,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>5449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654139</v>
+        <v>654314</v>
       </c>
       <c r="R42" t="n">
-        <v>7008299</v>
+        <v>7007905</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5189,7 +5201,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5199,7 +5211,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5226,10 +5238,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120085300</v>
+        <v>120088184</v>
       </c>
       <c r="B43" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5238,41 +5250,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654207</v>
+        <v>654118</v>
       </c>
       <c r="R43" t="n">
-        <v>7008193</v>
+        <v>7008347</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5299,9 +5311,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5316,22 +5343,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120088111</v>
+        <v>120085939</v>
       </c>
       <c r="B44" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5340,38 +5367,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Renudden, Renudden, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654070</v>
+        <v>654279</v>
       </c>
       <c r="R44" t="n">
-        <v>7008447</v>
+        <v>7008217</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5403,7 +5430,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5413,7 +5440,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5440,10 +5467,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120088520</v>
+        <v>120082934</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5452,25 +5479,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5480,10 +5507,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654121</v>
+        <v>654181</v>
       </c>
       <c r="R45" t="n">
-        <v>7008041</v>
+        <v>7007955</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5515,7 +5542,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5525,12 +5552,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5545,22 +5567,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120082329</v>
+        <v>120082434</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5573,21 +5595,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5597,10 +5619,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654290</v>
+        <v>654303</v>
       </c>
       <c r="R46" t="n">
-        <v>7007940</v>
+        <v>7007918</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5632,7 +5654,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5642,12 +5664,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5674,10 +5691,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120086783</v>
+        <v>120087250</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5686,25 +5703,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5714,13 +5731,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654209</v>
+        <v>654191</v>
       </c>
       <c r="R47" t="n">
-        <v>7008406</v>
+        <v>7008385</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5747,24 +5764,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5779,22 +5781,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120085424</v>
+        <v>120087230</v>
       </c>
       <c r="B48" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5807,37 +5809,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654284</v>
+        <v>654170</v>
       </c>
       <c r="R48" t="n">
-        <v>7008101</v>
+        <v>7008380</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5864,19 +5866,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5891,22 +5883,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120085068</v>
+        <v>120085491</v>
       </c>
       <c r="B49" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5915,41 +5907,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654217</v>
+        <v>654200</v>
       </c>
       <c r="R49" t="n">
-        <v>7008168</v>
+        <v>7008326</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5978,7 +5970,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5988,7 +5980,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6015,7 +6012,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120086958</v>
+        <v>120087288</v>
       </c>
       <c r="B50" t="n">
         <v>90562</v>
@@ -6055,13 +6052,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654151</v>
+        <v>654159</v>
       </c>
       <c r="R50" t="n">
-        <v>7008440</v>
+        <v>7008481</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6105,22 +6102,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120082214</v>
+        <v>120082158</v>
       </c>
       <c r="B51" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6129,38 +6126,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654279</v>
+        <v>654220</v>
       </c>
       <c r="R51" t="n">
-        <v>7007930</v>
+        <v>7007891</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6192,7 +6189,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6202,12 +6199,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färskt bohål.</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6234,10 +6226,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120082342</v>
+        <v>120085755</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6246,47 +6238,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654125</v>
+        <v>654292</v>
       </c>
       <c r="R52" t="n">
-        <v>7007981</v>
+        <v>7008151</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6318,7 +6306,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6328,7 +6316,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6343,22 +6331,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120088261</v>
+        <v>120085300</v>
       </c>
       <c r="B53" t="n">
-        <v>57310</v>
+        <v>91005</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6367,41 +6355,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svartnäsviken, Svartnäsviken, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654154</v>
+        <v>654207</v>
       </c>
       <c r="R53" t="n">
-        <v>7008250</v>
+        <v>7008193</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6428,24 +6416,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6460,22 +6433,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120085211</v>
+        <v>120085759</v>
       </c>
       <c r="B54" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6488,21 +6461,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6512,13 +6485,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654207</v>
+        <v>654293</v>
       </c>
       <c r="R54" t="n">
-        <v>7008193</v>
+        <v>7008191</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6562,22 +6535,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120087985</v>
+        <v>120085695</v>
       </c>
       <c r="B55" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6586,42 +6559,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654128</v>
+        <v>654200</v>
       </c>
       <c r="R55" t="n">
-        <v>7008520</v>
+        <v>7008363</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6653,7 +6622,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6663,7 +6632,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6678,22 +6652,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120088486</v>
+        <v>120086940</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>78263</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6706,34 +6680,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654118</v>
+        <v>654160</v>
       </c>
       <c r="R56" t="n">
-        <v>7008045</v>
+        <v>7008398</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6765,7 +6739,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6775,12 +6749,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6807,10 +6776,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120082434</v>
+        <v>120088189</v>
       </c>
       <c r="B57" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6823,34 +6792,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654303</v>
+        <v>654128</v>
       </c>
       <c r="R57" t="n">
-        <v>7007918</v>
+        <v>7008344</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6882,7 +6851,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6892,7 +6861,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6919,10 +6893,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120085755</v>
+        <v>120086991</v>
       </c>
       <c r="B58" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6935,16 +6909,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6953,21 +6927,16 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654292</v>
+        <v>654156</v>
       </c>
       <c r="R58" t="n">
-        <v>7008151</v>
+        <v>7008421</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6999,7 +6968,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7009,7 +6978,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7024,22 +6998,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120085919</v>
+        <v>120082215</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7048,38 +7022,47 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654285</v>
+        <v>654150</v>
       </c>
       <c r="R59" t="n">
-        <v>7008199</v>
+        <v>7007925</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7111,7 +7094,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7121,12 +7104,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7141,19 +7119,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120088072</v>
+        <v>120087102</v>
       </c>
       <c r="B60" t="n">
         <v>97907</v>
@@ -7188,7 +7166,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7197,10 +7180,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>654111</v>
+        <v>654149</v>
       </c>
       <c r="R60" t="n">
-        <v>7008487</v>
+        <v>7008498</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7232,7 +7215,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7242,7 +7225,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7257,22 +7240,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120087649</v>
+        <v>120088364</v>
       </c>
       <c r="B61" t="n">
-        <v>97907</v>
+        <v>90905</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7285,41 +7268,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654117</v>
+        <v>654153</v>
       </c>
       <c r="R61" t="n">
-        <v>7008449</v>
+        <v>7008523</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7363,22 +7342,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120088364</v>
+        <v>120088261</v>
       </c>
       <c r="B62" t="n">
-        <v>90905</v>
+        <v>57310</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7387,41 +7366,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsviken, Svartnäsviken, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654153</v>
+        <v>654154</v>
       </c>
       <c r="R62" t="n">
-        <v>7008523</v>
+        <v>7008250</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7448,9 +7427,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7465,22 +7459,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120087230</v>
+        <v>120086638</v>
       </c>
       <c r="B63" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7493,21 +7487,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7517,13 +7511,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654170</v>
+        <v>654208</v>
       </c>
       <c r="R63" t="n">
-        <v>7008380</v>
+        <v>7008351</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7550,9 +7544,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7567,22 +7576,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120087102</v>
+        <v>120085485</v>
       </c>
       <c r="B64" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7591,50 +7600,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654149</v>
+        <v>654276</v>
       </c>
       <c r="R64" t="n">
-        <v>7008498</v>
+        <v>7008093</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7661,19 +7661,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7688,22 +7678,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120085757</v>
+        <v>120082329</v>
       </c>
       <c r="B65" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7716,21 +7706,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7740,13 +7730,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654286</v>
+        <v>654290</v>
       </c>
       <c r="R65" t="n">
-        <v>7008186</v>
+        <v>7007940</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7773,9 +7763,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7790,22 +7795,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120085193</v>
+        <v>120085919</v>
       </c>
       <c r="B66" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7818,21 +7823,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7842,13 +7847,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654207</v>
+        <v>654285</v>
       </c>
       <c r="R66" t="n">
-        <v>7008193</v>
+        <v>7008199</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7875,9 +7880,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7892,22 +7912,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120085648</v>
+        <v>120085706</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7916,41 +7936,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654195</v>
+        <v>654297</v>
       </c>
       <c r="R67" t="n">
-        <v>7008349</v>
+        <v>7008132</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7977,24 +7997,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8009,22 +8014,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120081327</v>
+        <v>120087238</v>
       </c>
       <c r="B68" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8037,34 +8042,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654200</v>
+        <v>654193</v>
       </c>
       <c r="R68" t="n">
-        <v>7007872</v>
+        <v>7008384</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8097,11 +8102,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -4786,10 +4786,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120085648</v>
+        <v>120082214</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4802,16 +4802,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4822,14 +4822,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654195</v>
+        <v>654279</v>
       </c>
       <c r="R39" t="n">
-        <v>7008349</v>
+        <v>7007930</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4891,22 +4891,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120082214</v>
+        <v>120082669</v>
       </c>
       <c r="B40" t="n">
-        <v>57326</v>
+        <v>91884</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4919,21 +4919,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654279</v>
+        <v>654314</v>
       </c>
       <c r="R40" t="n">
-        <v>7007930</v>
+        <v>7007905</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4988,12 +4988,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färskt bohål.</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5020,10 +5015,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120087649</v>
+        <v>120088184</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5032,45 +5027,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654117</v>
+        <v>654118</v>
       </c>
       <c r="R41" t="n">
-        <v>7008449</v>
+        <v>7008347</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5097,9 +5088,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5114,22 +5120,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120082669</v>
+        <v>120085648</v>
       </c>
       <c r="B42" t="n">
-        <v>91884</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5142,34 +5148,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654314</v>
+        <v>654195</v>
       </c>
       <c r="R42" t="n">
-        <v>7007905</v>
+        <v>7008349</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5201,7 +5207,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5211,7 +5217,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5226,22 +5237,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120088184</v>
+        <v>120087649</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5250,41 +5261,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654118</v>
+        <v>654117</v>
       </c>
       <c r="R43" t="n">
-        <v>7008347</v>
+        <v>7008449</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5311,24 +5326,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5343,12 +5343,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120085300</v>
+        <v>120085695</v>
       </c>
       <c r="B53" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6355,41 +6355,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654207</v>
+        <v>654200</v>
       </c>
       <c r="R53" t="n">
-        <v>7008193</v>
+        <v>7008363</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6416,9 +6416,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6433,22 +6448,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120085759</v>
+        <v>120085300</v>
       </c>
       <c r="B54" t="n">
-        <v>90562</v>
+        <v>91005</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6457,25 +6472,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6485,13 +6500,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654293</v>
+        <v>654207</v>
       </c>
       <c r="R54" t="n">
-        <v>7008191</v>
+        <v>7008193</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6535,22 +6550,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120085695</v>
+        <v>120085759</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6563,37 +6578,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654200</v>
+        <v>654293</v>
       </c>
       <c r="R55" t="n">
-        <v>7008363</v>
+        <v>7008191</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6620,24 +6635,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6652,12 +6652,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120088364</v>
+        <v>120085485</v>
       </c>
       <c r="B61" t="n">
-        <v>90905</v>
+        <v>90846</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7264,41 +7264,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654153</v>
+        <v>654276</v>
       </c>
       <c r="R61" t="n">
-        <v>7008523</v>
+        <v>7008093</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7342,19 +7342,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120088261</v>
+        <v>120082329</v>
       </c>
       <c r="B62" t="n">
         <v>57310</v>
@@ -7390,14 +7390,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Svartnäsviken, Svartnäsviken, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654154</v>
+        <v>654290</v>
       </c>
       <c r="R62" t="n">
-        <v>7008250</v>
+        <v>7007940</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7459,19 +7459,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120086638</v>
+        <v>120085919</v>
       </c>
       <c r="B63" t="n">
         <v>57310</v>
@@ -7507,14 +7507,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654208</v>
+        <v>654285</v>
       </c>
       <c r="R63" t="n">
-        <v>7008351</v>
+        <v>7008199</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7556,12 +7556,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7576,22 +7576,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120085485</v>
+        <v>120088261</v>
       </c>
       <c r="B64" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7604,37 +7604,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäsviken, Svartnäsviken, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654276</v>
+        <v>654154</v>
       </c>
       <c r="R64" t="n">
-        <v>7008093</v>
+        <v>7008250</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7661,9 +7661,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7678,19 +7693,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120082329</v>
+        <v>120086638</v>
       </c>
       <c r="B65" t="n">
         <v>57310</v>
@@ -7726,14 +7741,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654290</v>
+        <v>654208</v>
       </c>
       <c r="R65" t="n">
-        <v>7007940</v>
+        <v>7008351</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7765,7 +7780,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7775,12 +7790,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7795,22 +7810,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120085919</v>
+        <v>120088364</v>
       </c>
       <c r="B66" t="n">
-        <v>57310</v>
+        <v>90905</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7819,41 +7834,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654285</v>
+        <v>654153</v>
       </c>
       <c r="R66" t="n">
-        <v>7008199</v>
+        <v>7008523</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7880,24 +7895,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7912,22 +7912,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120085706</v>
+        <v>120087238</v>
       </c>
       <c r="B67" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7936,38 +7936,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654297</v>
+        <v>654193</v>
       </c>
       <c r="R67" t="n">
-        <v>7008132</v>
+        <v>7008384</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120087238</v>
+        <v>120085706</v>
       </c>
       <c r="B68" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8038,38 +8038,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654193</v>
+        <v>654297</v>
       </c>
       <c r="R68" t="n">
-        <v>7008384</v>
+        <v>7008132</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088486</v>
+        <v>120088072</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,38 +2011,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654118</v>
+        <v>654111</v>
       </c>
       <c r="R14" t="n">
-        <v>7008045</v>
+        <v>7008487</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,12 +2088,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,19 +2103,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088639</v>
+        <v>120088486</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2156,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654098</v>
+        <v>654118</v>
       </c>
       <c r="R15" t="n">
-        <v>7007903</v>
+        <v>7008045</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2190,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,12 +2200,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088072</v>
+        <v>120088639</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,42 +2244,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654111</v>
+        <v>654098</v>
       </c>
       <c r="R16" t="n">
-        <v>7008487</v>
+        <v>7007903</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2312,7 +2307,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2322,7 +2317,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,12 +2337,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120082214</v>
+        <v>120085648</v>
       </c>
       <c r="B39" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4802,16 +4802,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4822,14 +4822,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654279</v>
+        <v>654195</v>
       </c>
       <c r="R39" t="n">
-        <v>7007930</v>
+        <v>7008349</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färskt bohål.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4891,22 +4891,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120082669</v>
+        <v>120082214</v>
       </c>
       <c r="B40" t="n">
-        <v>91884</v>
+        <v>57326</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4919,21 +4919,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654314</v>
+        <v>654279</v>
       </c>
       <c r="R40" t="n">
-        <v>7007905</v>
+        <v>7007930</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4988,7 +4988,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5015,10 +5020,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120088184</v>
+        <v>120087649</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5027,41 +5032,45 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654118</v>
+        <v>654117</v>
       </c>
       <c r="R41" t="n">
-        <v>7008347</v>
+        <v>7008449</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5088,24 +5097,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,22 +5114,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120085648</v>
+        <v>120082669</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>91884</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5148,34 +5142,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654195</v>
+        <v>654314</v>
       </c>
       <c r="R42" t="n">
-        <v>7008349</v>
+        <v>7007905</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5207,7 +5201,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5217,12 +5211,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5237,22 +5226,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120087649</v>
+        <v>120088184</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5261,45 +5250,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654117</v>
+        <v>654118</v>
       </c>
       <c r="R43" t="n">
-        <v>7008449</v>
+        <v>7008347</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,9 +5311,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5343,12 +5343,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120085695</v>
+        <v>120085300</v>
       </c>
       <c r="B53" t="n">
-        <v>57310</v>
+        <v>91005</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6355,41 +6355,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654200</v>
+        <v>654207</v>
       </c>
       <c r="R53" t="n">
-        <v>7008363</v>
+        <v>7008193</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6416,24 +6416,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6448,22 +6433,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120085300</v>
+        <v>120085759</v>
       </c>
       <c r="B54" t="n">
-        <v>91005</v>
+        <v>90562</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6472,25 +6457,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6500,13 +6485,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654207</v>
+        <v>654293</v>
       </c>
       <c r="R54" t="n">
-        <v>7008193</v>
+        <v>7008191</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6550,22 +6535,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120085759</v>
+        <v>120085695</v>
       </c>
       <c r="B55" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6578,37 +6563,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654293</v>
+        <v>654200</v>
       </c>
       <c r="R55" t="n">
-        <v>7008191</v>
+        <v>7008363</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6635,9 +6620,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6652,12 +6652,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120085485</v>
+        <v>120088364</v>
       </c>
       <c r="B61" t="n">
-        <v>90846</v>
+        <v>90905</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7264,41 +7264,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654276</v>
+        <v>654153</v>
       </c>
       <c r="R61" t="n">
-        <v>7008093</v>
+        <v>7008523</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7342,19 +7342,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120082329</v>
+        <v>120088261</v>
       </c>
       <c r="B62" t="n">
         <v>57310</v>
@@ -7390,14 +7390,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäsviken, Svartnäsviken, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654290</v>
+        <v>654154</v>
       </c>
       <c r="R62" t="n">
-        <v>7007940</v>
+        <v>7008250</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7459,19 +7459,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120085919</v>
+        <v>120086638</v>
       </c>
       <c r="B63" t="n">
         <v>57310</v>
@@ -7507,14 +7507,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654285</v>
+        <v>654208</v>
       </c>
       <c r="R63" t="n">
-        <v>7008199</v>
+        <v>7008351</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7556,12 +7556,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7576,22 +7576,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120088261</v>
+        <v>120085485</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7604,37 +7604,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svartnäsviken, Svartnäsviken, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654154</v>
+        <v>654276</v>
       </c>
       <c r="R64" t="n">
-        <v>7008250</v>
+        <v>7008093</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7661,24 +7661,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7693,19 +7678,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120086638</v>
+        <v>120082329</v>
       </c>
       <c r="B65" t="n">
         <v>57310</v>
@@ -7741,14 +7726,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654208</v>
+        <v>654290</v>
       </c>
       <c r="R65" t="n">
-        <v>7008351</v>
+        <v>7007940</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7780,7 +7765,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7790,12 +7775,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7810,22 +7795,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120088364</v>
+        <v>120085919</v>
       </c>
       <c r="B66" t="n">
-        <v>90905</v>
+        <v>57310</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7834,41 +7819,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654153</v>
+        <v>654285</v>
       </c>
       <c r="R66" t="n">
-        <v>7008523</v>
+        <v>7008199</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7895,9 +7880,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7912,22 +7912,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120087238</v>
+        <v>120085706</v>
       </c>
       <c r="B67" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7936,38 +7936,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654193</v>
+        <v>654297</v>
       </c>
       <c r="R67" t="n">
-        <v>7008384</v>
+        <v>7008132</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120085706</v>
+        <v>120087238</v>
       </c>
       <c r="B68" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8038,38 +8038,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654297</v>
+        <v>654193</v>
       </c>
       <c r="R68" t="n">
-        <v>7008132</v>
+        <v>7008384</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -5355,10 +5355,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120085939</v>
+        <v>120082934</v>
       </c>
       <c r="B44" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5367,38 +5367,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654279</v>
+        <v>654181</v>
       </c>
       <c r="R44" t="n">
-        <v>7008217</v>
+        <v>7007955</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5455,22 +5455,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120082934</v>
+        <v>120085939</v>
       </c>
       <c r="B45" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5479,38 +5479,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654181</v>
+        <v>654279</v>
       </c>
       <c r="R45" t="n">
-        <v>7007955</v>
+        <v>7008217</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5567,12 +5567,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6114,10 +6114,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120082158</v>
+        <v>120085755</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6126,38 +6126,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654220</v>
+        <v>654292</v>
       </c>
       <c r="R51" t="n">
-        <v>7007891</v>
+        <v>7008151</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6189,7 +6194,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6199,7 +6204,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6226,10 +6231,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120085755</v>
+        <v>120082158</v>
       </c>
       <c r="B52" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6238,43 +6243,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654292</v>
+        <v>654220</v>
       </c>
       <c r="R52" t="n">
-        <v>7008151</v>
+        <v>7007891</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6343,10 +6343,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120085300</v>
+        <v>120085695</v>
       </c>
       <c r="B53" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6355,41 +6355,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654207</v>
+        <v>654200</v>
       </c>
       <c r="R53" t="n">
-        <v>7008193</v>
+        <v>7008363</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6416,9 +6416,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6433,22 +6448,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120085759</v>
+        <v>120085300</v>
       </c>
       <c r="B54" t="n">
-        <v>90562</v>
+        <v>91005</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6457,25 +6472,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6485,13 +6500,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654293</v>
+        <v>654207</v>
       </c>
       <c r="R54" t="n">
-        <v>7008191</v>
+        <v>7008193</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6535,22 +6550,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120085695</v>
+        <v>120085759</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6563,37 +6578,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654200</v>
+        <v>654293</v>
       </c>
       <c r="R55" t="n">
-        <v>7008363</v>
+        <v>7008191</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6620,24 +6635,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6652,12 +6652,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7252,10 +7252,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120088364</v>
+        <v>120085485</v>
       </c>
       <c r="B61" t="n">
-        <v>90905</v>
+        <v>90846</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7264,41 +7264,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654153</v>
+        <v>654276</v>
       </c>
       <c r="R61" t="n">
-        <v>7008523</v>
+        <v>7008093</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7342,19 +7342,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120088261</v>
+        <v>120082329</v>
       </c>
       <c r="B62" t="n">
         <v>57310</v>
@@ -7390,14 +7390,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Svartnäsviken, Svartnäsviken, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654154</v>
+        <v>654290</v>
       </c>
       <c r="R62" t="n">
-        <v>7008250</v>
+        <v>7007940</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7459,19 +7459,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120086638</v>
+        <v>120085919</v>
       </c>
       <c r="B63" t="n">
         <v>57310</v>
@@ -7507,14 +7507,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654208</v>
+        <v>654285</v>
       </c>
       <c r="R63" t="n">
-        <v>7008351</v>
+        <v>7008199</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7556,12 +7556,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7576,22 +7576,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120085485</v>
+        <v>120088261</v>
       </c>
       <c r="B64" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7604,37 +7604,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäsviken, Svartnäsviken, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654276</v>
+        <v>654154</v>
       </c>
       <c r="R64" t="n">
-        <v>7008093</v>
+        <v>7008250</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7661,9 +7661,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7678,19 +7693,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120082329</v>
+        <v>120086638</v>
       </c>
       <c r="B65" t="n">
         <v>57310</v>
@@ -7726,14 +7741,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654290</v>
+        <v>654208</v>
       </c>
       <c r="R65" t="n">
-        <v>7007940</v>
+        <v>7008351</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7765,7 +7780,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7775,12 +7790,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7795,22 +7810,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120085919</v>
+        <v>120088364</v>
       </c>
       <c r="B66" t="n">
-        <v>57310</v>
+        <v>90905</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7819,41 +7834,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654285</v>
+        <v>654153</v>
       </c>
       <c r="R66" t="n">
-        <v>7008199</v>
+        <v>7008523</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7880,24 +7895,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7912,12 +7912,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088072</v>
+        <v>120088486</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,42 +2011,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654111</v>
+        <v>654118</v>
       </c>
       <c r="R14" t="n">
-        <v>7008487</v>
+        <v>7008045</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2088,7 +2084,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,19 +2104,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088486</v>
+        <v>120088639</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2155,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654118</v>
+        <v>654098</v>
       </c>
       <c r="R15" t="n">
-        <v>7008045</v>
+        <v>7007903</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2200,12 +2201,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2232,10 +2233,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088639</v>
+        <v>120088072</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,38 +2245,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654098</v>
+        <v>654111</v>
       </c>
       <c r="R16" t="n">
-        <v>7007903</v>
+        <v>7008487</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2317,12 +2322,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,12 +2337,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120087985</v>
+        <v>120086920</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2478,42 +2478,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654128</v>
+        <v>654164</v>
       </c>
       <c r="R18" t="n">
-        <v>7008520</v>
+        <v>7008398</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2545,7 +2541,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2555,7 +2551,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2570,22 +2571,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120085506</v>
+        <v>120087985</v>
       </c>
       <c r="B19" t="n">
-        <v>90905</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2598,34 +2599,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654287</v>
+        <v>654128</v>
       </c>
       <c r="R19" t="n">
-        <v>7008086</v>
+        <v>7008520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2657,7 +2662,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2667,7 +2672,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120085468</v>
+        <v>120085506</v>
       </c>
       <c r="B20" t="n">
-        <v>90527</v>
+        <v>90905</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2706,25 +2711,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2734,13 +2739,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654268</v>
+        <v>654287</v>
       </c>
       <c r="R20" t="n">
-        <v>7008096</v>
+        <v>7008086</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2767,9 +2772,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2784,22 +2799,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120086920</v>
+        <v>120085468</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2808,41 +2823,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654164</v>
+        <v>654268</v>
       </c>
       <c r="R21" t="n">
-        <v>7008398</v>
+        <v>7008096</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2869,24 +2884,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,12 +2901,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120085211</v>
+        <v>120086159</v>
       </c>
       <c r="B37" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4583,37 +4583,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654207</v>
+        <v>654239</v>
       </c>
       <c r="R37" t="n">
-        <v>7008193</v>
+        <v>7008276</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4640,9 +4640,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4657,22 +4672,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120086159</v>
+        <v>120085211</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4685,37 +4700,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654239</v>
+        <v>654207</v>
       </c>
       <c r="R38" t="n">
-        <v>7008276</v>
+        <v>7008193</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4742,24 +4757,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4774,22 +4774,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120085648</v>
+        <v>120082214</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4802,16 +4802,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4822,14 +4822,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654195</v>
+        <v>654279</v>
       </c>
       <c r="R39" t="n">
-        <v>7008349</v>
+        <v>7007930</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4891,22 +4891,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120082214</v>
+        <v>120082669</v>
       </c>
       <c r="B40" t="n">
-        <v>57326</v>
+        <v>91884</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4919,21 +4919,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654279</v>
+        <v>654314</v>
       </c>
       <c r="R40" t="n">
-        <v>7007930</v>
+        <v>7007905</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4988,12 +4988,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färskt bohål.</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5020,10 +5015,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120087649</v>
+        <v>120088184</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5032,45 +5027,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654117</v>
+        <v>654118</v>
       </c>
       <c r="R41" t="n">
-        <v>7008449</v>
+        <v>7008347</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5097,9 +5088,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5114,22 +5120,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120082669</v>
+        <v>120085648</v>
       </c>
       <c r="B42" t="n">
-        <v>91884</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5142,34 +5148,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654314</v>
+        <v>654195</v>
       </c>
       <c r="R42" t="n">
-        <v>7007905</v>
+        <v>7008349</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5201,7 +5207,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5211,7 +5217,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5226,22 +5237,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120088184</v>
+        <v>120087649</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5250,41 +5261,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654118</v>
+        <v>654117</v>
       </c>
       <c r="R43" t="n">
-        <v>7008347</v>
+        <v>7008449</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5311,24 +5326,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5343,22 +5343,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120082934</v>
+        <v>120085939</v>
       </c>
       <c r="B44" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5367,38 +5367,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654181</v>
+        <v>654279</v>
       </c>
       <c r="R44" t="n">
-        <v>7007955</v>
+        <v>7008217</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5455,22 +5455,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120085939</v>
+        <v>120082934</v>
       </c>
       <c r="B45" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5479,38 +5479,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654279</v>
+        <v>654181</v>
       </c>
       <c r="R45" t="n">
-        <v>7008217</v>
+        <v>7007955</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5567,12 +5567,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120085695</v>
+        <v>120085300</v>
       </c>
       <c r="B53" t="n">
-        <v>57310</v>
+        <v>91005</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6355,41 +6355,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654200</v>
+        <v>654207</v>
       </c>
       <c r="R53" t="n">
-        <v>7008363</v>
+        <v>7008193</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6416,24 +6416,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6448,22 +6433,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120085300</v>
+        <v>120085759</v>
       </c>
       <c r="B54" t="n">
-        <v>91005</v>
+        <v>90562</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6472,25 +6457,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6500,13 +6485,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654207</v>
+        <v>654293</v>
       </c>
       <c r="R54" t="n">
-        <v>7008193</v>
+        <v>7008191</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6550,22 +6535,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120085759</v>
+        <v>120085695</v>
       </c>
       <c r="B55" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6578,37 +6563,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654293</v>
+        <v>654200</v>
       </c>
       <c r="R55" t="n">
-        <v>7008191</v>
+        <v>7008363</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6635,9 +6620,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6652,12 +6652,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7924,10 +7924,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120085706</v>
+        <v>120087238</v>
       </c>
       <c r="B67" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7936,38 +7936,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654297</v>
+        <v>654193</v>
       </c>
       <c r="R67" t="n">
-        <v>7008132</v>
+        <v>7008384</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120087238</v>
+        <v>120085706</v>
       </c>
       <c r="B68" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8038,38 +8038,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654193</v>
+        <v>654297</v>
       </c>
       <c r="R68" t="n">
-        <v>7008384</v>
+        <v>7008132</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088486</v>
+        <v>120088072</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,38 +2011,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654118</v>
+        <v>654111</v>
       </c>
       <c r="R14" t="n">
-        <v>7008045</v>
+        <v>7008487</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,12 +2088,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,19 +2103,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088639</v>
+        <v>120088486</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2156,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654098</v>
+        <v>654118</v>
       </c>
       <c r="R15" t="n">
-        <v>7007903</v>
+        <v>7008045</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2190,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,12 +2200,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088072</v>
+        <v>120088639</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,42 +2244,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654111</v>
+        <v>654098</v>
       </c>
       <c r="R16" t="n">
-        <v>7008487</v>
+        <v>7007903</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2312,7 +2307,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2322,7 +2317,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,12 +2337,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -6114,10 +6114,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120085755</v>
+        <v>120082158</v>
       </c>
       <c r="B51" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6126,43 +6126,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654292</v>
+        <v>654220</v>
       </c>
       <c r="R51" t="n">
-        <v>7008151</v>
+        <v>7007891</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6194,7 +6189,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6204,7 +6199,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6231,10 +6226,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120082158</v>
+        <v>120085755</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6243,38 +6238,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654220</v>
+        <v>654292</v>
       </c>
       <c r="R52" t="n">
-        <v>7007891</v>
+        <v>7008151</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -4786,10 +4786,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120082214</v>
+        <v>120085648</v>
       </c>
       <c r="B39" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4802,16 +4802,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4822,14 +4822,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654279</v>
+        <v>654195</v>
       </c>
       <c r="R39" t="n">
-        <v>7007930</v>
+        <v>7008349</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färskt bohål.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4891,22 +4891,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120082669</v>
+        <v>120082214</v>
       </c>
       <c r="B40" t="n">
-        <v>91884</v>
+        <v>57326</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4919,21 +4919,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654314</v>
+        <v>654279</v>
       </c>
       <c r="R40" t="n">
-        <v>7007905</v>
+        <v>7007930</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4988,7 +4988,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5015,10 +5020,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120088184</v>
+        <v>120087649</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5027,41 +5032,45 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654118</v>
+        <v>654117</v>
       </c>
       <c r="R41" t="n">
-        <v>7008347</v>
+        <v>7008449</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5088,24 +5097,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,22 +5114,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120085648</v>
+        <v>120082669</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>91884</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5148,34 +5142,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654195</v>
+        <v>654314</v>
       </c>
       <c r="R42" t="n">
-        <v>7008349</v>
+        <v>7007905</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5207,7 +5201,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5217,12 +5211,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5237,22 +5226,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120087649</v>
+        <v>120088184</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5261,45 +5250,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654117</v>
+        <v>654118</v>
       </c>
       <c r="R43" t="n">
-        <v>7008449</v>
+        <v>7008347</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,9 +5311,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5343,12 +5343,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6114,10 +6114,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120082158</v>
+        <v>120085755</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6126,38 +6126,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654220</v>
+        <v>654292</v>
       </c>
       <c r="R51" t="n">
-        <v>7007891</v>
+        <v>7008151</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6189,7 +6194,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6199,7 +6204,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6226,10 +6231,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120085755</v>
+        <v>120082158</v>
       </c>
       <c r="B52" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6238,43 +6243,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654292</v>
+        <v>654220</v>
       </c>
       <c r="R52" t="n">
-        <v>7008151</v>
+        <v>7007891</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088072</v>
+        <v>120087985</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654111</v>
+        <v>654128</v>
       </c>
       <c r="R14" t="n">
-        <v>7008487</v>
+        <v>7008520</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088486</v>
+        <v>120085485</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>90864</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,37 +2131,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654118</v>
+        <v>654276</v>
       </c>
       <c r="R15" t="n">
-        <v>7008045</v>
+        <v>7008093</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2188,24 +2188,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2220,22 +2205,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088639</v>
+        <v>120085300</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>91023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,41 +2229,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654098</v>
+        <v>654207</v>
       </c>
       <c r="R16" t="n">
-        <v>7007903</v>
+        <v>7008193</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2305,24 +2290,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,22 +2307,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120087568</v>
+        <v>120085193</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,37 +2335,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654173</v>
+        <v>654207</v>
       </c>
       <c r="R17" t="n">
-        <v>7008502</v>
+        <v>7008193</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2422,24 +2392,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,22 +2409,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120086920</v>
+        <v>120085706</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90545</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2478,41 +2433,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654164</v>
+        <v>654297</v>
       </c>
       <c r="R18" t="n">
-        <v>7008398</v>
+        <v>7008132</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2539,24 +2494,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,22 +2511,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120087985</v>
+        <v>120085695</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,42 +2535,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654128</v>
+        <v>654200</v>
       </c>
       <c r="R19" t="n">
-        <v>7008520</v>
+        <v>7008363</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2662,7 +2598,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2672,7 +2608,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2687,22 +2628,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120085506</v>
+        <v>120088639</v>
       </c>
       <c r="B20" t="n">
-        <v>90905</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,38 +2652,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654287</v>
+        <v>654098</v>
       </c>
       <c r="R20" t="n">
-        <v>7008086</v>
+        <v>7007903</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,7 +2715,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2784,7 +2725,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2799,12 +2745,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2814,7 +2760,7 @@
         <v>120085468</v>
       </c>
       <c r="B21" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2913,10 +2859,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120085424</v>
+        <v>120088520</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2929,34 +2875,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654284</v>
+        <v>654121</v>
       </c>
       <c r="R22" t="n">
-        <v>7008101</v>
+        <v>7008041</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2988,7 +2934,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2998,7 +2944,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3025,10 +2976,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120085068</v>
+        <v>120086159</v>
       </c>
       <c r="B23" t="n">
-        <v>91005</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3037,38 +2988,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654217</v>
+        <v>654239</v>
       </c>
       <c r="R23" t="n">
-        <v>7008168</v>
+        <v>7008276</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,7 +3051,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3110,7 +3061,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,22 +3081,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088111</v>
+        <v>120082669</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3149,38 +3105,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Renudden, Renudden, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654070</v>
+        <v>654314</v>
       </c>
       <c r="R24" t="n">
-        <v>7008447</v>
+        <v>7007905</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3212,7 +3168,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3222,7 +3178,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3252,7 +3208,7 @@
         <v>120086783</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3366,10 +3322,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088260</v>
+        <v>120082215</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3378,38 +3334,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654139</v>
+        <v>654150</v>
       </c>
       <c r="R26" t="n">
-        <v>7008299</v>
+        <v>7007925</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3441,7 +3406,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3451,7 +3416,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3466,22 +3431,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120085757</v>
+        <v>120085759</v>
       </c>
       <c r="B27" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3494,21 +3459,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3518,10 +3483,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654286</v>
+        <v>654293</v>
       </c>
       <c r="R27" t="n">
-        <v>7008186</v>
+        <v>7008191</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3580,10 +3545,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088520</v>
+        <v>120085930</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>91023</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3592,41 +3557,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654121</v>
+        <v>654269</v>
       </c>
       <c r="R28" t="n">
-        <v>7008041</v>
+        <v>7008197</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3653,24 +3618,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3685,22 +3635,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120081327</v>
+        <v>120085211</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>90864</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3713,37 +3663,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654200</v>
+        <v>654207</v>
       </c>
       <c r="R29" t="n">
-        <v>7007872</v>
+        <v>7008193</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3773,11 +3723,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3792,22 +3737,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120085434</v>
+        <v>120085939</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3820,37 +3765,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654217</v>
+        <v>654279</v>
       </c>
       <c r="R30" t="n">
-        <v>7008312</v>
+        <v>7008217</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3879,7 +3824,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3889,12 +3834,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3909,22 +3849,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120082342</v>
+        <v>120088364</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>90923</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3937,46 +3877,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654125</v>
+        <v>654153</v>
       </c>
       <c r="R31" t="n">
-        <v>7007981</v>
+        <v>7008523</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4003,19 +3934,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4030,22 +3951,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120085930</v>
+        <v>120088072</v>
       </c>
       <c r="B32" t="n">
-        <v>91005</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4058,37 +3979,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654269</v>
+        <v>654111</v>
       </c>
       <c r="R32" t="n">
-        <v>7008197</v>
+        <v>7008487</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4115,9 +4040,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4132,22 +4067,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120085493</v>
+        <v>120086920</v>
       </c>
       <c r="B33" t="n">
-        <v>86878</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4160,21 +4095,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4184,13 +4119,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654196</v>
+        <v>654164</v>
       </c>
       <c r="R33" t="n">
-        <v>7008339</v>
+        <v>7008398</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4217,9 +4152,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4234,22 +4184,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120085193</v>
+        <v>120088189</v>
       </c>
       <c r="B34" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4262,37 +4212,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654207</v>
+        <v>654128</v>
       </c>
       <c r="R34" t="n">
-        <v>7008193</v>
+        <v>7008344</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4319,9 +4269,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4336,22 +4301,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120086958</v>
+        <v>120085755</v>
       </c>
       <c r="B35" t="n">
-        <v>90562</v>
+        <v>57336</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4364,37 +4329,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654151</v>
+        <v>654292</v>
       </c>
       <c r="R35" t="n">
-        <v>7008440</v>
+        <v>7008151</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4421,9 +4391,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4438,22 +4418,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120082271</v>
+        <v>120082158</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4462,25 +4442,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4490,10 +4470,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654150</v>
+        <v>654220</v>
       </c>
       <c r="R36" t="n">
-        <v>7007925</v>
+        <v>7007891</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4525,7 +4505,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4535,12 +4515,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,22 +4530,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120086159</v>
+        <v>120087238</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4583,21 +4558,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4607,13 +4582,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654239</v>
+        <v>654193</v>
       </c>
       <c r="R37" t="n">
-        <v>7008276</v>
+        <v>7008384</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4640,24 +4615,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4672,22 +4632,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120085211</v>
+        <v>120087250</v>
       </c>
       <c r="B38" t="n">
-        <v>90846</v>
+        <v>90545</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4696,41 +4656,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654207</v>
+        <v>654191</v>
       </c>
       <c r="R38" t="n">
-        <v>7008193</v>
+        <v>7008385</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4774,22 +4734,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120085648</v>
+        <v>120085434</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4826,13 +4786,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654195</v>
+        <v>654217</v>
       </c>
       <c r="R39" t="n">
-        <v>7008349</v>
+        <v>7008312</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4861,7 +4821,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4871,7 +4831,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4903,10 +4863,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120082214</v>
+        <v>120085919</v>
       </c>
       <c r="B40" t="n">
-        <v>57326</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4919,16 +4879,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4943,10 +4903,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654279</v>
+        <v>654285</v>
       </c>
       <c r="R40" t="n">
-        <v>7007930</v>
+        <v>7008199</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,7 +4938,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4988,12 +4948,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färskt bohål.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5020,10 +4980,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120087649</v>
+        <v>120087102</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5055,7 +5015,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5064,13 +5029,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654117</v>
+        <v>654149</v>
       </c>
       <c r="R41" t="n">
-        <v>7008449</v>
+        <v>7008498</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5097,9 +5062,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5114,22 +5089,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120082669</v>
+        <v>120085493</v>
       </c>
       <c r="B42" t="n">
-        <v>91884</v>
+        <v>86895</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5142,37 +5117,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>510</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654314</v>
+        <v>654196</v>
       </c>
       <c r="R42" t="n">
-        <v>7007905</v>
+        <v>7008339</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5199,19 +5174,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5226,22 +5191,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120088184</v>
+        <v>120085757</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>90864</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5254,37 +5219,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654118</v>
+        <v>654286</v>
       </c>
       <c r="R43" t="n">
-        <v>7008347</v>
+        <v>7008186</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5311,24 +5276,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5343,22 +5293,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120085939</v>
+        <v>120082271</v>
       </c>
       <c r="B44" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5371,34 +5321,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654279</v>
+        <v>654150</v>
       </c>
       <c r="R44" t="n">
-        <v>7008217</v>
+        <v>7007925</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5430,7 +5380,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5440,7 +5390,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5455,22 +5410,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120082934</v>
+        <v>120082342</v>
       </c>
       <c r="B45" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5479,38 +5434,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654181</v>
+        <v>654125</v>
       </c>
       <c r="R45" t="n">
-        <v>7007955</v>
+        <v>7007981</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5542,7 +5506,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5552,7 +5516,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5579,10 +5543,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120082434</v>
+        <v>120082934</v>
       </c>
       <c r="B46" t="n">
-        <v>91832</v>
+        <v>91858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5591,38 +5555,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654303</v>
+        <v>654181</v>
       </c>
       <c r="R46" t="n">
-        <v>7007918</v>
+        <v>7007955</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5654,7 +5618,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5664,7 +5628,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5679,22 +5643,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120087250</v>
+        <v>120086958</v>
       </c>
       <c r="B47" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5703,25 +5667,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5731,13 +5695,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654191</v>
+        <v>654151</v>
       </c>
       <c r="R47" t="n">
-        <v>7008385</v>
+        <v>7008440</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5781,22 +5745,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120087230</v>
+        <v>120082329</v>
       </c>
       <c r="B48" t="n">
-        <v>90846</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5809,37 +5773,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654170</v>
+        <v>654290</v>
       </c>
       <c r="R48" t="n">
-        <v>7008380</v>
+        <v>7007940</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5866,9 +5830,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5883,22 +5862,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120085491</v>
+        <v>120082434</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>91850</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5911,37 +5890,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654200</v>
+        <v>654303</v>
       </c>
       <c r="R49" t="n">
-        <v>7008326</v>
+        <v>7007918</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5970,7 +5949,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5980,12 +5959,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6000,22 +5974,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120087288</v>
+        <v>120087230</v>
       </c>
       <c r="B50" t="n">
-        <v>90562</v>
+        <v>90864</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6028,21 +6002,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6052,10 +6026,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654159</v>
+        <v>654170</v>
       </c>
       <c r="R50" t="n">
-        <v>7008481</v>
+        <v>7008380</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6114,10 +6088,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120085755</v>
+        <v>120088260</v>
       </c>
       <c r="B51" t="n">
-        <v>57326</v>
+        <v>90598</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6130,39 +6104,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654292</v>
+        <v>654139</v>
       </c>
       <c r="R51" t="n">
-        <v>7008151</v>
+        <v>7008299</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6194,7 +6163,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6204,7 +6173,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6231,10 +6200,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120082158</v>
+        <v>120081327</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6243,25 +6212,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6271,13 +6240,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654220</v>
+        <v>654200</v>
       </c>
       <c r="R52" t="n">
-        <v>7007891</v>
+        <v>7007872</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6304,19 +6273,14 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:14</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6331,22 +6295,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120085300</v>
+        <v>120088486</v>
       </c>
       <c r="B53" t="n">
-        <v>91005</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6355,41 +6319,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654207</v>
+        <v>654118</v>
       </c>
       <c r="R53" t="n">
-        <v>7008193</v>
+        <v>7008045</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6416,9 +6380,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6433,22 +6412,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120085759</v>
+        <v>120085424</v>
       </c>
       <c r="B54" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6485,13 +6464,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654293</v>
+        <v>654284</v>
       </c>
       <c r="R54" t="n">
-        <v>7008191</v>
+        <v>7008101</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6518,9 +6497,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6535,22 +6524,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120085695</v>
+        <v>120085491</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6590,10 +6579,10 @@
         <v>654200</v>
       </c>
       <c r="R55" t="n">
-        <v>7008363</v>
+        <v>7008326</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6622,7 +6611,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6632,12 +6621,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6664,10 +6653,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120086940</v>
+        <v>120088261</v>
       </c>
       <c r="B56" t="n">
-        <v>78263</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6680,34 +6669,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsviken, Svartnäsviken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654160</v>
+        <v>654154</v>
       </c>
       <c r="R56" t="n">
-        <v>7008398</v>
+        <v>7008250</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6739,7 +6728,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6749,7 +6738,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6776,10 +6770,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120088189</v>
+        <v>120085648</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6816,10 +6810,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654128</v>
+        <v>654195</v>
       </c>
       <c r="R57" t="n">
-        <v>7008344</v>
+        <v>7008349</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6851,7 +6845,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6861,12 +6855,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6881,22 +6875,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120086991</v>
+        <v>120085068</v>
       </c>
       <c r="B58" t="n">
-        <v>57310</v>
+        <v>91023</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6905,38 +6899,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654156</v>
+        <v>654217</v>
       </c>
       <c r="R58" t="n">
-        <v>7008421</v>
+        <v>7008168</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6968,7 +6962,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6978,12 +6972,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7010,10 +6999,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120082215</v>
+        <v>120082214</v>
       </c>
       <c r="B59" t="n">
-        <v>97907</v>
+        <v>57336</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7022,47 +7011,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654150</v>
+        <v>654279</v>
       </c>
       <c r="R59" t="n">
-        <v>7007925</v>
+        <v>7007930</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7094,7 +7074,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7104,7 +7084,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7119,22 +7104,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120087102</v>
+        <v>120088184</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7143,47 +7128,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>654149</v>
+        <v>654118</v>
       </c>
       <c r="R60" t="n">
-        <v>7008498</v>
+        <v>7008347</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7215,7 +7191,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7225,7 +7201,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7252,10 +7233,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120085485</v>
+        <v>120086991</v>
       </c>
       <c r="B61" t="n">
-        <v>90846</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7268,37 +7249,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654276</v>
+        <v>654156</v>
       </c>
       <c r="R61" t="n">
-        <v>7008093</v>
+        <v>7008421</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7325,9 +7306,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7342,22 +7338,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120082329</v>
+        <v>120085506</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>90923</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7366,25 +7362,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7394,10 +7390,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654290</v>
+        <v>654287</v>
       </c>
       <c r="R62" t="n">
-        <v>7007940</v>
+        <v>7008086</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7429,7 +7425,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7439,12 +7435,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7471,10 +7462,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120085919</v>
+        <v>120086940</v>
       </c>
       <c r="B63" t="n">
-        <v>57310</v>
+        <v>78279</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7487,34 +7478,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654285</v>
+        <v>654160</v>
       </c>
       <c r="R63" t="n">
-        <v>7008199</v>
+        <v>7008398</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7546,7 +7537,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7556,12 +7547,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7576,22 +7562,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120088261</v>
+        <v>120087568</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7624,14 +7610,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svartnäsviken, Svartnäsviken, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654154</v>
+        <v>654173</v>
       </c>
       <c r="R64" t="n">
-        <v>7008250</v>
+        <v>7008502</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7663,7 +7649,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7673,12 +7659,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7708,7 +7694,7 @@
         <v>120086638</v>
       </c>
       <c r="B65" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7822,10 +7808,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120088364</v>
+        <v>120087649</v>
       </c>
       <c r="B66" t="n">
-        <v>90905</v>
+        <v>97930</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7838,37 +7824,41 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654153</v>
+        <v>654117</v>
       </c>
       <c r="R66" t="n">
-        <v>7008523</v>
+        <v>7008449</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7912,22 +7902,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120087238</v>
+        <v>120088111</v>
       </c>
       <c r="B67" t="n">
-        <v>90562</v>
+        <v>91858</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7936,41 +7926,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Renudden, Renudden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654193</v>
+        <v>654070</v>
       </c>
       <c r="R67" t="n">
-        <v>7008384</v>
+        <v>7008447</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7997,9 +7987,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8014,22 +8014,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120085706</v>
+        <v>120087288</v>
       </c>
       <c r="B68" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8038,38 +8038,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654297</v>
+        <v>654159</v>
       </c>
       <c r="R68" t="n">
-        <v>7008132</v>
+        <v>7008481</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -3093,10 +3093,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120082669</v>
+        <v>120086783</v>
       </c>
       <c r="B24" t="n">
-        <v>91902</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3109,34 +3109,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654314</v>
+        <v>654209</v>
       </c>
       <c r="R24" t="n">
-        <v>7007905</v>
+        <v>7008406</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3178,7 +3178,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3205,10 +3210,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120086783</v>
+        <v>120082669</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>91902</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3221,34 +3226,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654209</v>
+        <v>654314</v>
       </c>
       <c r="R25" t="n">
-        <v>7008406</v>
+        <v>7007905</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3280,7 +3285,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3290,12 +3295,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3322,10 +3322,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120082215</v>
+        <v>120085759</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3334,50 +3334,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654150</v>
+        <v>654293</v>
       </c>
       <c r="R26" t="n">
-        <v>7007925</v>
+        <v>7008191</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3404,19 +3395,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3431,22 +3412,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120085759</v>
+        <v>120085930</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3455,25 +3436,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3483,10 +3464,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654293</v>
+        <v>654269</v>
       </c>
       <c r="R27" t="n">
-        <v>7008191</v>
+        <v>7008197</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3545,10 +3526,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120085930</v>
+        <v>120082215</v>
       </c>
       <c r="B28" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3561,37 +3542,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654269</v>
+        <v>654150</v>
       </c>
       <c r="R28" t="n">
-        <v>7008197</v>
+        <v>7007925</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3618,9 +3608,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3635,12 +3635,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120086920</v>
+        <v>120085755</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4113,16 +4113,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654164</v>
+        <v>654292</v>
       </c>
       <c r="R33" t="n">
-        <v>7008398</v>
+        <v>7008151</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,7 +4159,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4164,12 +4169,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4184,19 +4184,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120088189</v>
+        <v>120086920</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654128</v>
+        <v>654164</v>
       </c>
       <c r="R34" t="n">
-        <v>7008344</v>
+        <v>7008398</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4301,22 +4301,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120085755</v>
+        <v>120088189</v>
       </c>
       <c r="B35" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4329,16 +4329,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4347,21 +4347,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654292</v>
+        <v>654128</v>
       </c>
       <c r="R35" t="n">
-        <v>7008151</v>
+        <v>7008344</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4393,7 +4388,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4403,7 +4398,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4980,10 +4980,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120087102</v>
+        <v>120085493</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>86895</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4992,50 +4992,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654149</v>
+        <v>654196</v>
       </c>
       <c r="R41" t="n">
-        <v>7008498</v>
+        <v>7008339</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5062,19 +5053,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5089,22 +5070,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120085493</v>
+        <v>120085757</v>
       </c>
       <c r="B42" t="n">
-        <v>86895</v>
+        <v>90864</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5117,37 +5098,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654196</v>
+        <v>654286</v>
       </c>
       <c r="R42" t="n">
-        <v>7008339</v>
+        <v>7008186</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5191,22 +5172,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120085757</v>
+        <v>120082271</v>
       </c>
       <c r="B43" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5219,37 +5200,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654286</v>
+        <v>654150</v>
       </c>
       <c r="R43" t="n">
-        <v>7008186</v>
+        <v>7007925</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5276,9 +5257,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5293,22 +5289,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120082271</v>
+        <v>120087102</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5317,38 +5313,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654150</v>
+        <v>654149</v>
       </c>
       <c r="R44" t="n">
-        <v>7007925</v>
+        <v>7008498</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5380,7 +5385,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5390,12 +5395,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5543,10 +5543,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120082934</v>
+        <v>120086958</v>
       </c>
       <c r="B46" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5555,41 +5555,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654181</v>
+        <v>654151</v>
       </c>
       <c r="R46" t="n">
-        <v>7007955</v>
+        <v>7008440</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5616,19 +5616,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5643,22 +5633,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120086958</v>
+        <v>120082329</v>
       </c>
       <c r="B47" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5671,37 +5661,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654151</v>
+        <v>654290</v>
       </c>
       <c r="R47" t="n">
-        <v>7008440</v>
+        <v>7007940</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5728,9 +5718,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5745,22 +5750,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120082329</v>
+        <v>120082934</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5769,38 +5774,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654290</v>
+        <v>654181</v>
       </c>
       <c r="R48" t="n">
-        <v>7007940</v>
+        <v>7007955</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5832,7 +5837,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5842,12 +5847,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5862,12 +5862,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120088184</v>
+        <v>120086940</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7132,21 +7132,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>654118</v>
+        <v>654160</v>
       </c>
       <c r="R60" t="n">
-        <v>7008347</v>
+        <v>7008398</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7191,7 +7191,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7201,12 +7201,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7233,7 +7228,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120086991</v>
+        <v>120088184</v>
       </c>
       <c r="B61" t="n">
         <v>57320</v>
@@ -7273,10 +7268,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654156</v>
+        <v>654118</v>
       </c>
       <c r="R61" t="n">
-        <v>7008421</v>
+        <v>7008347</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7308,7 +7303,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7318,7 +7313,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7350,10 +7345,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120085506</v>
+        <v>120086991</v>
       </c>
       <c r="B62" t="n">
-        <v>90923</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7362,38 +7357,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654287</v>
+        <v>654156</v>
       </c>
       <c r="R62" t="n">
-        <v>7008086</v>
+        <v>7008421</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7425,7 +7420,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7435,7 +7430,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7450,22 +7450,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120086940</v>
+        <v>120085506</v>
       </c>
       <c r="B63" t="n">
-        <v>78279</v>
+        <v>90923</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7474,38 +7474,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>2062</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654160</v>
+        <v>654287</v>
       </c>
       <c r="R63" t="n">
-        <v>7008398</v>
+        <v>7008086</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7562,12 +7562,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7808,10 +7808,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120087649</v>
+        <v>120088111</v>
       </c>
       <c r="B66" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7820,45 +7820,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Renudden, Renudden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654117</v>
+        <v>654070</v>
       </c>
       <c r="R66" t="n">
-        <v>7008449</v>
+        <v>7008447</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7885,9 +7881,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7902,22 +7908,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120088111</v>
+        <v>120087288</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7926,41 +7932,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Renudden, Renudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654070</v>
+        <v>654159</v>
       </c>
       <c r="R67" t="n">
-        <v>7008447</v>
+        <v>7008481</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7987,19 +7993,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8014,22 +8010,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120087288</v>
+        <v>120087649</v>
       </c>
       <c r="B68" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8038,38 +8034,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654159</v>
+        <v>654117</v>
       </c>
       <c r="R68" t="n">
-        <v>7008481</v>
+        <v>7008449</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120087985</v>
+        <v>120082214</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,42 +2011,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654128</v>
+        <v>654279</v>
       </c>
       <c r="R14" t="n">
-        <v>7008520</v>
+        <v>7007930</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2088,7 +2084,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,7 +2116,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120085485</v>
+        <v>120085411</v>
       </c>
       <c r="B15" t="n">
         <v>90864</v>
@@ -2155,13 +2156,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654276</v>
+        <v>654207</v>
       </c>
       <c r="R15" t="n">
-        <v>7008093</v>
+        <v>7008193</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,22 +2206,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120085300</v>
+        <v>120085424</v>
       </c>
       <c r="B16" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2229,25 +2230,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2257,13 +2258,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654207</v>
+        <v>654284</v>
       </c>
       <c r="R16" t="n">
-        <v>7008193</v>
+        <v>7008101</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2290,9 +2291,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2307,22 +2318,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120085193</v>
+        <v>120086783</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2335,37 +2346,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654207</v>
+        <v>654209</v>
       </c>
       <c r="R17" t="n">
-        <v>7008193</v>
+        <v>7008406</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2392,9 +2403,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,22 +2435,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120085706</v>
+        <v>120087649</v>
       </c>
       <c r="B18" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2433,38 +2459,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654297</v>
+        <v>654117</v>
       </c>
       <c r="R18" t="n">
-        <v>7008132</v>
+        <v>7008449</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2523,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120085695</v>
+        <v>120086958</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2539,21 +2569,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2563,13 +2593,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654200</v>
+        <v>654151</v>
       </c>
       <c r="R19" t="n">
-        <v>7008363</v>
+        <v>7008440</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2596,24 +2626,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,22 +2643,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088639</v>
+        <v>120088364</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>90923</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2652,41 +2667,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654098</v>
+        <v>654153</v>
       </c>
       <c r="R20" t="n">
-        <v>7007903</v>
+        <v>7008523</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2713,24 +2728,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,12 +2745,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088520</v>
+        <v>120086920</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2895,14 +2895,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654121</v>
+        <v>654164</v>
       </c>
       <c r="R22" t="n">
-        <v>7008041</v>
+        <v>7008398</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2964,22 +2964,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120086159</v>
+        <v>120087288</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3016,13 +3016,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654239</v>
+        <v>654159</v>
       </c>
       <c r="R23" t="n">
-        <v>7008276</v>
+        <v>7008481</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3049,24 +3049,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,22 +3066,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120086783</v>
+        <v>120088111</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3105,38 +3090,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Renudden, Renudden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654209</v>
+        <v>654070</v>
       </c>
       <c r="R24" t="n">
-        <v>7008406</v>
+        <v>7008447</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3168,7 +3153,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3178,12 +3163,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3210,10 +3190,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120082669</v>
+        <v>120088260</v>
       </c>
       <c r="B25" t="n">
-        <v>91902</v>
+        <v>90598</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3226,34 +3206,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654314</v>
+        <v>654139</v>
       </c>
       <c r="R25" t="n">
-        <v>7007905</v>
+        <v>7008299</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,7 +3265,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3295,7 +3275,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3322,10 +3302,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120085759</v>
+        <v>120085757</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3338,21 +3318,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3362,10 +3342,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654293</v>
+        <v>654286</v>
       </c>
       <c r="R26" t="n">
-        <v>7008191</v>
+        <v>7008186</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3424,10 +3404,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120085930</v>
+        <v>120088520</v>
       </c>
       <c r="B27" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3436,41 +3416,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654269</v>
+        <v>654121</v>
       </c>
       <c r="R27" t="n">
-        <v>7008197</v>
+        <v>7008041</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3497,9 +3477,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3514,22 +3509,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120082215</v>
+        <v>120085930</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>91023</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3542,46 +3537,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654150</v>
+        <v>654269</v>
       </c>
       <c r="R28" t="n">
-        <v>7007925</v>
+        <v>7008197</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3608,19 +3594,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3635,22 +3611,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120085211</v>
+        <v>120087250</v>
       </c>
       <c r="B29" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3659,41 +3635,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654207</v>
+        <v>654191</v>
       </c>
       <c r="R29" t="n">
-        <v>7008193</v>
+        <v>7008385</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3737,19 +3713,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120085939</v>
+        <v>120085193</v>
       </c>
       <c r="B30" t="n">
         <v>90580</v>
@@ -3789,13 +3765,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654279</v>
+        <v>654207</v>
       </c>
       <c r="R30" t="n">
-        <v>7008217</v>
+        <v>7008193</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3822,19 +3798,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3849,19 +3815,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088364</v>
+        <v>120085506</v>
       </c>
       <c r="B31" t="n">
         <v>90923</v>
@@ -3897,17 +3863,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654153</v>
+        <v>654287</v>
       </c>
       <c r="R31" t="n">
-        <v>7008523</v>
+        <v>7008086</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3934,9 +3900,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3951,22 +3927,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088072</v>
+        <v>120082158</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3975,42 +3951,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654111</v>
+        <v>654220</v>
       </c>
       <c r="R32" t="n">
-        <v>7008487</v>
+        <v>7007891</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4042,7 +4014,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4052,7 +4024,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4079,10 +4051,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120085755</v>
+        <v>120082669</v>
       </c>
       <c r="B33" t="n">
-        <v>57336</v>
+        <v>91902</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4095,39 +4067,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654292</v>
+        <v>654314</v>
       </c>
       <c r="R33" t="n">
-        <v>7008151</v>
+        <v>7007905</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,7 +4126,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4169,7 +4136,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4196,10 +4163,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120086920</v>
+        <v>120088072</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4208,38 +4175,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654164</v>
+        <v>654111</v>
       </c>
       <c r="R34" t="n">
-        <v>7008398</v>
+        <v>7008487</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4271,7 +4242,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4281,12 +4252,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4301,19 +4267,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120088189</v>
+        <v>120085919</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4349,14 +4315,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654128</v>
+        <v>654285</v>
       </c>
       <c r="R35" t="n">
-        <v>7008344</v>
+        <v>7008199</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4388,7 +4354,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4398,7 +4364,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4430,10 +4396,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120082158</v>
+        <v>120085939</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4442,38 +4408,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654220</v>
+        <v>654279</v>
       </c>
       <c r="R36" t="n">
-        <v>7007891</v>
+        <v>7008217</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4505,7 +4471,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4515,7 +4481,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4542,10 +4508,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120087238</v>
+        <v>120088639</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4558,37 +4524,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654193</v>
+        <v>654098</v>
       </c>
       <c r="R37" t="n">
-        <v>7008384</v>
+        <v>7007903</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4615,9 +4581,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4632,22 +4613,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120087250</v>
+        <v>120085695</v>
       </c>
       <c r="B38" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4656,25 +4637,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4684,13 +4665,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654191</v>
+        <v>654200</v>
       </c>
       <c r="R38" t="n">
-        <v>7008385</v>
+        <v>7008363</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4717,9 +4698,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4734,19 +4730,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120085434</v>
+        <v>120088189</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4786,13 +4782,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654217</v>
+        <v>654128</v>
       </c>
       <c r="R39" t="n">
-        <v>7008312</v>
+        <v>7008344</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4821,7 +4817,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4831,12 +4827,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4851,19 +4847,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120085919</v>
+        <v>120085648</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4899,14 +4895,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654285</v>
+        <v>654195</v>
       </c>
       <c r="R40" t="n">
-        <v>7008199</v>
+        <v>7008349</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4938,7 +4934,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4948,12 +4944,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4968,22 +4964,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120085493</v>
+        <v>120086940</v>
       </c>
       <c r="B41" t="n">
-        <v>86895</v>
+        <v>78279</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4996,21 +4992,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>510</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5020,13 +5016,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654196</v>
+        <v>654160</v>
       </c>
       <c r="R41" t="n">
-        <v>7008339</v>
+        <v>7008398</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5053,9 +5049,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5070,22 +5076,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120085757</v>
+        <v>120082434</v>
       </c>
       <c r="B42" t="n">
-        <v>90864</v>
+        <v>91850</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5098,21 +5104,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5122,13 +5128,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654286</v>
+        <v>654303</v>
       </c>
       <c r="R42" t="n">
-        <v>7008186</v>
+        <v>7007918</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5155,9 +5161,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5172,19 +5188,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120082271</v>
+        <v>120081327</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5224,13 +5240,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654150</v>
+        <v>654200</v>
       </c>
       <c r="R43" t="n">
-        <v>7007925</v>
+        <v>7007872</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5257,24 +5273,14 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5289,22 +5295,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120087102</v>
+        <v>120085493</v>
       </c>
       <c r="B44" t="n">
-        <v>97930</v>
+        <v>86895</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5313,50 +5319,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654149</v>
+        <v>654196</v>
       </c>
       <c r="R44" t="n">
-        <v>7008498</v>
+        <v>7008339</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5383,19 +5380,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5410,22 +5397,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120082342</v>
+        <v>120086991</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5434,47 +5421,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654125</v>
+        <v>654156</v>
       </c>
       <c r="R45" t="n">
-        <v>7007981</v>
+        <v>7008421</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5506,7 +5484,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5516,7 +5494,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5543,10 +5526,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120086958</v>
+        <v>120086638</v>
       </c>
       <c r="B46" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5559,21 +5542,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5583,13 +5566,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654151</v>
+        <v>654208</v>
       </c>
       <c r="R46" t="n">
-        <v>7008440</v>
+        <v>7008351</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5616,9 +5599,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5633,22 +5631,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120082329</v>
+        <v>120085706</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5657,25 +5655,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5685,13 +5683,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654290</v>
+        <v>654297</v>
       </c>
       <c r="R47" t="n">
-        <v>7007940</v>
+        <v>7008132</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5718,24 +5716,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5750,22 +5733,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120082934</v>
+        <v>120085755</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5774,38 +5757,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654181</v>
+        <v>654292</v>
       </c>
       <c r="R48" t="n">
-        <v>7007955</v>
+        <v>7008151</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5837,7 +5825,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5847,7 +5835,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5862,22 +5850,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120082434</v>
+        <v>120088184</v>
       </c>
       <c r="B49" t="n">
-        <v>91850</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5890,34 +5878,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654303</v>
+        <v>654118</v>
       </c>
       <c r="R49" t="n">
-        <v>7007918</v>
+        <v>7008347</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5949,7 +5937,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5959,7 +5947,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5974,22 +5967,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120087230</v>
+        <v>120082329</v>
       </c>
       <c r="B50" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6002,37 +5995,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654170</v>
+        <v>654290</v>
       </c>
       <c r="R50" t="n">
-        <v>7008380</v>
+        <v>7007940</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6059,9 +6052,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6076,22 +6084,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120088260</v>
+        <v>120087102</v>
       </c>
       <c r="B51" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6100,38 +6108,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654139</v>
+        <v>654149</v>
       </c>
       <c r="R51" t="n">
-        <v>7008299</v>
+        <v>7008498</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6163,7 +6180,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6173,7 +6190,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6188,22 +6205,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120081327</v>
+        <v>120087230</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6216,34 +6233,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654200</v>
+        <v>654170</v>
       </c>
       <c r="R52" t="n">
-        <v>7007872</v>
+        <v>7008380</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6276,11 +6293,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6307,10 +6319,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120088486</v>
+        <v>120085485</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6323,37 +6335,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654118</v>
+        <v>654276</v>
       </c>
       <c r="R53" t="n">
-        <v>7008045</v>
+        <v>7008093</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6380,24 +6392,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6412,19 +6409,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120085424</v>
+        <v>120087238</v>
       </c>
       <c r="B54" t="n">
         <v>90580</v>
@@ -6460,17 +6457,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654284</v>
+        <v>654193</v>
       </c>
       <c r="R54" t="n">
-        <v>7008101</v>
+        <v>7008384</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6497,19 +6494,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6524,22 +6511,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120085491</v>
+        <v>120082215</v>
       </c>
       <c r="B55" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6548,41 +6535,50 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654200</v>
+        <v>654150</v>
       </c>
       <c r="R55" t="n">
-        <v>7008326</v>
+        <v>7007925</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6611,7 +6607,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6621,12 +6617,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,7 +6761,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120085648</v>
+        <v>120088486</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6806,14 +6797,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654195</v>
+        <v>654118</v>
       </c>
       <c r="R57" t="n">
-        <v>7008349</v>
+        <v>7008045</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6845,7 +6836,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6855,12 +6846,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6887,7 +6878,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120085068</v>
+        <v>120085300</v>
       </c>
       <c r="B58" t="n">
         <v>91023</v>
@@ -6927,13 +6918,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654217</v>
+        <v>654207</v>
       </c>
       <c r="R58" t="n">
-        <v>7008168</v>
+        <v>7008193</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6960,19 +6951,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6987,22 +6968,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120082214</v>
+        <v>120085068</v>
       </c>
       <c r="B59" t="n">
-        <v>57336</v>
+        <v>91023</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7011,25 +6992,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7039,10 +7020,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654279</v>
+        <v>654217</v>
       </c>
       <c r="R59" t="n">
-        <v>7007930</v>
+        <v>7008168</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7074,7 +7055,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7084,12 +7065,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färskt bohål.</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7104,22 +7080,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120086940</v>
+        <v>120082342</v>
       </c>
       <c r="B60" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7128,38 +7104,47 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>654160</v>
+        <v>654125</v>
       </c>
       <c r="R60" t="n">
-        <v>7008398</v>
+        <v>7007981</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7191,7 +7176,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7201,7 +7186,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7228,7 +7213,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120088184</v>
+        <v>120085491</v>
       </c>
       <c r="B61" t="n">
         <v>57320</v>
@@ -7268,13 +7253,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654118</v>
+        <v>654200</v>
       </c>
       <c r="R61" t="n">
-        <v>7008347</v>
+        <v>7008326</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7303,7 +7288,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7313,12 +7298,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7345,7 +7330,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120086991</v>
+        <v>120087568</v>
       </c>
       <c r="B62" t="n">
         <v>57320</v>
@@ -7385,10 +7370,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654156</v>
+        <v>654173</v>
       </c>
       <c r="R62" t="n">
-        <v>7008421</v>
+        <v>7008502</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7420,7 +7405,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7430,12 +7415,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7462,10 +7447,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120085506</v>
+        <v>120087985</v>
       </c>
       <c r="B63" t="n">
-        <v>90923</v>
+        <v>97930</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7478,34 +7463,38 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654287</v>
+        <v>654128</v>
       </c>
       <c r="R63" t="n">
-        <v>7008086</v>
+        <v>7008520</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7537,7 +7526,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7547,7 +7536,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7574,7 +7563,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120087568</v>
+        <v>120085434</v>
       </c>
       <c r="B64" t="n">
         <v>57320</v>
@@ -7614,13 +7603,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654173</v>
+        <v>654217</v>
       </c>
       <c r="R64" t="n">
-        <v>7008502</v>
+        <v>7008312</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7649,7 +7638,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7659,12 +7648,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack på  gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7691,7 +7680,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120086638</v>
+        <v>120082271</v>
       </c>
       <c r="B65" t="n">
         <v>57320</v>
@@ -7727,14 +7716,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654208</v>
+        <v>654150</v>
       </c>
       <c r="R65" t="n">
-        <v>7008351</v>
+        <v>7007925</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7766,7 +7755,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7776,7 +7765,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7808,10 +7797,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120088111</v>
+        <v>120086159</v>
       </c>
       <c r="B66" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7820,38 +7809,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Renudden, Renudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654070</v>
+        <v>654239</v>
       </c>
       <c r="R66" t="n">
-        <v>7008447</v>
+        <v>7008276</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7883,7 +7872,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7893,7 +7882,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7920,7 +7914,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120087288</v>
+        <v>120085759</v>
       </c>
       <c r="B67" t="n">
         <v>90580</v>
@@ -7956,14 +7950,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654159</v>
+        <v>654293</v>
       </c>
       <c r="R67" t="n">
-        <v>7008481</v>
+        <v>7008191</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8022,10 +8016,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120087649</v>
+        <v>120082934</v>
       </c>
       <c r="B68" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8034,45 +8028,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654117</v>
+        <v>654181</v>
       </c>
       <c r="R68" t="n">
-        <v>7008449</v>
+        <v>7007955</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8099,9 +8089,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8116,12 +8116,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -2976,10 +2976,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120087288</v>
+        <v>120088111</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2988,41 +2988,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Renudden, Renudden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654159</v>
+        <v>654070</v>
       </c>
       <c r="R23" t="n">
-        <v>7008481</v>
+        <v>7008447</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3049,9 +3049,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3066,22 +3076,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088111</v>
+        <v>120088260</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3090,38 +3100,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Renudden, Renudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654070</v>
+        <v>654139</v>
       </c>
       <c r="R24" t="n">
-        <v>7008447</v>
+        <v>7008299</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3153,7 +3163,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3163,7 +3173,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3190,10 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088260</v>
+        <v>120087288</v>
       </c>
       <c r="B25" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3206,21 +3216,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3230,13 +3240,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654139</v>
+        <v>654159</v>
       </c>
       <c r="R25" t="n">
-        <v>7008299</v>
+        <v>7008481</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3263,19 +3273,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3290,12 +3290,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120085930</v>
+        <v>120085193</v>
       </c>
       <c r="B28" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3533,25 +3533,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3561,13 +3561,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654269</v>
+        <v>654207</v>
       </c>
       <c r="R28" t="n">
-        <v>7008197</v>
+        <v>7008193</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3611,22 +3611,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120087250</v>
+        <v>120085930</v>
       </c>
       <c r="B29" t="n">
-        <v>90545</v>
+        <v>91023</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3635,38 +3635,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654191</v>
+        <v>654269</v>
       </c>
       <c r="R29" t="n">
-        <v>7008385</v>
+        <v>7008197</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120085193</v>
+        <v>120087250</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3737,41 +3737,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654207</v>
+        <v>654191</v>
       </c>
       <c r="R30" t="n">
-        <v>7008193</v>
+        <v>7008385</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3815,12 +3815,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120086638</v>
+        <v>120082329</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5562,14 +5562,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654208</v>
+        <v>654290</v>
       </c>
       <c r="R46" t="n">
-        <v>7008351</v>
+        <v>7007940</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5631,22 +5631,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120085706</v>
+        <v>120086638</v>
       </c>
       <c r="B47" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5655,41 +5655,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654297</v>
+        <v>654208</v>
       </c>
       <c r="R47" t="n">
-        <v>7008132</v>
+        <v>7008351</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5716,9 +5716,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5733,22 +5748,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120085755</v>
+        <v>120088184</v>
       </c>
       <c r="B48" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5761,16 +5776,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5779,21 +5794,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654292</v>
+        <v>654118</v>
       </c>
       <c r="R48" t="n">
-        <v>7008151</v>
+        <v>7008347</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5825,7 +5835,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5835,7 +5845,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5850,22 +5865,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120088184</v>
+        <v>120087102</v>
       </c>
       <c r="B49" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5874,38 +5889,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654118</v>
+        <v>654149</v>
       </c>
       <c r="R49" t="n">
-        <v>7008347</v>
+        <v>7008498</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5937,7 +5961,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5947,12 +5971,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5979,10 +5998,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120082329</v>
+        <v>120085706</v>
       </c>
       <c r="B50" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5991,25 +6010,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6019,13 +6038,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654290</v>
+        <v>654297</v>
       </c>
       <c r="R50" t="n">
-        <v>7007940</v>
+        <v>7008132</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6052,24 +6071,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6084,22 +6088,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120087102</v>
+        <v>120085755</v>
       </c>
       <c r="B51" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6108,47 +6112,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654149</v>
+        <v>654292</v>
       </c>
       <c r="R51" t="n">
-        <v>7008498</v>
+        <v>7008151</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6205,19 +6205,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120087230</v>
+        <v>120085485</v>
       </c>
       <c r="B52" t="n">
         <v>90864</v>
@@ -6253,14 +6253,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654170</v>
+        <v>654276</v>
       </c>
       <c r="R52" t="n">
-        <v>7008380</v>
+        <v>7008093</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6319,10 +6319,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120085485</v>
+        <v>120087238</v>
       </c>
       <c r="B53" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6335,34 +6335,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654276</v>
+        <v>654193</v>
       </c>
       <c r="R53" t="n">
-        <v>7008093</v>
+        <v>7008384</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6421,10 +6421,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120087238</v>
+        <v>120082215</v>
       </c>
       <c r="B54" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6433,41 +6433,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654193</v>
+        <v>654150</v>
       </c>
       <c r="R54" t="n">
-        <v>7008384</v>
+        <v>7007925</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6494,9 +6503,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6511,22 +6530,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120082215</v>
+        <v>120087230</v>
       </c>
       <c r="B55" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6535,50 +6554,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654150</v>
+        <v>654170</v>
       </c>
       <c r="R55" t="n">
-        <v>7007925</v>
+        <v>7008380</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6605,19 +6615,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6632,12 +6632,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120082214</v>
+        <v>120085434</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2015,16 +2015,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2035,17 +2035,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654279</v>
+        <v>654217</v>
       </c>
       <c r="R14" t="n">
-        <v>7007930</v>
+        <v>7008312</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färskt bohål.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,22 +2104,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120085411</v>
+        <v>120087102</v>
       </c>
       <c r="B15" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,41 +2128,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654207</v>
+        <v>654149</v>
       </c>
       <c r="R15" t="n">
-        <v>7008193</v>
+        <v>7008498</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2189,9 +2198,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,22 +2225,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120085424</v>
+        <v>120085211</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2234,21 +2253,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2258,13 +2277,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654284</v>
+        <v>654207</v>
       </c>
       <c r="R16" t="n">
-        <v>7008101</v>
+        <v>7008193</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2291,19 +2310,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2318,22 +2327,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120086783</v>
+        <v>120087230</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,21 +2355,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,13 +2379,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654209</v>
+        <v>654170</v>
       </c>
       <c r="R17" t="n">
-        <v>7008406</v>
+        <v>7008380</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2403,24 +2412,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,22 +2429,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120087649</v>
+        <v>120086991</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2459,45 +2453,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654117</v>
+        <v>654156</v>
       </c>
       <c r="R18" t="n">
-        <v>7008449</v>
+        <v>7008421</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2524,9 +2514,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2541,22 +2546,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120086958</v>
+        <v>120086940</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>78279</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,21 +2574,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2593,13 +2598,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654151</v>
+        <v>654160</v>
       </c>
       <c r="R19" t="n">
-        <v>7008440</v>
+        <v>7008398</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2626,9 +2631,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2643,22 +2658,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088364</v>
+        <v>120085757</v>
       </c>
       <c r="B20" t="n">
-        <v>90923</v>
+        <v>90864</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2667,41 +2682,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654153</v>
+        <v>654286</v>
       </c>
       <c r="R20" t="n">
-        <v>7008523</v>
+        <v>7008186</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2745,22 +2760,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120085468</v>
+        <v>120088111</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2773,37 +2788,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Renudden, Renudden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654268</v>
+        <v>654070</v>
       </c>
       <c r="R21" t="n">
-        <v>7008096</v>
+        <v>7008447</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2830,9 +2845,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2847,22 +2872,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120086920</v>
+        <v>120088260</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2875,21 +2900,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2899,10 +2924,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654164</v>
+        <v>654139</v>
       </c>
       <c r="R22" t="n">
-        <v>7008398</v>
+        <v>7008299</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,7 +2959,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2944,12 +2969,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2964,22 +2984,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088111</v>
+        <v>120087288</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2988,41 +3008,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Renudden, Renudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654070</v>
+        <v>654159</v>
       </c>
       <c r="R23" t="n">
-        <v>7008447</v>
+        <v>7008481</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3049,19 +3069,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3076,22 +3086,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088260</v>
+        <v>120085939</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3104,34 +3114,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654139</v>
+        <v>654279</v>
       </c>
       <c r="R24" t="n">
-        <v>7008299</v>
+        <v>7008217</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3163,7 +3173,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3173,7 +3183,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3200,10 +3210,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120087288</v>
+        <v>120085485</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3216,34 +3226,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654159</v>
+        <v>654276</v>
       </c>
       <c r="R25" t="n">
-        <v>7008481</v>
+        <v>7008093</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3302,10 +3312,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120085757</v>
+        <v>120085468</v>
       </c>
       <c r="B26" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3314,25 +3324,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3342,10 +3352,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654286</v>
+        <v>654268</v>
       </c>
       <c r="R26" t="n">
-        <v>7008186</v>
+        <v>7008096</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3404,7 +3414,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088520</v>
+        <v>120086920</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3440,14 +3450,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654121</v>
+        <v>654164</v>
       </c>
       <c r="R27" t="n">
-        <v>7008041</v>
+        <v>7008398</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3479,7 +3489,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3489,12 +3499,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3509,22 +3519,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120085193</v>
+        <v>120086159</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3537,37 +3547,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654207</v>
+        <v>654239</v>
       </c>
       <c r="R28" t="n">
-        <v>7008193</v>
+        <v>7008276</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3594,9 +3604,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3611,22 +3636,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120085930</v>
+        <v>120088261</v>
       </c>
       <c r="B29" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3635,41 +3660,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäsviken, Svartnäsviken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654269</v>
+        <v>654154</v>
       </c>
       <c r="R29" t="n">
-        <v>7008197</v>
+        <v>7008250</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3696,9 +3721,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3713,22 +3753,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120087250</v>
+        <v>120088364</v>
       </c>
       <c r="B30" t="n">
-        <v>90545</v>
+        <v>90923</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3737,25 +3777,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3765,13 +3805,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654191</v>
+        <v>654153</v>
       </c>
       <c r="R30" t="n">
-        <v>7008385</v>
+        <v>7008523</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3815,22 +3855,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120085506</v>
+        <v>120088486</v>
       </c>
       <c r="B31" t="n">
-        <v>90923</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3839,38 +3879,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654287</v>
+        <v>654118</v>
       </c>
       <c r="R31" t="n">
-        <v>7008086</v>
+        <v>7008045</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3902,7 +3942,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3912,7 +3952,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3927,22 +3972,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120082158</v>
+        <v>120082329</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3951,38 +3996,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654220</v>
+        <v>654290</v>
       </c>
       <c r="R32" t="n">
-        <v>7007891</v>
+        <v>7007940</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4014,7 +4059,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4024,7 +4069,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4051,10 +4101,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120082669</v>
+        <v>120088520</v>
       </c>
       <c r="B33" t="n">
-        <v>91902</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4067,34 +4117,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654314</v>
+        <v>654121</v>
       </c>
       <c r="R33" t="n">
-        <v>7007905</v>
+        <v>7008041</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,7 +4176,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4136,7 +4186,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4163,10 +4218,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120088072</v>
+        <v>120085648</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4175,42 +4230,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654111</v>
+        <v>654195</v>
       </c>
       <c r="R34" t="n">
-        <v>7008487</v>
+        <v>7008349</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4242,7 +4293,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4252,7 +4303,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4267,19 +4323,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120085919</v>
+        <v>120086638</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4315,14 +4371,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654285</v>
+        <v>654208</v>
       </c>
       <c r="R35" t="n">
-        <v>7008199</v>
+        <v>7008351</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4354,7 +4410,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4364,12 +4420,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4384,19 +4440,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120085939</v>
+        <v>120086958</v>
       </c>
       <c r="B36" t="n">
         <v>90580</v>
@@ -4432,17 +4488,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654279</v>
+        <v>654151</v>
       </c>
       <c r="R36" t="n">
-        <v>7008217</v>
+        <v>7008440</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4469,19 +4525,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4496,22 +4542,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120088639</v>
+        <v>120085755</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4524,16 +4570,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4542,16 +4588,21 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654098</v>
+        <v>654292</v>
       </c>
       <c r="R37" t="n">
-        <v>7007903</v>
+        <v>7008151</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4583,7 +4634,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4593,12 +4644,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4613,22 +4659,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120085695</v>
+        <v>120085930</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4637,41 +4683,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654200</v>
+        <v>654269</v>
       </c>
       <c r="R38" t="n">
-        <v>7008363</v>
+        <v>7008197</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4698,24 +4744,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4730,19 +4761,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120088189</v>
+        <v>120087568</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4782,10 +4813,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654128</v>
+        <v>654173</v>
       </c>
       <c r="R39" t="n">
-        <v>7008344</v>
+        <v>7008502</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4817,7 +4848,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4827,12 +4858,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4847,22 +4878,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120085648</v>
+        <v>120085193</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4875,37 +4906,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654195</v>
+        <v>654207</v>
       </c>
       <c r="R40" t="n">
-        <v>7008349</v>
+        <v>7008193</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4932,24 +4963,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4964,22 +4980,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120086940</v>
+        <v>120082214</v>
       </c>
       <c r="B41" t="n">
-        <v>78279</v>
+        <v>57336</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4992,34 +5008,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654160</v>
+        <v>654279</v>
       </c>
       <c r="R41" t="n">
-        <v>7008398</v>
+        <v>7007930</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5051,7 +5067,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5061,7 +5077,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5076,22 +5097,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120082434</v>
+        <v>120085424</v>
       </c>
       <c r="B42" t="n">
-        <v>91850</v>
+        <v>90580</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5104,21 +5125,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5128,10 +5149,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654303</v>
+        <v>654284</v>
       </c>
       <c r="R42" t="n">
-        <v>7007918</v>
+        <v>7008101</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5163,7 +5184,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5173,7 +5194,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5200,7 +5221,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120081327</v>
+        <v>120085695</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5236,17 +5257,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
         <v>654200</v>
       </c>
       <c r="R43" t="n">
-        <v>7007872</v>
+        <v>7008363</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5273,14 +5294,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5295,22 +5326,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120085493</v>
+        <v>120085759</v>
       </c>
       <c r="B44" t="n">
-        <v>86895</v>
+        <v>90580</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5323,37 +5354,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654196</v>
+        <v>654293</v>
       </c>
       <c r="R44" t="n">
-        <v>7008339</v>
+        <v>7008191</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,22 +5428,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120086991</v>
+        <v>120082669</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>91902</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5425,34 +5456,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654156</v>
+        <v>654314</v>
       </c>
       <c r="R45" t="n">
-        <v>7008421</v>
+        <v>7007905</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5484,7 +5515,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5494,12 +5525,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5514,19 +5540,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120082329</v>
+        <v>120088639</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5562,14 +5588,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654290</v>
+        <v>654098</v>
       </c>
       <c r="R46" t="n">
-        <v>7007940</v>
+        <v>7007903</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5601,7 +5627,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5611,12 +5637,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5631,19 +5657,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120086638</v>
+        <v>120086783</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -5683,10 +5709,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654208</v>
+        <v>654209</v>
       </c>
       <c r="R47" t="n">
-        <v>7008351</v>
+        <v>7008406</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5718,7 +5744,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5728,12 +5754,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5748,22 +5774,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120088184</v>
+        <v>120085300</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5772,41 +5798,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654118</v>
+        <v>654207</v>
       </c>
       <c r="R48" t="n">
-        <v>7008347</v>
+        <v>7008193</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5833,24 +5859,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5865,22 +5876,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120087102</v>
+        <v>120081327</v>
       </c>
       <c r="B49" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5889,50 +5900,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654149</v>
+        <v>654200</v>
       </c>
       <c r="R49" t="n">
-        <v>7008498</v>
+        <v>7007872</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5959,19 +5961,14 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:19</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5986,22 +5983,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120085706</v>
+        <v>120085919</v>
       </c>
       <c r="B50" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6010,25 +6007,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6038,13 +6035,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654297</v>
+        <v>654285</v>
       </c>
       <c r="R50" t="n">
-        <v>7008132</v>
+        <v>7008199</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6071,9 +6068,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6088,22 +6100,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120085755</v>
+        <v>120082434</v>
       </c>
       <c r="B51" t="n">
-        <v>57336</v>
+        <v>91850</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6116,39 +6128,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654292</v>
+        <v>654303</v>
       </c>
       <c r="R51" t="n">
-        <v>7008151</v>
+        <v>7007918</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6180,7 +6187,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6190,7 +6197,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6217,10 +6224,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120085485</v>
+        <v>120085506</v>
       </c>
       <c r="B52" t="n">
-        <v>90864</v>
+        <v>90923</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6229,25 +6236,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6257,13 +6264,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654276</v>
+        <v>654287</v>
       </c>
       <c r="R52" t="n">
-        <v>7008093</v>
+        <v>7008086</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6290,9 +6297,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6307,22 +6324,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120087238</v>
+        <v>120085706</v>
       </c>
       <c r="B53" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6331,38 +6348,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654193</v>
+        <v>654297</v>
       </c>
       <c r="R53" t="n">
-        <v>7008384</v>
+        <v>7008132</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6421,10 +6438,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120082215</v>
+        <v>120087238</v>
       </c>
       <c r="B54" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6433,50 +6450,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654150</v>
+        <v>654193</v>
       </c>
       <c r="R54" t="n">
-        <v>7007925</v>
+        <v>7008384</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6503,19 +6511,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6530,22 +6528,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120087230</v>
+        <v>120082934</v>
       </c>
       <c r="B55" t="n">
-        <v>90864</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6554,41 +6552,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654170</v>
+        <v>654181</v>
       </c>
       <c r="R55" t="n">
-        <v>7008380</v>
+        <v>7007955</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6615,9 +6613,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6632,22 +6640,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120088261</v>
+        <v>120087649</v>
       </c>
       <c r="B56" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6656,41 +6664,45 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svartnäsviken, Svartnäsviken, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654154</v>
+        <v>654117</v>
       </c>
       <c r="R56" t="n">
-        <v>7008250</v>
+        <v>7008449</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6717,24 +6729,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6749,22 +6746,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120088486</v>
+        <v>120085493</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>86895</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6777,37 +6774,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654118</v>
+        <v>654196</v>
       </c>
       <c r="R57" t="n">
-        <v>7008045</v>
+        <v>7008339</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6834,24 +6831,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6866,22 +6848,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120085300</v>
+        <v>120087250</v>
       </c>
       <c r="B58" t="n">
-        <v>91023</v>
+        <v>90545</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6890,41 +6872,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654207</v>
+        <v>654191</v>
       </c>
       <c r="R58" t="n">
-        <v>7008193</v>
+        <v>7008385</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6968,22 +6950,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120085068</v>
+        <v>120087985</v>
       </c>
       <c r="B59" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6996,34 +6978,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654217</v>
+        <v>654128</v>
       </c>
       <c r="R59" t="n">
-        <v>7008168</v>
+        <v>7008520</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7055,7 +7041,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7065,7 +7051,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7080,22 +7066,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120082342</v>
+        <v>120085068</v>
       </c>
       <c r="B60" t="n">
-        <v>97930</v>
+        <v>91023</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7108,43 +7094,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>654125</v>
+        <v>654217</v>
       </c>
       <c r="R60" t="n">
-        <v>7007981</v>
+        <v>7008168</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7176,7 +7153,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7186,7 +7163,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7213,10 +7190,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120085491</v>
+        <v>120082158</v>
       </c>
       <c r="B61" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7225,41 +7202,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654200</v>
+        <v>654220</v>
       </c>
       <c r="R61" t="n">
-        <v>7008326</v>
+        <v>7007891</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7288,7 +7265,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7298,12 +7275,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7318,19 +7290,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120087568</v>
+        <v>120088184</v>
       </c>
       <c r="B62" t="n">
         <v>57320</v>
@@ -7370,10 +7342,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654173</v>
+        <v>654118</v>
       </c>
       <c r="R62" t="n">
-        <v>7008502</v>
+        <v>7008347</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7405,7 +7377,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7415,12 +7387,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack på  gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7447,10 +7419,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120087985</v>
+        <v>120088189</v>
       </c>
       <c r="B63" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7459,32 +7431,28 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
@@ -7494,7 +7462,7 @@
         <v>654128</v>
       </c>
       <c r="R63" t="n">
-        <v>7008520</v>
+        <v>7008344</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7526,7 +7494,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7536,7 +7504,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7563,10 +7536,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120085434</v>
+        <v>120088072</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7575,41 +7548,45 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654217</v>
+        <v>654111</v>
       </c>
       <c r="R64" t="n">
-        <v>7008312</v>
+        <v>7008487</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7638,7 +7615,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7648,12 +7625,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7668,19 +7640,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120082271</v>
+        <v>120085491</v>
       </c>
       <c r="B65" t="n">
         <v>57320</v>
@@ -7716,17 +7688,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654150</v>
+        <v>654200</v>
       </c>
       <c r="R65" t="n">
-        <v>7007925</v>
+        <v>7008326</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7755,7 +7727,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7765,7 +7737,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7797,7 +7769,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120086159</v>
+        <v>120082271</v>
       </c>
       <c r="B66" t="n">
         <v>57320</v>
@@ -7833,14 +7805,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654239</v>
+        <v>654150</v>
       </c>
       <c r="R66" t="n">
-        <v>7008276</v>
+        <v>7007925</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7872,7 +7844,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7882,12 +7854,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7902,22 +7874,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120085759</v>
+        <v>120082342</v>
       </c>
       <c r="B67" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7926,41 +7898,50 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654293</v>
+        <v>654125</v>
       </c>
       <c r="R67" t="n">
-        <v>7008191</v>
+        <v>7007981</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7987,9 +7968,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8004,22 +7995,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120082934</v>
+        <v>120082215</v>
       </c>
       <c r="B68" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8028,38 +8019,47 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654181</v>
+        <v>654150</v>
       </c>
       <c r="R68" t="n">
-        <v>7007955</v>
+        <v>7007925</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -3765,10 +3765,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088364</v>
+        <v>120088486</v>
       </c>
       <c r="B30" t="n">
-        <v>90923</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3777,41 +3777,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654153</v>
+        <v>654118</v>
       </c>
       <c r="R30" t="n">
-        <v>7008523</v>
+        <v>7008045</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3838,9 +3838,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3855,19 +3870,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088486</v>
+        <v>120082329</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3903,14 +3918,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654118</v>
+        <v>654290</v>
       </c>
       <c r="R31" t="n">
-        <v>7008045</v>
+        <v>7007940</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3942,7 +3957,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3952,12 +3967,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3972,22 +3987,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120082329</v>
+        <v>120088364</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>90923</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3996,41 +4011,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654290</v>
+        <v>654153</v>
       </c>
       <c r="R32" t="n">
-        <v>7007940</v>
+        <v>7008523</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4057,24 +4072,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4089,22 +4089,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088520</v>
+        <v>120086958</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4117,37 +4117,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654121</v>
+        <v>654151</v>
       </c>
       <c r="R33" t="n">
-        <v>7008041</v>
+        <v>7008440</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4174,24 +4174,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4206,22 +4191,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120085648</v>
+        <v>120085755</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4234,16 +4219,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4252,16 +4237,21 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654195</v>
+        <v>654292</v>
       </c>
       <c r="R34" t="n">
-        <v>7008349</v>
+        <v>7008151</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4293,7 +4283,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4303,12 +4293,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4323,19 +4308,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120086638</v>
+        <v>120088520</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4371,14 +4356,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654208</v>
+        <v>654121</v>
       </c>
       <c r="R35" t="n">
-        <v>7008351</v>
+        <v>7008041</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4410,7 +4395,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4420,12 +4405,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4440,22 +4425,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120086958</v>
+        <v>120085648</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4468,21 +4453,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4492,13 +4477,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654151</v>
+        <v>654195</v>
       </c>
       <c r="R36" t="n">
-        <v>7008440</v>
+        <v>7008349</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4525,9 +4510,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4542,22 +4542,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120085755</v>
+        <v>120086638</v>
       </c>
       <c r="B37" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4570,16 +4570,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4588,21 +4588,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654292</v>
+        <v>654208</v>
       </c>
       <c r="R37" t="n">
-        <v>7008151</v>
+        <v>7008351</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4634,7 +4629,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4644,7 +4639,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4659,12 +4659,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -6112,10 +6112,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120082434</v>
+        <v>120087238</v>
       </c>
       <c r="B51" t="n">
-        <v>91850</v>
+        <v>90580</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6128,37 +6128,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654303</v>
+        <v>654193</v>
       </c>
       <c r="R51" t="n">
-        <v>7007918</v>
+        <v>7008384</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6185,19 +6185,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6212,12 +6202,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6438,10 +6428,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120087238</v>
+        <v>120082934</v>
       </c>
       <c r="B54" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6450,41 +6440,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654193</v>
+        <v>654181</v>
       </c>
       <c r="R54" t="n">
-        <v>7008384</v>
+        <v>7007955</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6511,9 +6501,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6528,22 +6528,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120082934</v>
+        <v>120082434</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6552,38 +6552,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654181</v>
+        <v>654303</v>
       </c>
       <c r="R55" t="n">
-        <v>7007955</v>
+        <v>7007918</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6640,12 +6640,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7536,10 +7536,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120088072</v>
+        <v>120085491</v>
       </c>
       <c r="B64" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7548,45 +7548,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654111</v>
+        <v>654200</v>
       </c>
       <c r="R64" t="n">
-        <v>7008487</v>
+        <v>7008326</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7615,7 +7611,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7625,7 +7621,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7640,19 +7641,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120085491</v>
+        <v>120082271</v>
       </c>
       <c r="B65" t="n">
         <v>57320</v>
@@ -7688,17 +7689,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654200</v>
+        <v>654150</v>
       </c>
       <c r="R65" t="n">
-        <v>7008326</v>
+        <v>7007925</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7727,7 +7728,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7737,7 +7738,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7769,10 +7770,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120082271</v>
+        <v>120082342</v>
       </c>
       <c r="B66" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7781,38 +7782,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654150</v>
+        <v>654125</v>
       </c>
       <c r="R66" t="n">
-        <v>7007925</v>
+        <v>7007981</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7844,7 +7854,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7854,12 +7864,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7886,7 +7891,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120082342</v>
+        <v>120082215</v>
       </c>
       <c r="B67" t="n">
         <v>97930</v>
@@ -7921,12 +7926,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7935,10 +7940,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654125</v>
+        <v>654150</v>
       </c>
       <c r="R67" t="n">
-        <v>7007981</v>
+        <v>7007925</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7970,7 +7975,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7980,7 +7985,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8007,7 +8012,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120082215</v>
+        <v>120088072</v>
       </c>
       <c r="B68" t="n">
         <v>97930</v>
@@ -8042,24 +8047,19 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654150</v>
+        <v>654111</v>
       </c>
       <c r="R68" t="n">
-        <v>7007925</v>
+        <v>7008487</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8116,12 +8116,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120085434</v>
+        <v>120087250</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,25 +2011,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654217</v>
+        <v>654191</v>
       </c>
       <c r="R14" t="n">
-        <v>7008312</v>
+        <v>7008385</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,24 +2072,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,22 +2089,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120087102</v>
+        <v>120087230</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,50 +2113,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654149</v>
+        <v>654170</v>
       </c>
       <c r="R15" t="n">
-        <v>7008498</v>
+        <v>7008380</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,19 +2174,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,22 +2191,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120085211</v>
+        <v>120085424</v>
       </c>
       <c r="B16" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,21 +2219,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,13 +2243,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654207</v>
+        <v>654284</v>
       </c>
       <c r="R16" t="n">
-        <v>7008193</v>
+        <v>7008101</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2310,9 +2276,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2327,22 +2303,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120087230</v>
+        <v>120085506</v>
       </c>
       <c r="B17" t="n">
-        <v>90864</v>
+        <v>90923</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2351,41 +2327,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654170</v>
+        <v>654287</v>
       </c>
       <c r="R17" t="n">
-        <v>7008380</v>
+        <v>7008086</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2412,9 +2388,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2429,19 +2415,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120086991</v>
+        <v>120086159</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2481,10 +2467,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654156</v>
+        <v>654239</v>
       </c>
       <c r="R18" t="n">
-        <v>7008421</v>
+        <v>7008276</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2516,7 +2502,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2526,12 +2512,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2546,22 +2532,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120086940</v>
+        <v>120085491</v>
       </c>
       <c r="B19" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2574,21 +2560,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2598,13 +2584,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654160</v>
+        <v>654200</v>
       </c>
       <c r="R19" t="n">
-        <v>7008398</v>
+        <v>7008326</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2633,7 +2619,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2643,7 +2629,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2670,10 +2661,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120085757</v>
+        <v>120088184</v>
       </c>
       <c r="B20" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,37 +2677,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654286</v>
+        <v>654118</v>
       </c>
       <c r="R20" t="n">
-        <v>7008186</v>
+        <v>7008347</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,9 +2734,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,22 +2766,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088111</v>
+        <v>120087102</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2784,38 +2790,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Renudden, Renudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654070</v>
+        <v>654149</v>
       </c>
       <c r="R21" t="n">
-        <v>7008447</v>
+        <v>7008498</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,7 +2862,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2857,7 +2872,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2872,22 +2887,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088260</v>
+        <v>120088364</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>90923</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2896,25 +2911,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2924,13 +2939,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654139</v>
+        <v>654153</v>
       </c>
       <c r="R22" t="n">
-        <v>7008299</v>
+        <v>7008523</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2957,19 +2972,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,22 +2989,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120087288</v>
+        <v>120086991</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3012,21 +3017,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3036,13 +3041,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654159</v>
+        <v>654156</v>
       </c>
       <c r="R23" t="n">
-        <v>7008481</v>
+        <v>7008421</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3069,9 +3074,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3086,22 +3106,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120085939</v>
+        <v>120085434</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3114,37 +3134,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654279</v>
+        <v>654217</v>
       </c>
       <c r="R24" t="n">
-        <v>7008217</v>
+        <v>7008312</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3173,7 +3193,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3183,7 +3203,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3198,22 +3223,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120085485</v>
+        <v>120085193</v>
       </c>
       <c r="B25" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3226,21 +3251,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3250,13 +3275,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654276</v>
+        <v>654207</v>
       </c>
       <c r="R25" t="n">
-        <v>7008093</v>
+        <v>7008193</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3300,22 +3325,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120085468</v>
+        <v>120082214</v>
       </c>
       <c r="B26" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3324,25 +3349,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3352,13 +3377,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654268</v>
+        <v>654279</v>
       </c>
       <c r="R26" t="n">
-        <v>7008096</v>
+        <v>7007930</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3385,9 +3410,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3402,19 +3442,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120086920</v>
+        <v>120088520</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3450,14 +3490,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654164</v>
+        <v>654121</v>
       </c>
       <c r="R27" t="n">
-        <v>7008398</v>
+        <v>7008041</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3489,7 +3529,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3499,12 +3539,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3519,22 +3559,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120086159</v>
+        <v>120085706</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3543,41 +3583,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654239</v>
+        <v>654297</v>
       </c>
       <c r="R28" t="n">
-        <v>7008276</v>
+        <v>7008132</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3604,24 +3644,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3636,22 +3661,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088261</v>
+        <v>120087288</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3664,37 +3689,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svartnäsviken, Svartnäsviken, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654154</v>
+        <v>654159</v>
       </c>
       <c r="R29" t="n">
-        <v>7008250</v>
+        <v>7008481</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3721,24 +3746,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,22 +3763,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088486</v>
+        <v>120082158</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3777,25 +3787,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3805,10 +3815,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654118</v>
+        <v>654220</v>
       </c>
       <c r="R30" t="n">
-        <v>7008045</v>
+        <v>7007891</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,7 +3850,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3850,12 +3860,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3870,19 +3875,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120082329</v>
+        <v>120085695</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3918,14 +3923,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654290</v>
+        <v>654200</v>
       </c>
       <c r="R31" t="n">
-        <v>7007940</v>
+        <v>7008363</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3957,7 +3962,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3967,12 +3972,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3987,22 +3992,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088364</v>
+        <v>120085300</v>
       </c>
       <c r="B32" t="n">
-        <v>90923</v>
+        <v>91023</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4015,34 +4020,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654153</v>
+        <v>654207</v>
       </c>
       <c r="R32" t="n">
-        <v>7008523</v>
+        <v>7008193</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4203,10 +4208,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120085755</v>
+        <v>120086783</v>
       </c>
       <c r="B34" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4219,16 +4224,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4237,21 +4242,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654292</v>
+        <v>654209</v>
       </c>
       <c r="R34" t="n">
-        <v>7008151</v>
+        <v>7008406</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4293,7 +4293,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4320,10 +4325,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120088520</v>
+        <v>120085755</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4336,16 +4341,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4354,16 +4359,21 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654121</v>
+        <v>654292</v>
       </c>
       <c r="R35" t="n">
-        <v>7008041</v>
+        <v>7008151</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4395,7 +4405,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4405,12 +4415,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4437,10 +4442,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120085648</v>
+        <v>120087649</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4449,41 +4454,45 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654195</v>
+        <v>654117</v>
       </c>
       <c r="R36" t="n">
-        <v>7008349</v>
+        <v>7008449</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4510,24 +4519,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4542,22 +4536,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120086638</v>
+        <v>120088260</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4570,21 +4564,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4594,10 +4588,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654208</v>
+        <v>654139</v>
       </c>
       <c r="R37" t="n">
-        <v>7008351</v>
+        <v>7008299</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4629,7 +4623,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4639,12 +4633,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4659,22 +4648,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120085930</v>
+        <v>120086920</v>
       </c>
       <c r="B38" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4683,41 +4672,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654269</v>
+        <v>654164</v>
       </c>
       <c r="R38" t="n">
-        <v>7008197</v>
+        <v>7008398</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4744,9 +4733,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4761,22 +4765,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120087568</v>
+        <v>120082215</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4785,38 +4789,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654173</v>
+        <v>654150</v>
       </c>
       <c r="R39" t="n">
-        <v>7008502</v>
+        <v>7007925</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4848,7 +4861,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4858,12 +4871,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på  gran</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4890,10 +4898,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120085193</v>
+        <v>120085211</v>
       </c>
       <c r="B40" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4906,21 +4914,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4992,10 +5000,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120082214</v>
+        <v>120082329</v>
       </c>
       <c r="B41" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5008,16 +5016,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5032,10 +5040,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654279</v>
+        <v>654290</v>
       </c>
       <c r="R41" t="n">
-        <v>7007930</v>
+        <v>7007940</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5067,7 +5075,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5077,12 +5085,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färskt bohål.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5109,10 +5117,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120085424</v>
+        <v>120088486</v>
       </c>
       <c r="B42" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5125,34 +5133,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654284</v>
+        <v>654118</v>
       </c>
       <c r="R42" t="n">
-        <v>7008101</v>
+        <v>7008045</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5184,7 +5192,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5194,7 +5202,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5209,22 +5222,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120085695</v>
+        <v>120082934</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5233,38 +5246,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654200</v>
+        <v>654181</v>
       </c>
       <c r="R43" t="n">
-        <v>7008363</v>
+        <v>7007955</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5296,7 +5309,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5306,12 +5319,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5338,10 +5346,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120085759</v>
+        <v>120088189</v>
       </c>
       <c r="B44" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5354,37 +5362,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654293</v>
+        <v>654128</v>
       </c>
       <c r="R44" t="n">
-        <v>7008191</v>
+        <v>7008344</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5411,9 +5419,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5428,22 +5451,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120082669</v>
+        <v>120088639</v>
       </c>
       <c r="B45" t="n">
-        <v>91902</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5456,34 +5479,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654314</v>
+        <v>654098</v>
       </c>
       <c r="R45" t="n">
-        <v>7007905</v>
+        <v>7007903</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5515,7 +5538,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5525,7 +5548,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5540,19 +5568,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120088639</v>
+        <v>120088261</v>
       </c>
       <c r="B46" t="n">
         <v>57320</v>
@@ -5588,14 +5616,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsviken, Svartnäsviken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654098</v>
+        <v>654154</v>
       </c>
       <c r="R46" t="n">
-        <v>7007903</v>
+        <v>7008250</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5627,7 +5655,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5637,7 +5665,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5669,10 +5697,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120086783</v>
+        <v>120088072</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5681,38 +5709,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654209</v>
+        <v>654111</v>
       </c>
       <c r="R47" t="n">
-        <v>7008406</v>
+        <v>7008487</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5744,7 +5776,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5754,12 +5786,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5786,10 +5813,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120085300</v>
+        <v>120088111</v>
       </c>
       <c r="B48" t="n">
-        <v>91023</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5798,41 +5825,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Renudden, Renudden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654207</v>
+        <v>654070</v>
       </c>
       <c r="R48" t="n">
-        <v>7008193</v>
+        <v>7008447</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5859,9 +5886,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5876,12 +5913,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5995,10 +6032,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120085919</v>
+        <v>120086940</v>
       </c>
       <c r="B50" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6011,34 +6048,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654285</v>
+        <v>654160</v>
       </c>
       <c r="R50" t="n">
-        <v>7008199</v>
+        <v>7008398</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6070,7 +6107,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6080,12 +6117,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6100,22 +6132,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120087238</v>
+        <v>120085757</v>
       </c>
       <c r="B51" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6128,34 +6160,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654193</v>
+        <v>654286</v>
       </c>
       <c r="R51" t="n">
-        <v>7008384</v>
+        <v>7008186</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6214,10 +6246,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120085506</v>
+        <v>120085939</v>
       </c>
       <c r="B52" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6226,25 +6258,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6254,10 +6286,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654287</v>
+        <v>654279</v>
       </c>
       <c r="R52" t="n">
-        <v>7008086</v>
+        <v>7008217</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6289,7 +6321,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6299,7 +6331,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6326,10 +6358,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120085706</v>
+        <v>120082342</v>
       </c>
       <c r="B53" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6338,41 +6370,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654297</v>
+        <v>654125</v>
       </c>
       <c r="R53" t="n">
-        <v>7008132</v>
+        <v>7007981</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6399,9 +6440,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6416,22 +6467,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120082934</v>
+        <v>120085468</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6444,37 +6495,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654181</v>
+        <v>654268</v>
       </c>
       <c r="R54" t="n">
-        <v>7007955</v>
+        <v>7008096</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6501,19 +6552,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6528,22 +6569,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120082434</v>
+        <v>120085493</v>
       </c>
       <c r="B55" t="n">
-        <v>91850</v>
+        <v>86895</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6556,37 +6597,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>510</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654303</v>
+        <v>654196</v>
       </c>
       <c r="R55" t="n">
-        <v>7007918</v>
+        <v>7008339</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6613,19 +6654,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6640,22 +6671,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120087649</v>
+        <v>120085068</v>
       </c>
       <c r="B56" t="n">
-        <v>97930</v>
+        <v>91023</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6668,41 +6699,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654117</v>
+        <v>654217</v>
       </c>
       <c r="R56" t="n">
-        <v>7008449</v>
+        <v>7008168</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6729,9 +6756,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6746,22 +6783,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120085493</v>
+        <v>120085930</v>
       </c>
       <c r="B57" t="n">
-        <v>86895</v>
+        <v>91023</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6770,41 +6807,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>510</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654196</v>
+        <v>654269</v>
       </c>
       <c r="R57" t="n">
-        <v>7008339</v>
+        <v>7008197</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6848,22 +6885,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120087250</v>
+        <v>120085919</v>
       </c>
       <c r="B58" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6872,41 +6909,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654191</v>
+        <v>654285</v>
       </c>
       <c r="R58" t="n">
-        <v>7008385</v>
+        <v>7008199</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6933,9 +6970,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6950,22 +7002,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120087985</v>
+        <v>120082271</v>
       </c>
       <c r="B59" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6974,42 +7026,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654128</v>
+        <v>654150</v>
       </c>
       <c r="R59" t="n">
-        <v>7008520</v>
+        <v>7007925</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7041,7 +7089,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7051,7 +7099,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7066,22 +7119,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120085068</v>
+        <v>120087985</v>
       </c>
       <c r="B60" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7094,34 +7147,38 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>654217</v>
+        <v>654128</v>
       </c>
       <c r="R60" t="n">
-        <v>7008168</v>
+        <v>7008520</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7153,7 +7210,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7163,7 +7220,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7178,22 +7235,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120082158</v>
+        <v>120086638</v>
       </c>
       <c r="B61" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7202,38 +7259,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654220</v>
+        <v>654208</v>
       </c>
       <c r="R61" t="n">
-        <v>7007891</v>
+        <v>7008351</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7265,7 +7322,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7275,7 +7332,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7290,22 +7352,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120088184</v>
+        <v>120082434</v>
       </c>
       <c r="B62" t="n">
-        <v>57320</v>
+        <v>91850</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7318,34 +7380,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654118</v>
+        <v>654303</v>
       </c>
       <c r="R62" t="n">
-        <v>7008347</v>
+        <v>7007918</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7377,7 +7439,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7387,12 +7449,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7407,19 +7464,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120088189</v>
+        <v>120085648</v>
       </c>
       <c r="B63" t="n">
         <v>57320</v>
@@ -7459,10 +7516,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654128</v>
+        <v>654195</v>
       </c>
       <c r="R63" t="n">
-        <v>7008344</v>
+        <v>7008349</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7494,7 +7551,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7504,12 +7561,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7524,22 +7581,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120085491</v>
+        <v>120087238</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7552,21 +7609,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7576,13 +7633,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654200</v>
+        <v>654193</v>
       </c>
       <c r="R64" t="n">
-        <v>7008326</v>
+        <v>7008384</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7609,24 +7666,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7641,22 +7683,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120082271</v>
+        <v>120082669</v>
       </c>
       <c r="B65" t="n">
-        <v>57320</v>
+        <v>91902</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7669,34 +7711,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654150</v>
+        <v>654314</v>
       </c>
       <c r="R65" t="n">
-        <v>7007925</v>
+        <v>7007905</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7728,7 +7770,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7738,12 +7780,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7758,22 +7795,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120082342</v>
+        <v>120087568</v>
       </c>
       <c r="B66" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7782,47 +7819,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654125</v>
+        <v>654173</v>
       </c>
       <c r="R66" t="n">
-        <v>7007981</v>
+        <v>7008502</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7854,7 +7882,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7864,7 +7892,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7891,10 +7924,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120082215</v>
+        <v>120085759</v>
       </c>
       <c r="B67" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7903,50 +7936,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654150</v>
+        <v>654293</v>
       </c>
       <c r="R67" t="n">
-        <v>7007925</v>
+        <v>7008191</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7973,19 +7997,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8000,22 +8014,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120088072</v>
+        <v>120085485</v>
       </c>
       <c r="B68" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8024,45 +8038,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654111</v>
+        <v>654276</v>
       </c>
       <c r="R68" t="n">
-        <v>7008487</v>
+        <v>7008093</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8089,19 +8099,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>16:01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8116,12 +8116,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120087250</v>
+        <v>120085434</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,25 +2011,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654191</v>
+        <v>654217</v>
       </c>
       <c r="R14" t="n">
-        <v>7008385</v>
+        <v>7008312</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,9 +2072,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,22 +2104,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120087230</v>
+        <v>120087985</v>
       </c>
       <c r="B15" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,41 +2128,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654170</v>
+        <v>654128</v>
       </c>
       <c r="R15" t="n">
-        <v>7008380</v>
+        <v>7008520</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2174,9 +2193,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,22 +2220,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120085424</v>
+        <v>120087250</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2215,41 +2244,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654284</v>
+        <v>654191</v>
       </c>
       <c r="R16" t="n">
-        <v>7008101</v>
+        <v>7008385</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2276,19 +2305,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,22 +2322,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120085506</v>
+        <v>120085939</v>
       </c>
       <c r="B17" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2327,25 +2346,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2355,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654287</v>
+        <v>654279</v>
       </c>
       <c r="R17" t="n">
-        <v>7008086</v>
+        <v>7008217</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2390,7 +2409,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2400,7 +2419,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2427,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120086159</v>
+        <v>120085506</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>90923</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2439,38 +2458,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654239</v>
+        <v>654287</v>
       </c>
       <c r="R18" t="n">
-        <v>7008276</v>
+        <v>7008086</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,7 +2521,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2512,12 +2531,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2544,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120085491</v>
+        <v>120085757</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2560,37 +2574,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654200</v>
+        <v>654286</v>
       </c>
       <c r="R19" t="n">
-        <v>7008326</v>
+        <v>7008186</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,24 +2631,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,19 +2648,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088184</v>
+        <v>120085695</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2701,10 +2700,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654118</v>
+        <v>654200</v>
       </c>
       <c r="R20" t="n">
-        <v>7008347</v>
+        <v>7008363</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2736,7 +2735,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2745,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2778,10 +2777,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120087102</v>
+        <v>120085193</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2790,50 +2789,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654149</v>
+        <v>654207</v>
       </c>
       <c r="R21" t="n">
-        <v>7008498</v>
+        <v>7008193</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2860,19 +2850,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2887,22 +2867,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088364</v>
+        <v>120081327</v>
       </c>
       <c r="B22" t="n">
-        <v>90923</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2911,41 +2891,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654153</v>
+        <v>654200</v>
       </c>
       <c r="R22" t="n">
-        <v>7008523</v>
+        <v>7007872</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2975,6 +2955,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,22 +2974,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120086991</v>
+        <v>120082434</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>91850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3017,34 +3002,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654156</v>
+        <v>654303</v>
       </c>
       <c r="R23" t="n">
-        <v>7008421</v>
+        <v>7007918</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3076,7 +3061,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3086,12 +3071,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,22 +3086,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120085434</v>
+        <v>120082934</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3130,41 +3110,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654217</v>
+        <v>654181</v>
       </c>
       <c r="R24" t="n">
-        <v>7008312</v>
+        <v>7007955</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3193,7 +3173,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3203,12 +3183,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,10 +3210,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120085193</v>
+        <v>120086638</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3251,37 +3226,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654207</v>
+        <v>654208</v>
       </c>
       <c r="R25" t="n">
-        <v>7008193</v>
+        <v>7008351</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3308,9 +3283,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3325,22 +3315,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120082214</v>
+        <v>120082669</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>91902</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3353,21 +3343,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3377,10 +3367,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654279</v>
+        <v>654314</v>
       </c>
       <c r="R26" t="n">
-        <v>7007930</v>
+        <v>7007905</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3412,7 +3402,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3422,12 +3412,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färskt bohål.</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,10 +3439,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088520</v>
+        <v>120088072</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3466,38 +3451,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654121</v>
+        <v>654111</v>
       </c>
       <c r="R27" t="n">
-        <v>7008041</v>
+        <v>7008487</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,7 +3518,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3539,12 +3528,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3571,10 +3555,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120085706</v>
+        <v>120082215</v>
       </c>
       <c r="B28" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3583,41 +3567,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654297</v>
+        <v>654150</v>
       </c>
       <c r="R28" t="n">
-        <v>7008132</v>
+        <v>7007925</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3644,9 +3637,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3661,22 +3664,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120087288</v>
+        <v>120085491</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3689,21 +3692,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3713,13 +3716,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654159</v>
+        <v>654200</v>
       </c>
       <c r="R29" t="n">
-        <v>7008481</v>
+        <v>7008326</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3746,9 +3749,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3763,22 +3781,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120082158</v>
+        <v>120087649</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3787,41 +3805,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654220</v>
+        <v>654117</v>
       </c>
       <c r="R30" t="n">
-        <v>7007891</v>
+        <v>7008449</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3848,19 +3870,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3875,19 +3887,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120085695</v>
+        <v>120088486</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3923,14 +3935,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654200</v>
+        <v>654118</v>
       </c>
       <c r="R31" t="n">
-        <v>7008363</v>
+        <v>7008045</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3962,7 +3974,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3972,12 +3984,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4004,10 +4016,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120085300</v>
+        <v>120086920</v>
       </c>
       <c r="B32" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4016,41 +4028,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654207</v>
+        <v>654164</v>
       </c>
       <c r="R32" t="n">
-        <v>7008193</v>
+        <v>7008398</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4077,9 +4089,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4094,22 +4121,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120086958</v>
+        <v>120085300</v>
       </c>
       <c r="B33" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4118,38 +4145,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654151</v>
+        <v>654207</v>
       </c>
       <c r="R33" t="n">
-        <v>7008440</v>
+        <v>7008193</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4208,10 +4235,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120086783</v>
+        <v>120087288</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4224,21 +4251,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,13 +4275,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654209</v>
+        <v>654159</v>
       </c>
       <c r="R34" t="n">
-        <v>7008406</v>
+        <v>7008481</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4281,24 +4308,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4313,22 +4325,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120085755</v>
+        <v>120082342</v>
       </c>
       <c r="B35" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4337,43 +4349,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654292</v>
+        <v>654125</v>
       </c>
       <c r="R35" t="n">
-        <v>7008151</v>
+        <v>7007981</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4405,7 +4421,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4415,7 +4431,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4430,22 +4446,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120087649</v>
+        <v>120085211</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4454,45 +4470,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654117</v>
+        <v>654207</v>
       </c>
       <c r="R36" t="n">
-        <v>7008449</v>
+        <v>7008193</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4536,22 +4548,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120088260</v>
+        <v>120087230</v>
       </c>
       <c r="B37" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4564,21 +4576,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4588,13 +4600,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654139</v>
+        <v>654170</v>
       </c>
       <c r="R37" t="n">
-        <v>7008299</v>
+        <v>7008380</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4621,19 +4633,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4648,19 +4650,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120086920</v>
+        <v>120088639</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4696,14 +4698,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654164</v>
+        <v>654098</v>
       </c>
       <c r="R38" t="n">
-        <v>7008398</v>
+        <v>7007903</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4735,7 +4737,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4745,7 +4747,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4777,10 +4779,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120082215</v>
+        <v>120088184</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4789,47 +4791,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654150</v>
+        <v>654118</v>
       </c>
       <c r="R39" t="n">
-        <v>7007925</v>
+        <v>7008347</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4861,7 +4854,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4871,7 +4864,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4898,10 +4896,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120085211</v>
+        <v>120088111</v>
       </c>
       <c r="B40" t="n">
-        <v>90864</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4910,41 +4908,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Renudden, Renudden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654207</v>
+        <v>654070</v>
       </c>
       <c r="R40" t="n">
-        <v>7008193</v>
+        <v>7008447</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4971,9 +4969,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4988,22 +4996,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120082329</v>
+        <v>120086940</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5016,34 +5024,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654290</v>
+        <v>654160</v>
       </c>
       <c r="R41" t="n">
-        <v>7007940</v>
+        <v>7008398</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5075,7 +5083,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5085,12 +5093,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5105,22 +5108,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120088486</v>
+        <v>120085424</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5133,34 +5136,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654118</v>
+        <v>654284</v>
       </c>
       <c r="R42" t="n">
-        <v>7008045</v>
+        <v>7008101</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5192,7 +5195,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5202,12 +5205,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5222,22 +5220,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120082934</v>
+        <v>120085759</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5246,41 +5244,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654181</v>
+        <v>654293</v>
       </c>
       <c r="R43" t="n">
-        <v>7007955</v>
+        <v>7008191</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5307,19 +5305,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5334,22 +5322,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120088189</v>
+        <v>120088364</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>90923</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5358,25 +5346,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5386,13 +5374,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654128</v>
+        <v>654153</v>
       </c>
       <c r="R44" t="n">
-        <v>7008344</v>
+        <v>7008523</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5419,24 +5407,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5451,22 +5424,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120088639</v>
+        <v>120086958</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5479,37 +5452,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654098</v>
+        <v>654151</v>
       </c>
       <c r="R45" t="n">
-        <v>7007903</v>
+        <v>7008440</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5536,24 +5509,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5568,12 +5526,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5697,10 +5655,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120088072</v>
+        <v>120086991</v>
       </c>
       <c r="B47" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5709,42 +5667,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654111</v>
+        <v>654156</v>
       </c>
       <c r="R47" t="n">
-        <v>7008487</v>
+        <v>7008421</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5776,7 +5730,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5786,7 +5740,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5801,22 +5760,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120088111</v>
+        <v>120082271</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5825,38 +5784,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Renudden, Renudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654070</v>
+        <v>654150</v>
       </c>
       <c r="R48" t="n">
-        <v>7008447</v>
+        <v>7007925</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5888,7 +5847,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5898,7 +5857,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5913,19 +5877,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120081327</v>
+        <v>120086159</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5961,17 +5925,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654200</v>
+        <v>654239</v>
       </c>
       <c r="R49" t="n">
-        <v>7007872</v>
+        <v>7008276</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5998,9 +5962,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6020,22 +5994,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120086940</v>
+        <v>120087102</v>
       </c>
       <c r="B50" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6044,38 +6018,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654160</v>
+        <v>654149</v>
       </c>
       <c r="R50" t="n">
-        <v>7008398</v>
+        <v>7008498</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6107,7 +6090,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6117,7 +6100,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6144,10 +6127,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120085757</v>
+        <v>120087238</v>
       </c>
       <c r="B51" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6160,34 +6143,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654286</v>
+        <v>654193</v>
       </c>
       <c r="R51" t="n">
-        <v>7008186</v>
+        <v>7008384</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6246,10 +6229,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120085939</v>
+        <v>120082214</v>
       </c>
       <c r="B52" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6262,21 +6245,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6289,7 +6272,7 @@
         <v>654279</v>
       </c>
       <c r="R52" t="n">
-        <v>7008217</v>
+        <v>7007930</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6321,7 +6304,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6331,7 +6314,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6358,10 +6346,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120082342</v>
+        <v>120085468</v>
       </c>
       <c r="B53" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6370,50 +6358,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654125</v>
+        <v>654268</v>
       </c>
       <c r="R53" t="n">
-        <v>7007981</v>
+        <v>7008096</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6440,19 +6419,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6467,22 +6436,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120085468</v>
+        <v>120082329</v>
       </c>
       <c r="B54" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6491,25 +6460,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6519,13 +6488,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654268</v>
+        <v>654290</v>
       </c>
       <c r="R54" t="n">
-        <v>7008096</v>
+        <v>7007940</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6552,9 +6521,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6569,22 +6553,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120085493</v>
+        <v>120085648</v>
       </c>
       <c r="B55" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6597,21 +6581,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6621,13 +6605,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654196</v>
+        <v>654195</v>
       </c>
       <c r="R55" t="n">
-        <v>7008339</v>
+        <v>7008349</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6654,9 +6638,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6671,12 +6670,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6897,7 +6896,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120085919</v>
+        <v>120086783</v>
       </c>
       <c r="B58" t="n">
         <v>57320</v>
@@ -6933,14 +6932,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654285</v>
+        <v>654209</v>
       </c>
       <c r="R58" t="n">
-        <v>7008199</v>
+        <v>7008406</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6972,7 +6971,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6982,7 +6981,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -7014,10 +7013,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120082271</v>
+        <v>120085493</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>86895</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7030,37 +7029,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654150</v>
+        <v>654196</v>
       </c>
       <c r="R59" t="n">
-        <v>7007925</v>
+        <v>7008339</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7087,24 +7086,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7119,22 +7103,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120087985</v>
+        <v>120085755</v>
       </c>
       <c r="B60" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7143,42 +7127,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>654128</v>
+        <v>654292</v>
       </c>
       <c r="R60" t="n">
-        <v>7008520</v>
+        <v>7008151</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7210,7 +7195,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7220,7 +7205,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7247,7 +7232,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120086638</v>
+        <v>120087568</v>
       </c>
       <c r="B61" t="n">
         <v>57320</v>
@@ -7287,10 +7272,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654208</v>
+        <v>654173</v>
       </c>
       <c r="R61" t="n">
-        <v>7008351</v>
+        <v>7008502</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7322,7 +7307,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7332,12 +7317,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7364,10 +7349,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120082434</v>
+        <v>120085919</v>
       </c>
       <c r="B62" t="n">
-        <v>91850</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7380,21 +7365,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7404,10 +7389,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654303</v>
+        <v>654285</v>
       </c>
       <c r="R62" t="n">
-        <v>7007918</v>
+        <v>7008199</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7439,7 +7424,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7449,7 +7434,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7476,10 +7466,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120085648</v>
+        <v>120085706</v>
       </c>
       <c r="B63" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7488,41 +7478,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654195</v>
+        <v>654297</v>
       </c>
       <c r="R63" t="n">
-        <v>7008349</v>
+        <v>7008132</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7549,24 +7539,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7581,22 +7556,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120087238</v>
+        <v>120088189</v>
       </c>
       <c r="B64" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7609,21 +7584,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7633,13 +7608,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654193</v>
+        <v>654128</v>
       </c>
       <c r="R64" t="n">
-        <v>7008384</v>
+        <v>7008344</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7666,9 +7641,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7683,22 +7673,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120082669</v>
+        <v>120085485</v>
       </c>
       <c r="B65" t="n">
-        <v>91902</v>
+        <v>90864</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7711,21 +7701,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7735,13 +7725,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654314</v>
+        <v>654276</v>
       </c>
       <c r="R65" t="n">
-        <v>7007905</v>
+        <v>7008093</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7768,19 +7758,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7795,22 +7775,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120087568</v>
+        <v>120088260</v>
       </c>
       <c r="B66" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7823,21 +7803,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7847,10 +7827,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654173</v>
+        <v>654139</v>
       </c>
       <c r="R66" t="n">
-        <v>7008502</v>
+        <v>7008299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7882,7 +7862,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7892,12 +7872,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på  gran</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7912,22 +7887,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120085759</v>
+        <v>120088520</v>
       </c>
       <c r="B67" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7940,37 +7915,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654293</v>
+        <v>654121</v>
       </c>
       <c r="R67" t="n">
-        <v>7008191</v>
+        <v>7008041</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7997,9 +7972,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8014,22 +8004,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120085485</v>
+        <v>120082158</v>
       </c>
       <c r="B68" t="n">
-        <v>90864</v>
+        <v>91858</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8038,41 +8028,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654276</v>
+        <v>654220</v>
       </c>
       <c r="R68" t="n">
-        <v>7008093</v>
+        <v>7007891</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8099,9 +8089,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8116,12 +8116,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -2232,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120087250</v>
+        <v>120085506</v>
       </c>
       <c r="B16" t="n">
-        <v>90545</v>
+        <v>90923</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,41 +2244,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654191</v>
+        <v>654287</v>
       </c>
       <c r="R16" t="n">
-        <v>7008385</v>
+        <v>7008086</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2305,9 +2305,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,12 +2332,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2446,10 +2456,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120085506</v>
+        <v>120087250</v>
       </c>
       <c r="B18" t="n">
-        <v>90923</v>
+        <v>90545</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2458,41 +2468,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654287</v>
+        <v>654191</v>
       </c>
       <c r="R18" t="n">
-        <v>7008086</v>
+        <v>7008385</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2519,19 +2529,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2546,22 +2546,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120085757</v>
+        <v>120085695</v>
       </c>
       <c r="B19" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2574,37 +2574,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654286</v>
+        <v>654200</v>
       </c>
       <c r="R19" t="n">
-        <v>7008186</v>
+        <v>7008363</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2631,9 +2631,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2648,22 +2663,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120085695</v>
+        <v>120085757</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2676,37 +2691,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654200</v>
+        <v>654286</v>
       </c>
       <c r="R20" t="n">
-        <v>7008363</v>
+        <v>7008186</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,24 +2748,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,12 +2765,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120082434</v>
+        <v>120082669</v>
       </c>
       <c r="B23" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3002,21 +3002,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654303</v>
+        <v>654314</v>
       </c>
       <c r="R23" t="n">
-        <v>7007918</v>
+        <v>7007905</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120082934</v>
+        <v>120086638</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3110,38 +3110,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654181</v>
+        <v>654208</v>
       </c>
       <c r="R24" t="n">
-        <v>7007955</v>
+        <v>7008351</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3183,7 +3183,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3210,10 +3215,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120086638</v>
+        <v>120082434</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>91850</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3226,34 +3231,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654208</v>
+        <v>654303</v>
       </c>
       <c r="R25" t="n">
-        <v>7008351</v>
+        <v>7007918</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,7 +3290,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3295,12 +3300,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3315,22 +3315,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120082669</v>
+        <v>120082934</v>
       </c>
       <c r="B26" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3339,38 +3339,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654314</v>
+        <v>654181</v>
       </c>
       <c r="R26" t="n">
-        <v>7007905</v>
+        <v>7007955</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3427,12 +3427,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4235,10 +4235,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120087288</v>
+        <v>120082342</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4247,41 +4247,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654159</v>
+        <v>654125</v>
       </c>
       <c r="R34" t="n">
-        <v>7008481</v>
+        <v>7007981</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4308,9 +4317,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4325,22 +4344,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120082342</v>
+        <v>120087288</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4349,50 +4368,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654125</v>
+        <v>654159</v>
       </c>
       <c r="R35" t="n">
-        <v>7007981</v>
+        <v>7008481</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4419,19 +4429,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4446,22 +4446,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120085211</v>
+        <v>120088639</v>
       </c>
       <c r="B36" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4474,37 +4474,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654207</v>
+        <v>654098</v>
       </c>
       <c r="R36" t="n">
-        <v>7008193</v>
+        <v>7007903</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4531,9 +4531,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4548,22 +4563,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120087230</v>
+        <v>120088184</v>
       </c>
       <c r="B37" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4576,21 +4591,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4600,13 +4615,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654170</v>
+        <v>654118</v>
       </c>
       <c r="R37" t="n">
-        <v>7008380</v>
+        <v>7008347</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4633,9 +4648,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4650,22 +4680,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120088639</v>
+        <v>120085211</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4678,37 +4708,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654098</v>
+        <v>654207</v>
       </c>
       <c r="R38" t="n">
-        <v>7007903</v>
+        <v>7008193</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4735,24 +4765,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4767,22 +4782,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120088184</v>
+        <v>120087230</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4795,21 +4810,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4819,13 +4834,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654118</v>
+        <v>654170</v>
       </c>
       <c r="R39" t="n">
-        <v>7008347</v>
+        <v>7008380</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4852,24 +4867,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4884,12 +4884,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -6346,10 +6346,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120085468</v>
+        <v>120082329</v>
       </c>
       <c r="B53" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6358,25 +6358,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6386,13 +6386,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654268</v>
+        <v>654290</v>
       </c>
       <c r="R53" t="n">
-        <v>7008096</v>
+        <v>7007940</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6419,9 +6419,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6436,19 +6451,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120082329</v>
+        <v>120085648</v>
       </c>
       <c r="B54" t="n">
         <v>57320</v>
@@ -6484,14 +6499,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654290</v>
+        <v>654195</v>
       </c>
       <c r="R54" t="n">
-        <v>7007940</v>
+        <v>7008349</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6523,7 +6538,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6533,12 +6548,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6553,22 +6568,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120085648</v>
+        <v>120085468</v>
       </c>
       <c r="B55" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6577,41 +6592,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654195</v>
+        <v>654268</v>
       </c>
       <c r="R55" t="n">
-        <v>7008349</v>
+        <v>7008096</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6638,24 +6653,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6670,22 +6670,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120085068</v>
+        <v>120085493</v>
       </c>
       <c r="B56" t="n">
-        <v>91023</v>
+        <v>86895</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6694,41 +6694,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1209</v>
+        <v>510</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654217</v>
+        <v>654196</v>
       </c>
       <c r="R56" t="n">
-        <v>7008168</v>
+        <v>7008339</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6755,19 +6755,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6782,19 +6772,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120085930</v>
+        <v>120085068</v>
       </c>
       <c r="B57" t="n">
         <v>91023</v>
@@ -6834,13 +6824,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654269</v>
+        <v>654217</v>
       </c>
       <c r="R57" t="n">
-        <v>7008197</v>
+        <v>7008168</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6867,9 +6857,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6884,22 +6884,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120086783</v>
+        <v>120085930</v>
       </c>
       <c r="B58" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6908,41 +6908,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654209</v>
+        <v>654269</v>
       </c>
       <c r="R58" t="n">
-        <v>7008406</v>
+        <v>7008197</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6969,24 +6969,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7001,22 +6986,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120085493</v>
+        <v>120086783</v>
       </c>
       <c r="B59" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7029,21 +7014,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7053,13 +7038,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654196</v>
+        <v>654209</v>
       </c>
       <c r="R59" t="n">
-        <v>7008339</v>
+        <v>7008406</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7086,9 +7071,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7103,12 +7103,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7466,10 +7466,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120085706</v>
+        <v>120085485</v>
       </c>
       <c r="B63" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7478,25 +7478,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7506,10 +7506,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654297</v>
+        <v>654276</v>
       </c>
       <c r="R63" t="n">
-        <v>7008132</v>
+        <v>7008093</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7568,10 +7568,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120088189</v>
+        <v>120085706</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7580,41 +7580,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654128</v>
+        <v>654297</v>
       </c>
       <c r="R64" t="n">
-        <v>7008344</v>
+        <v>7008132</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7641,24 +7641,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7673,22 +7658,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120085485</v>
+        <v>120088189</v>
       </c>
       <c r="B65" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7701,37 +7686,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654276</v>
+        <v>654128</v>
       </c>
       <c r="R65" t="n">
-        <v>7008093</v>
+        <v>7008344</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7758,9 +7743,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7775,12 +7775,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,7 +1999,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120085434</v>
+        <v>120088486</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2035,17 +2035,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654217</v>
+        <v>654118</v>
       </c>
       <c r="R14" t="n">
-        <v>7008312</v>
+        <v>7008045</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120087985</v>
+        <v>120082934</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,42 +2128,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654128</v>
+        <v>654181</v>
       </c>
       <c r="R15" t="n">
-        <v>7008520</v>
+        <v>7007955</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2205,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2220,22 +2216,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120085506</v>
+        <v>120088189</v>
       </c>
       <c r="B16" t="n">
-        <v>90923</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,38 +2240,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654287</v>
+        <v>654128</v>
       </c>
       <c r="R16" t="n">
-        <v>7008086</v>
+        <v>7008344</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2317,7 +2313,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120085939</v>
+        <v>120087985</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,38 +2357,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654279</v>
+        <v>654128</v>
       </c>
       <c r="R17" t="n">
-        <v>7008217</v>
+        <v>7008520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,7 +2424,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2429,7 +2434,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2456,10 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120087250</v>
+        <v>120087649</v>
       </c>
       <c r="B18" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,38 +2473,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654191</v>
+        <v>654117</v>
       </c>
       <c r="R18" t="n">
-        <v>7008385</v>
+        <v>7008449</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2558,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120085695</v>
+        <v>120085468</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,41 +2579,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654200</v>
+        <v>654268</v>
       </c>
       <c r="R19" t="n">
-        <v>7008363</v>
+        <v>7008096</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2631,24 +2640,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,22 +2657,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120085757</v>
+        <v>120082669</v>
       </c>
       <c r="B20" t="n">
-        <v>90864</v>
+        <v>91902</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2691,21 +2685,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2715,13 +2709,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654286</v>
+        <v>654314</v>
       </c>
       <c r="R20" t="n">
-        <v>7008186</v>
+        <v>7007905</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2748,9 +2742,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,22 +2769,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120085193</v>
+        <v>120082329</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2793,21 +2797,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2817,13 +2821,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654207</v>
+        <v>654290</v>
       </c>
       <c r="R21" t="n">
-        <v>7008193</v>
+        <v>7007940</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2850,9 +2854,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2867,19 +2886,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120081327</v>
+        <v>120088261</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2915,17 +2934,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsviken, Svartnäsviken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654200</v>
+        <v>654154</v>
       </c>
       <c r="R22" t="n">
-        <v>7007872</v>
+        <v>7008250</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2952,14 +2971,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,22 +3003,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120082669</v>
+        <v>120086940</v>
       </c>
       <c r="B23" t="n">
-        <v>91902</v>
+        <v>78279</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3002,34 +3031,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654314</v>
+        <v>654160</v>
       </c>
       <c r="R23" t="n">
-        <v>7007905</v>
+        <v>7008398</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3061,7 +3090,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3071,7 +3100,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3086,22 +3115,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120086638</v>
+        <v>120088260</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3114,21 +3143,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3138,10 +3167,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654208</v>
+        <v>654139</v>
       </c>
       <c r="R24" t="n">
-        <v>7008351</v>
+        <v>7008299</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3173,7 +3202,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3183,12 +3212,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3203,22 +3227,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120082434</v>
+        <v>120085068</v>
       </c>
       <c r="B25" t="n">
-        <v>91850</v>
+        <v>91023</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3227,25 +3251,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3255,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654303</v>
+        <v>654217</v>
       </c>
       <c r="R25" t="n">
-        <v>7007918</v>
+        <v>7008168</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3290,7 +3314,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3300,7 +3324,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3315,22 +3339,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120082934</v>
+        <v>120087568</v>
       </c>
       <c r="B26" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3339,38 +3363,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654181</v>
+        <v>654173</v>
       </c>
       <c r="R26" t="n">
-        <v>7007955</v>
+        <v>7008502</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3402,7 +3426,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3412,7 +3436,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,10 +3468,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088072</v>
+        <v>120085930</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>91023</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3455,41 +3484,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654111</v>
+        <v>654269</v>
       </c>
       <c r="R27" t="n">
-        <v>7008487</v>
+        <v>7008197</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3516,19 +3541,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3543,22 +3558,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120082215</v>
+        <v>120085434</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3567,50 +3582,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654150</v>
+        <v>654217</v>
       </c>
       <c r="R28" t="n">
-        <v>7007925</v>
+        <v>7008312</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3639,7 +3645,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3649,7 +3655,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3676,7 +3687,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120085491</v>
+        <v>120085695</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3719,10 +3730,10 @@
         <v>654200</v>
       </c>
       <c r="R29" t="n">
-        <v>7008326</v>
+        <v>7008363</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3751,7 +3762,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3761,12 +3772,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3793,10 +3804,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120087649</v>
+        <v>120082158</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3805,45 +3816,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654117</v>
+        <v>654220</v>
       </c>
       <c r="R30" t="n">
-        <v>7008449</v>
+        <v>7007891</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3870,9 +3877,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3887,19 +3904,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088486</v>
+        <v>120086783</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3935,14 +3952,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654118</v>
+        <v>654209</v>
       </c>
       <c r="R31" t="n">
-        <v>7008045</v>
+        <v>7008406</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3974,7 +3991,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3984,12 +4001,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4004,22 +4021,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120086920</v>
+        <v>120087238</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4032,21 +4049,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4056,13 +4073,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654164</v>
+        <v>654193</v>
       </c>
       <c r="R32" t="n">
-        <v>7008398</v>
+        <v>7008384</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4089,24 +4106,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4121,22 +4123,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120085300</v>
+        <v>120085919</v>
       </c>
       <c r="B33" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4145,25 +4147,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4173,13 +4175,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654207</v>
+        <v>654285</v>
       </c>
       <c r="R33" t="n">
-        <v>7008193</v>
+        <v>7008199</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4206,9 +4208,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4223,22 +4240,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120082342</v>
+        <v>120088520</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4247,47 +4264,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654125</v>
+        <v>654121</v>
       </c>
       <c r="R34" t="n">
-        <v>7007981</v>
+        <v>7008041</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4319,7 +4327,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4329,7 +4337,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4344,22 +4357,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120087288</v>
+        <v>120088111</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4368,41 +4381,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Renudden, Renudden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654159</v>
+        <v>654070</v>
       </c>
       <c r="R35" t="n">
-        <v>7008481</v>
+        <v>7008447</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4429,9 +4442,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4446,19 +4469,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120088639</v>
+        <v>120086159</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4494,14 +4517,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654098</v>
+        <v>654239</v>
       </c>
       <c r="R36" t="n">
-        <v>7007903</v>
+        <v>7008276</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4533,7 +4556,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4543,12 +4566,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4563,22 +4586,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120088184</v>
+        <v>120085757</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4591,37 +4614,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654118</v>
+        <v>654286</v>
       </c>
       <c r="R37" t="n">
-        <v>7008347</v>
+        <v>7008186</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4648,24 +4671,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,22 +4688,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120085211</v>
+        <v>120082434</v>
       </c>
       <c r="B38" t="n">
-        <v>90864</v>
+        <v>91850</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4708,21 +4716,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4732,13 +4740,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654207</v>
+        <v>654303</v>
       </c>
       <c r="R38" t="n">
-        <v>7008193</v>
+        <v>7007918</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4765,9 +4773,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4782,22 +4800,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120087230</v>
+        <v>120088184</v>
       </c>
       <c r="B39" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4810,21 +4828,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4834,13 +4852,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654170</v>
+        <v>654118</v>
       </c>
       <c r="R39" t="n">
-        <v>7008380</v>
+        <v>7008347</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4867,9 +4885,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4884,22 +4917,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120088111</v>
+        <v>120087230</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>90864</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4908,41 +4941,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Renudden, Renudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654070</v>
+        <v>654170</v>
       </c>
       <c r="R40" t="n">
-        <v>7008447</v>
+        <v>7008380</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4969,19 +5002,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4996,22 +5019,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120086940</v>
+        <v>120085424</v>
       </c>
       <c r="B41" t="n">
-        <v>78279</v>
+        <v>90580</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5024,34 +5047,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654160</v>
+        <v>654284</v>
       </c>
       <c r="R41" t="n">
-        <v>7008398</v>
+        <v>7008101</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5083,7 +5106,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5093,7 +5116,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5108,22 +5131,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120085424</v>
+        <v>120082215</v>
       </c>
       <c r="B42" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5132,38 +5155,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654284</v>
+        <v>654150</v>
       </c>
       <c r="R42" t="n">
-        <v>7008101</v>
+        <v>7007925</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5195,7 +5227,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5205,7 +5237,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5220,22 +5252,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120085759</v>
+        <v>120087102</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5244,41 +5276,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654293</v>
+        <v>654149</v>
       </c>
       <c r="R43" t="n">
-        <v>7008191</v>
+        <v>7008498</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5305,9 +5346,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5322,22 +5373,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120088364</v>
+        <v>120085491</v>
       </c>
       <c r="B44" t="n">
-        <v>90923</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5346,25 +5397,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5374,10 +5425,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654153</v>
+        <v>654200</v>
       </c>
       <c r="R44" t="n">
-        <v>7008523</v>
+        <v>7008326</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5407,9 +5458,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5424,22 +5490,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120086958</v>
+        <v>120085755</v>
       </c>
       <c r="B45" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5452,37 +5518,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654151</v>
+        <v>654292</v>
       </c>
       <c r="R45" t="n">
-        <v>7008440</v>
+        <v>7008151</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5509,9 +5580,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5526,22 +5607,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120088261</v>
+        <v>120085411</v>
       </c>
       <c r="B46" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5554,37 +5635,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svartnäsviken, Svartnäsviken, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654154</v>
+        <v>654207</v>
       </c>
       <c r="R46" t="n">
-        <v>7008250</v>
+        <v>7008193</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5611,24 +5692,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5643,22 +5709,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120086991</v>
+        <v>120085706</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5667,41 +5733,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654156</v>
+        <v>654297</v>
       </c>
       <c r="R47" t="n">
-        <v>7008421</v>
+        <v>7008132</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5728,24 +5794,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5760,22 +5811,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120082271</v>
+        <v>120087250</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5784,41 +5835,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654150</v>
+        <v>654191</v>
       </c>
       <c r="R48" t="n">
-        <v>7007925</v>
+        <v>7008385</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5845,24 +5896,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5877,19 +5913,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120086159</v>
+        <v>120088639</v>
       </c>
       <c r="B49" t="n">
         <v>57320</v>
@@ -5925,14 +5961,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654239</v>
+        <v>654098</v>
       </c>
       <c r="R49" t="n">
-        <v>7008276</v>
+        <v>7007903</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5964,7 +6000,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5974,12 +6010,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5994,22 +6030,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120087102</v>
+        <v>120088364</v>
       </c>
       <c r="B50" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6022,46 +6058,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654149</v>
+        <v>654153</v>
       </c>
       <c r="R50" t="n">
-        <v>7008498</v>
+        <v>7008523</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6088,19 +6115,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6115,22 +6132,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120087238</v>
+        <v>120085506</v>
       </c>
       <c r="B51" t="n">
-        <v>90580</v>
+        <v>90923</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6139,41 +6156,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654193</v>
+        <v>654287</v>
       </c>
       <c r="R51" t="n">
-        <v>7008384</v>
+        <v>7008086</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6200,9 +6217,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6217,22 +6244,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120082214</v>
+        <v>120088072</v>
       </c>
       <c r="B52" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6241,38 +6268,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654279</v>
+        <v>654111</v>
       </c>
       <c r="R52" t="n">
-        <v>7007930</v>
+        <v>7008487</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6304,7 +6335,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6314,12 +6345,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färskt bohål.</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6346,10 +6372,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120082329</v>
+        <v>120085485</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6362,21 +6388,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6386,13 +6412,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654290</v>
+        <v>654276</v>
       </c>
       <c r="R53" t="n">
-        <v>7007940</v>
+        <v>7008093</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6419,24 +6445,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6451,12 +6462,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6580,10 +6591,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120085468</v>
+        <v>120081327</v>
       </c>
       <c r="B55" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6592,38 +6603,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654268</v>
+        <v>654200</v>
       </c>
       <c r="R55" t="n">
-        <v>7008096</v>
+        <v>7007872</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6656,6 +6667,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6682,10 +6698,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120085493</v>
+        <v>120086991</v>
       </c>
       <c r="B56" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6698,21 +6714,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6722,13 +6738,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654196</v>
+        <v>654156</v>
       </c>
       <c r="R56" t="n">
-        <v>7008339</v>
+        <v>7008421</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6755,9 +6771,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6772,22 +6803,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120085068</v>
+        <v>120082271</v>
       </c>
       <c r="B57" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6796,38 +6827,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654217</v>
+        <v>654150</v>
       </c>
       <c r="R57" t="n">
-        <v>7008168</v>
+        <v>7007925</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6859,7 +6890,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6869,7 +6900,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6896,10 +6932,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120085930</v>
+        <v>120082342</v>
       </c>
       <c r="B58" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6912,37 +6948,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654269</v>
+        <v>654125</v>
       </c>
       <c r="R58" t="n">
-        <v>7008197</v>
+        <v>7007981</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6969,9 +7014,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6986,22 +7041,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120086783</v>
+        <v>120087288</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7014,21 +7069,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7038,13 +7093,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654209</v>
+        <v>654159</v>
       </c>
       <c r="R59" t="n">
-        <v>7008406</v>
+        <v>7008481</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7071,24 +7126,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7103,22 +7143,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120085755</v>
+        <v>120085493</v>
       </c>
       <c r="B60" t="n">
-        <v>57336</v>
+        <v>86895</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7131,42 +7171,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>654292</v>
+        <v>654196</v>
       </c>
       <c r="R60" t="n">
-        <v>7008151</v>
+        <v>7008339</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7193,19 +7228,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:43</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7220,22 +7245,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120087568</v>
+        <v>120085939</v>
       </c>
       <c r="B61" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7248,34 +7273,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654173</v>
+        <v>654279</v>
       </c>
       <c r="R61" t="n">
-        <v>7008502</v>
+        <v>7008217</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7307,7 +7332,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7317,12 +7342,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på  gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7337,22 +7357,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120085919</v>
+        <v>120085300</v>
       </c>
       <c r="B62" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7361,25 +7381,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7389,13 +7409,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654285</v>
+        <v>654207</v>
       </c>
       <c r="R62" t="n">
-        <v>7008199</v>
+        <v>7008193</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7422,24 +7442,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7454,22 +7459,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120085485</v>
+        <v>120085759</v>
       </c>
       <c r="B63" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7482,21 +7487,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7506,10 +7511,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654276</v>
+        <v>654293</v>
       </c>
       <c r="R63" t="n">
-        <v>7008093</v>
+        <v>7008191</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7568,10 +7573,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120085706</v>
+        <v>120085193</v>
       </c>
       <c r="B64" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7580,25 +7585,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7608,13 +7613,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654297</v>
+        <v>654207</v>
       </c>
       <c r="R64" t="n">
-        <v>7008132</v>
+        <v>7008193</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7658,19 +7663,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120088189</v>
+        <v>120086638</v>
       </c>
       <c r="B65" t="n">
         <v>57320</v>
@@ -7710,10 +7715,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654128</v>
+        <v>654208</v>
       </c>
       <c r="R65" t="n">
-        <v>7008344</v>
+        <v>7008351</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7745,7 +7750,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7755,12 +7760,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7775,22 +7780,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120088260</v>
+        <v>120086958</v>
       </c>
       <c r="B66" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7803,21 +7808,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7827,13 +7832,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654139</v>
+        <v>654151</v>
       </c>
       <c r="R66" t="n">
-        <v>7008299</v>
+        <v>7008440</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7860,19 +7865,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7887,22 +7882,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120088520</v>
+        <v>120082214</v>
       </c>
       <c r="B67" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7915,16 +7910,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7935,14 +7930,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654121</v>
+        <v>654279</v>
       </c>
       <c r="R67" t="n">
-        <v>7008041</v>
+        <v>7007930</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7974,7 +7969,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7984,12 +7979,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8016,10 +8011,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120082158</v>
+        <v>120086920</v>
       </c>
       <c r="B68" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8028,38 +8023,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654220</v>
+        <v>654164</v>
       </c>
       <c r="R68" t="n">
-        <v>7007891</v>
+        <v>7008398</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8091,7 +8086,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8101,7 +8096,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8116,12 +8116,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088486</v>
+        <v>120085759</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2015,37 +2015,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654118</v>
+        <v>654293</v>
       </c>
       <c r="R14" t="n">
-        <v>7008045</v>
+        <v>7008191</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,24 +2072,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,22 +2089,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120082934</v>
+        <v>120085068</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>91023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,38 +2113,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654181</v>
+        <v>654217</v>
       </c>
       <c r="R15" t="n">
-        <v>7007955</v>
+        <v>7008168</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2176,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2186,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,10 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088189</v>
+        <v>120086958</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,21 +2229,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,13 +2253,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654128</v>
+        <v>654151</v>
       </c>
       <c r="R16" t="n">
-        <v>7008344</v>
+        <v>7008440</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2301,24 +2286,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2333,22 +2303,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120087985</v>
+        <v>120085411</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2357,45 +2327,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654128</v>
+        <v>654207</v>
       </c>
       <c r="R17" t="n">
-        <v>7008520</v>
+        <v>7008193</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2422,19 +2388,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,22 +2405,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120087649</v>
+        <v>120082669</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>91902</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2473,45 +2429,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654117</v>
+        <v>654314</v>
       </c>
       <c r="R18" t="n">
-        <v>7008449</v>
+        <v>7007905</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2538,9 +2490,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2555,22 +2517,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120085468</v>
+        <v>120086920</v>
       </c>
       <c r="B19" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2579,41 +2541,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654268</v>
+        <v>654164</v>
       </c>
       <c r="R19" t="n">
-        <v>7008096</v>
+        <v>7008398</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2640,9 +2602,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,22 +2634,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120082669</v>
+        <v>120086991</v>
       </c>
       <c r="B20" t="n">
-        <v>91902</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2685,34 +2662,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654314</v>
+        <v>654156</v>
       </c>
       <c r="R20" t="n">
-        <v>7007905</v>
+        <v>7008421</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,7 +2721,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2731,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2769,19 +2751,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120082329</v>
+        <v>120086159</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2817,14 +2799,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654290</v>
+        <v>654239</v>
       </c>
       <c r="R21" t="n">
-        <v>7007940</v>
+        <v>7008276</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,7 +2838,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,7 +2848,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2898,7 +2880,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088261</v>
+        <v>120082329</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2934,14 +2916,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svartnäsviken, Svartnäsviken, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654154</v>
+        <v>654290</v>
       </c>
       <c r="R22" t="n">
-        <v>7008250</v>
+        <v>7007940</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2973,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2983,12 +2965,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3003,22 +2985,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120086940</v>
+        <v>120087568</v>
       </c>
       <c r="B23" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3031,21 +3013,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3055,10 +3037,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654160</v>
+        <v>654173</v>
       </c>
       <c r="R23" t="n">
-        <v>7008398</v>
+        <v>7008502</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3090,7 +3072,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3100,7 +3082,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088260</v>
+        <v>120085648</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3143,21 +3130,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3167,10 +3154,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654139</v>
+        <v>654195</v>
       </c>
       <c r="R24" t="n">
-        <v>7008299</v>
+        <v>7008349</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3202,7 +3189,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3212,7 +3199,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3227,22 +3219,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120085068</v>
+        <v>120082158</v>
       </c>
       <c r="B25" t="n">
-        <v>91023</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3251,38 +3243,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654217</v>
+        <v>654220</v>
       </c>
       <c r="R25" t="n">
-        <v>7008168</v>
+        <v>7007891</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3314,7 +3306,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3324,7 +3316,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,22 +3331,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120087568</v>
+        <v>120085930</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3363,41 +3355,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654173</v>
+        <v>654269</v>
       </c>
       <c r="R26" t="n">
-        <v>7008502</v>
+        <v>7008197</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3424,24 +3416,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på  gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3456,22 +3433,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120085930</v>
+        <v>120085193</v>
       </c>
       <c r="B27" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3480,25 +3457,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3508,13 +3485,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654269</v>
+        <v>654207</v>
       </c>
       <c r="R27" t="n">
-        <v>7008197</v>
+        <v>7008193</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3558,19 +3535,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120085434</v>
+        <v>120088486</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3606,17 +3583,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654217</v>
+        <v>654118</v>
       </c>
       <c r="R28" t="n">
-        <v>7008312</v>
+        <v>7008045</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3645,7 +3622,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3655,12 +3632,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3687,7 +3664,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120085695</v>
+        <v>120088189</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3727,10 +3704,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654200</v>
+        <v>654128</v>
       </c>
       <c r="R29" t="n">
-        <v>7008363</v>
+        <v>7008344</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3762,7 +3739,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3772,12 +3749,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3792,22 +3769,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120082158</v>
+        <v>120085434</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3816,41 +3793,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654220</v>
+        <v>654217</v>
       </c>
       <c r="R30" t="n">
-        <v>7007891</v>
+        <v>7008312</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3879,7 +3856,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3889,7 +3866,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3904,22 +3886,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120086783</v>
+        <v>120085755</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3932,16 +3914,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3950,16 +3932,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654209</v>
+        <v>654292</v>
       </c>
       <c r="R31" t="n">
-        <v>7008406</v>
+        <v>7008151</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3991,7 +3978,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4001,12 +3988,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4033,10 +4015,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120087238</v>
+        <v>120081327</v>
       </c>
       <c r="B32" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4049,34 +4031,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654193</v>
+        <v>654200</v>
       </c>
       <c r="R32" t="n">
-        <v>7008384</v>
+        <v>7007872</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4109,6 +4091,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4135,10 +4122,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120085919</v>
+        <v>120085485</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4151,21 +4138,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4175,13 +4162,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654285</v>
+        <v>654276</v>
       </c>
       <c r="R33" t="n">
-        <v>7008199</v>
+        <v>7008093</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,24 +4195,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4240,19 +4212,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120088520</v>
+        <v>120088639</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4292,10 +4264,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654121</v>
+        <v>654098</v>
       </c>
       <c r="R34" t="n">
-        <v>7008041</v>
+        <v>7007903</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4327,7 +4299,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4337,12 +4309,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4357,22 +4329,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120088111</v>
+        <v>120087288</v>
       </c>
       <c r="B35" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4381,41 +4353,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Renudden, Renudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654070</v>
+        <v>654159</v>
       </c>
       <c r="R35" t="n">
-        <v>7008447</v>
+        <v>7008481</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4442,19 +4414,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,22 +4431,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120086159</v>
+        <v>120085506</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>90923</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4493,38 +4455,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654239</v>
+        <v>654287</v>
       </c>
       <c r="R36" t="n">
-        <v>7008276</v>
+        <v>7008086</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4556,7 +4518,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4566,12 +4528,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4700,10 +4657,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120082434</v>
+        <v>120087250</v>
       </c>
       <c r="B38" t="n">
-        <v>91850</v>
+        <v>90545</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4712,41 +4669,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654303</v>
+        <v>654191</v>
       </c>
       <c r="R38" t="n">
-        <v>7007918</v>
+        <v>7008385</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4773,19 +4730,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4800,19 +4747,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120088184</v>
+        <v>120086638</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4852,10 +4799,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654118</v>
+        <v>654208</v>
       </c>
       <c r="R39" t="n">
-        <v>7008347</v>
+        <v>7008351</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4887,7 +4834,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4897,12 +4844,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4929,10 +4876,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120087230</v>
+        <v>120088111</v>
       </c>
       <c r="B40" t="n">
-        <v>90864</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4941,41 +4888,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Renudden, Renudden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654170</v>
+        <v>654070</v>
       </c>
       <c r="R40" t="n">
-        <v>7008380</v>
+        <v>7008447</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5002,9 +4949,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5019,22 +4976,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120085424</v>
+        <v>120088184</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5047,34 +5004,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654284</v>
+        <v>654118</v>
       </c>
       <c r="R41" t="n">
-        <v>7008101</v>
+        <v>7008347</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5106,7 +5063,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5116,7 +5073,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5131,22 +5093,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120082215</v>
+        <v>120087238</v>
       </c>
       <c r="B42" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5155,50 +5117,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654150</v>
+        <v>654193</v>
       </c>
       <c r="R42" t="n">
-        <v>7007925</v>
+        <v>7008384</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5225,19 +5178,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5252,22 +5195,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120087102</v>
+        <v>120085706</v>
       </c>
       <c r="B43" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5276,50 +5219,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654149</v>
+        <v>654297</v>
       </c>
       <c r="R43" t="n">
-        <v>7008498</v>
+        <v>7008132</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5346,19 +5280,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5373,22 +5297,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120085491</v>
+        <v>120085468</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5397,41 +5321,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654200</v>
+        <v>654268</v>
       </c>
       <c r="R44" t="n">
-        <v>7008326</v>
+        <v>7008096</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5458,24 +5382,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5490,22 +5399,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120085755</v>
+        <v>120082215</v>
       </c>
       <c r="B45" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5514,43 +5423,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654292</v>
+        <v>654150</v>
       </c>
       <c r="R45" t="n">
-        <v>7008151</v>
+        <v>7007925</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5582,7 +5495,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5592,7 +5505,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5607,22 +5520,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120085411</v>
+        <v>120086940</v>
       </c>
       <c r="B46" t="n">
-        <v>90864</v>
+        <v>78279</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5635,37 +5548,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654207</v>
+        <v>654160</v>
       </c>
       <c r="R46" t="n">
-        <v>7008193</v>
+        <v>7008398</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5692,9 +5605,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5709,22 +5632,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120085706</v>
+        <v>120082214</v>
       </c>
       <c r="B47" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5733,25 +5656,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5761,13 +5684,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654297</v>
+        <v>654279</v>
       </c>
       <c r="R47" t="n">
-        <v>7008132</v>
+        <v>7007930</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5794,9 +5717,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5811,22 +5749,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120087250</v>
+        <v>120082342</v>
       </c>
       <c r="B48" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5835,41 +5773,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654191</v>
+        <v>654125</v>
       </c>
       <c r="R48" t="n">
-        <v>7008385</v>
+        <v>7007981</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5896,9 +5843,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5913,22 +5870,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120088639</v>
+        <v>120085493</v>
       </c>
       <c r="B49" t="n">
-        <v>57320</v>
+        <v>86895</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5941,37 +5898,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654098</v>
+        <v>654196</v>
       </c>
       <c r="R49" t="n">
-        <v>7007903</v>
+        <v>7008339</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5998,24 +5955,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6030,22 +5972,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120088364</v>
+        <v>120087230</v>
       </c>
       <c r="B50" t="n">
-        <v>90923</v>
+        <v>90864</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6054,25 +5996,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6082,13 +6024,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654153</v>
+        <v>654170</v>
       </c>
       <c r="R50" t="n">
-        <v>7008523</v>
+        <v>7008380</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6132,22 +6074,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120085506</v>
+        <v>120085424</v>
       </c>
       <c r="B51" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6156,25 +6098,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6184,10 +6126,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654287</v>
+        <v>654284</v>
       </c>
       <c r="R51" t="n">
-        <v>7008086</v>
+        <v>7008101</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6219,7 +6161,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6229,7 +6171,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6256,10 +6198,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120088072</v>
+        <v>120085939</v>
       </c>
       <c r="B52" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6268,42 +6210,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654111</v>
+        <v>654279</v>
       </c>
       <c r="R52" t="n">
-        <v>7008487</v>
+        <v>7008217</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6335,7 +6273,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6345,7 +6283,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6372,10 +6310,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120085485</v>
+        <v>120085919</v>
       </c>
       <c r="B53" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6388,21 +6326,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6412,13 +6350,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654276</v>
+        <v>654285</v>
       </c>
       <c r="R53" t="n">
-        <v>7008093</v>
+        <v>7008199</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6445,9 +6383,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6462,22 +6415,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120085648</v>
+        <v>120088260</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6490,21 +6443,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6514,10 +6467,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654195</v>
+        <v>654139</v>
       </c>
       <c r="R54" t="n">
-        <v>7008349</v>
+        <v>7008299</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6549,7 +6502,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6559,12 +6512,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6579,19 +6527,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120081327</v>
+        <v>120085491</v>
       </c>
       <c r="B55" t="n">
         <v>57320</v>
@@ -6627,17 +6575,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
         <v>654200</v>
       </c>
       <c r="R55" t="n">
-        <v>7007872</v>
+        <v>7008326</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6664,14 +6612,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6686,19 +6644,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120086991</v>
+        <v>120088261</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6734,14 +6692,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsviken, Svartnäsviken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654156</v>
+        <v>654154</v>
       </c>
       <c r="R56" t="n">
-        <v>7008421</v>
+        <v>7008250</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6773,7 +6731,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6783,7 +6741,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -6815,7 +6773,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120082271</v>
+        <v>120086783</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6851,14 +6809,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654150</v>
+        <v>654209</v>
       </c>
       <c r="R57" t="n">
-        <v>7007925</v>
+        <v>7008406</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6890,7 +6848,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6900,12 +6858,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6920,19 +6878,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120082342</v>
+        <v>120087649</v>
       </c>
       <c r="B58" t="n">
         <v>97930</v>
@@ -6967,27 +6925,22 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654125</v>
+        <v>654117</v>
       </c>
       <c r="R58" t="n">
-        <v>7007981</v>
+        <v>7008449</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7014,19 +6967,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7041,22 +6984,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120087288</v>
+        <v>120082434</v>
       </c>
       <c r="B59" t="n">
-        <v>90580</v>
+        <v>91850</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7069,37 +7012,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654159</v>
+        <v>654303</v>
       </c>
       <c r="R59" t="n">
-        <v>7008481</v>
+        <v>7007918</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7126,9 +7069,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7143,22 +7096,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120085493</v>
+        <v>120085695</v>
       </c>
       <c r="B60" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7171,21 +7124,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7195,13 +7148,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>654196</v>
+        <v>654200</v>
       </c>
       <c r="R60" t="n">
-        <v>7008339</v>
+        <v>7008363</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7228,9 +7181,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7245,22 +7213,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120085939</v>
+        <v>120088072</v>
       </c>
       <c r="B61" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7269,38 +7237,42 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654279</v>
+        <v>654111</v>
       </c>
       <c r="R61" t="n">
-        <v>7008217</v>
+        <v>7008487</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7332,7 +7304,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7342,7 +7314,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7369,10 +7341,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120085300</v>
+        <v>120087985</v>
       </c>
       <c r="B62" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7385,37 +7357,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654207</v>
+        <v>654128</v>
       </c>
       <c r="R62" t="n">
-        <v>7008193</v>
+        <v>7008520</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7442,9 +7418,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7459,22 +7445,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120085759</v>
+        <v>120082934</v>
       </c>
       <c r="B63" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7483,41 +7469,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654293</v>
+        <v>654181</v>
       </c>
       <c r="R63" t="n">
-        <v>7008191</v>
+        <v>7007955</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7544,9 +7530,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7561,22 +7557,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120085193</v>
+        <v>120082271</v>
       </c>
       <c r="B64" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7589,37 +7585,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654207</v>
+        <v>654150</v>
       </c>
       <c r="R64" t="n">
-        <v>7008193</v>
+        <v>7007925</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7646,9 +7642,24 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7663,22 +7674,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120086638</v>
+        <v>120087102</v>
       </c>
       <c r="B65" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7687,38 +7698,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654208</v>
+        <v>654149</v>
       </c>
       <c r="R65" t="n">
-        <v>7008351</v>
+        <v>7008498</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7750,7 +7770,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7760,12 +7780,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7792,10 +7807,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120086958</v>
+        <v>120085300</v>
       </c>
       <c r="B66" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7804,38 +7819,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäsudden, Svartnäsudden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654151</v>
+        <v>654207</v>
       </c>
       <c r="R66" t="n">
-        <v>7008440</v>
+        <v>7008193</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7894,10 +7909,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120082214</v>
+        <v>120088364</v>
       </c>
       <c r="B67" t="n">
-        <v>57336</v>
+        <v>90923</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7906,41 +7921,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svartnäsudden, Svartnäsudden, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654279</v>
+        <v>654153</v>
       </c>
       <c r="R67" t="n">
-        <v>7007930</v>
+        <v>7008523</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7967,24 +7982,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7999,19 +7999,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120086920</v>
+        <v>120088520</v>
       </c>
       <c r="B68" t="n">
         <v>57320</v>
@@ -8047,14 +8047,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654164</v>
+        <v>654121</v>
       </c>
       <c r="R68" t="n">
-        <v>7008398</v>
+        <v>7008041</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8116,12 +8116,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 18809-2024 artfynd.xlsx
+++ b/artfynd/A 18809-2024 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120085759</v>
+        <v>120085068</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,25 +2011,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654293</v>
+        <v>654217</v>
       </c>
       <c r="R14" t="n">
-        <v>7008191</v>
+        <v>7008168</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,9 +2072,19 @@
           <t>2024-09-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,22 +2099,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120085068</v>
+        <v>120085759</v>
       </c>
       <c r="B15" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,25 +2123,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2141,13 +2151,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654217</v>
+        <v>654293</v>
       </c>
       <c r="R15" t="n">
-        <v>7008168</v>
+        <v>7008191</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2174,19 +2184,9 @@
           <t>2024-09-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,12 +2201,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120082934</v>
+        <v>120087102</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7469,38 +7469,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Svartnäset, Svartnäset, Ång</t>
+          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654181</v>
+        <v>654149</v>
       </c>
       <c r="R63" t="n">
-        <v>7007955</v>
+        <v>7008498</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7532,7 +7541,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7542,7 +7551,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7569,10 +7578,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120082271</v>
+        <v>120082934</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7581,25 +7590,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7609,10 +7618,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654150</v>
+        <v>654181</v>
       </c>
       <c r="R64" t="n">
-        <v>7007925</v>
+        <v>7007955</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7644,7 +7653,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7654,12 +7663,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7686,10 +7690,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120087102</v>
+        <v>120082271</v>
       </c>
       <c r="B65" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7698,47 +7702,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stubbhällmyran, Stubbhällmyran, Ång</t>
+          <t>Svartnäset, Svartnäset, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654149</v>
+        <v>654150</v>
       </c>
       <c r="R65" t="n">
-        <v>7008498</v>
+        <v>7007925</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7770,7 +7765,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7780,7 +7775,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
